--- a/data.xlsx
+++ b/data.xlsx
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Hoja1'!$A$1:$O$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hoja2'!$A$1:$S$208</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +72,13 @@
       <u val="single"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -85,8 +91,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00106EBE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -103,12 +114,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <right style="medium">
+        <color rgb="00FFFFFF"/>
+      </right>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -124,6 +140,10 @@
     </xf>
     <xf numFmtId="22" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -7198,99 +7218,120 @@
   </sheetPr>
   <dimension ref="A1:S208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4.14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="77" customWidth="1" min="3" max="3"/>
+    <col width="40.57" customWidth="1" min="4" max="4"/>
+    <col width="19.57" customWidth="1" min="5" max="5"/>
+    <col width="15.43" customWidth="1" min="6" max="6"/>
+    <col width="17.71" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15.71" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="9.289999999999999" customWidth="1" min="11" max="11"/>
+    <col width="17.71" customWidth="1" min="12" max="12"/>
+    <col width="47.71" customWidth="1" min="13" max="13"/>
+    <col width="255.71" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="35.43" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="24.71" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Work Item Type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Iteration Path</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Estados</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Finish Date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Finish Date Chinalco</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Aplicación</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Ticket Chinalco</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Ticket SyC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Assigned To</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Tipo Caso</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Tipo Evento</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>Tipo Estabilización</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
@@ -7321,13 +7362,13 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="8" t="n">
         <v>45900.79166666666</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="8" t="n">
         <v>45914.79166666666</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="8" t="n">
         <v>46019.79166666666</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -7398,13 +7439,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="8" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="8" t="n">
         <v>45937.57916666667</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="8" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -7475,9 +7516,9 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>WAPSA web</t>
@@ -7542,9 +7583,9 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>WAPSA web</t>
@@ -7609,9 +7650,9 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>WAPSA web</t>
@@ -7676,11 +7717,11 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="8" t="n">
         <v>45391.79166666666</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -7749,13 +7790,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="8" t="n">
         <v>45810.79166666666</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="8" t="n">
         <v>45873.79166666666</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="8" t="n">
         <v>45937.57847222222</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -7830,13 +7871,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="8" t="n">
         <v>45863.71805555555</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="8" t="n">
         <v>45863.71805555555</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="8" t="n">
         <v>45901.26458333333</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -7911,13 +7952,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="8" t="n">
         <v>45487.79166666666</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="8" t="n">
         <v>45487.79166666666</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="8" t="n">
         <v>45530.79166666666</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -7994,13 +8035,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="8" t="n">
         <v>45544.79166666666</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="8" t="n">
         <v>45544.79166666666</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="8" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -8077,13 +8118,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="8" t="n">
         <v>45933.35277777778</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="8" t="n">
         <v>45937.575</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="8" t="n">
         <v>45959.20069444444</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -8158,13 +8199,13 @@
           <t>[Ver 4.1]</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="8" t="n">
         <v>45937.58055555556</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="8" t="n">
         <v>45937.58055555556</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="8" t="n">
         <v>45959.20069444444</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -8239,13 +8280,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="8" t="n">
         <v>45414.79166666666</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="8" t="n">
         <v>45431.79166666666</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="8" t="n">
         <v>45426.79166666666</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -8320,13 +8361,13 @@
           <t>[2.16.1]</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="8" t="n">
         <v>45414.79166666666</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="8" t="n">
         <v>45440.79166666666</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="8" t="n">
         <v>45438.79166666666</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -8401,13 +8442,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="8" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="8" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="8" t="n">
         <v>45372.79166666666</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -8485,11 +8526,11 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="8" t="n">
         <v>46073.42986111111</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
@@ -8558,13 +8599,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="8" t="n">
         <v>45704.79166666666</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="8" t="n">
         <v>45715.79166666666</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="8" t="n">
         <v>45728.79166666666</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -8639,13 +8680,13 @@
           <t>[Ver. 2.22]</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="8" t="n">
         <v>45771.79166666666</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="8" t="n">
         <v>45774.79166666666</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="8" t="n">
         <v>45810.79166666666</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -8720,13 +8761,13 @@
           <t>[Ver. 2.23]</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="8" t="n">
         <v>45819.36388888889</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="8" t="n">
         <v>45819.36388888889</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="8" t="n">
         <v>45832.42916666667</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -8801,13 +8842,13 @@
           <t>[Ver 4.0]</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="8" t="n">
         <v>45819.36388888889</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="8" t="n">
         <v>45819.36388888889</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="8" t="n">
         <v>45827.79166666666</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -8882,13 +8923,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="8" t="n">
         <v>45327.79166666666</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="8" t="n">
         <v>45354.79166666666</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -8979,13 +9020,13 @@
           <t>[Ver.2.4]</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="8" t="n">
         <v>45337.79166666666</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="8" t="n">
         <v>45342.79166666666</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="8" t="n">
         <v>45343.79166666666</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -9056,13 +9097,13 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="8" t="n">
         <v>46019.79166666666</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="8" t="n">
         <v>46022.65347222222</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="8" t="n">
         <v>46045.65347222222</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -9135,13 +9176,13 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="8" t="n">
         <v>46019.79166666666</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="8" t="n">
         <v>46021.79166666666</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="8" t="n">
         <v>46045.65555555555</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -9218,13 +9259,13 @@
           <t>v2.25.3</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="8" t="n">
         <v>45988.79166666666</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="8" t="n">
         <v>45992.59097222222</v>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" s="8" t="n"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -9285,13 +9326,13 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="8" t="n">
         <v>45992.42916666667</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="8" t="n">
         <v>45991.79166666666</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="8" t="n">
         <v>45995.79166666666</v>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -9362,13 +9403,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="8" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="8" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="8" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -9445,13 +9486,13 @@
           <t>[Ver. 2.20]</t>
         </is>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="8" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="8" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="8" t="n">
         <v>45665.79166666666</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -9526,13 +9567,13 @@
           <t>[Ver. 1.1]</t>
         </is>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="8" t="n">
         <v>45490.79166666666</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="8" t="n">
         <v>45490.79166666666</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="8" t="n">
         <v>45511.79166666666</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -9603,13 +9644,13 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="8" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="8" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="8" t="n">
         <v>45550.79166666666</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -9682,13 +9723,13 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="8" t="n">
         <v>45427.79166666666</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="8" t="n">
         <v>45439.79166666666</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="8" t="n">
         <v>45440.79166666666</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -9761,13 +9802,13 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="8" t="n">
         <v>45348.79166666666</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="8" t="n">
         <v>45354.79166666666</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -9838,13 +9879,13 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="8" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="8" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="8" t="n">
         <v>45369.79166666666</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -9917,13 +9958,13 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="8" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="8" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="8" t="n">
         <v>45383.79166666666</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -9996,13 +10037,13 @@
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="8" t="n">
         <v>45396.79166666666</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="8" t="n">
         <v>45415.79166666666</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="8" t="n">
         <v>45415.79166666666</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -10079,13 +10120,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="8" t="n">
         <v>45911.30347222222</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="8" t="n">
         <v>45937.57916666667</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" s="8" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -10156,9 +10197,9 @@
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10227,13 +10268,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="8" t="n">
         <v>45930.79166666666</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="8" t="n">
         <v>45937.45138888889</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I39" s="8" t="n">
         <v>45937.57986111111</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -10304,9 +10345,9 @@
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10375,11 +10416,11 @@
           <t>[Ver. 2.27]; [Ver. 2.28]</t>
         </is>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G41" s="8" t="n">
         <v>45991.79166666666</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10448,13 +10489,13 @@
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" s="6" t="n">
+      <c r="G42" s="8" t="n">
         <v>45931.79166666666</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H42" s="8" t="n">
         <v>46008.79166666666</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" s="8" t="n">
         <v>46008.79166666666</v>
       </c>
       <c r="J42" t="inlineStr">
@@ -10529,13 +10570,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="8" t="n">
         <v>45854.72638888889</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" s="8" t="n">
         <v>45854.72638888889</v>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" s="8" t="n"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10608,13 +10649,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="8" t="n">
         <v>45417.79166666666</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" s="8" t="n">
         <v>45424.79166666666</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" s="8" t="n">
         <v>45421.79166666666</v>
       </c>
       <c r="J44" t="inlineStr">
@@ -10689,13 +10730,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" s="8" t="n">
         <v>45426.79166666666</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H45" s="8" t="n">
         <v>45476.79166666666</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" s="8" t="n">
         <v>45538.79166666666</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -10770,13 +10811,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G46" s="8" t="n">
         <v>45445.79166666666</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H46" s="8" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I46" s="8" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -10851,13 +10892,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G47" s="6" t="n">
+      <c r="G47" s="8" t="n">
         <v>45382.79166666666</v>
       </c>
-      <c r="H47" s="6" t="n">
+      <c r="H47" s="8" t="n">
         <v>45388.79166666666</v>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" s="8" t="n">
         <v>45418.79166666666</v>
       </c>
       <c r="J47" t="inlineStr">
@@ -10928,13 +10969,13 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" s="6" t="n">
+      <c r="G48" s="8" t="n">
         <v>45418.79166666666</v>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H48" s="8" t="n">
         <v>45421.79166666666</v>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I48" s="8" t="n">
         <v>45421.79166666666</v>
       </c>
       <c r="J48" t="inlineStr">
@@ -11005,13 +11046,13 @@
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" s="6" t="n">
+      <c r="G49" s="8" t="n">
         <v>45418.79166666666</v>
       </c>
-      <c r="H49" s="6" t="n">
+      <c r="H49" s="8" t="n">
         <v>45421.79166666666</v>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" s="8" t="n">
         <v>45421.79166666666</v>
       </c>
       <c r="J49" t="inlineStr">
@@ -11086,11 +11127,11 @@
           <t>[Ver. 1.3]</t>
         </is>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G50" s="8" t="n">
         <v>45446.79166666666</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Wapsa ES</t>
@@ -11163,13 +11204,13 @@
           <t>[Ver. 1.3]</t>
         </is>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G51" s="8" t="n">
         <v>45420.79166666666</v>
       </c>
-      <c r="H51" s="6" t="n">
+      <c r="H51" s="8" t="n">
         <v>45424.79166666666</v>
       </c>
-      <c r="I51" s="6" t="n">
+      <c r="I51" s="8" t="n">
         <v>45511.79166666666</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -11244,13 +11285,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G52" s="8" t="n">
         <v>45439.79166666666</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H52" s="8" t="n">
         <v>45482.79166666666</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I52" s="8" t="n">
         <v>45489.79166666666</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -11325,13 +11366,13 @@
           <t>[Ver. 1.1]</t>
         </is>
       </c>
-      <c r="G53" s="6" t="n">
+      <c r="G53" s="8" t="n">
         <v>45420.79166666666</v>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="H53" s="8" t="n">
         <v>45421.79166666666</v>
       </c>
-      <c r="I53" s="6" t="n">
+      <c r="I53" s="8" t="n">
         <v>45511.79166666666</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -11406,13 +11447,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G54" s="6" t="n">
+      <c r="G54" s="8" t="n">
         <v>45900.79166666666</v>
       </c>
-      <c r="H54" s="6" t="n">
+      <c r="H54" s="8" t="n">
         <v>45901.79166666666</v>
       </c>
-      <c r="I54" s="6" t="n">
+      <c r="I54" s="8" t="n">
         <v>45937.57847222222</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -11487,13 +11528,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G55" s="6" t="n">
+      <c r="G55" s="8" t="n">
         <v>45874.79166666666</v>
       </c>
-      <c r="H55" s="6" t="n">
+      <c r="H55" s="8" t="n">
         <v>45900.79166666666</v>
       </c>
-      <c r="I55" s="6" t="n">
+      <c r="I55" s="8" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -11568,13 +11609,13 @@
           <t>[Ver 4.1]</t>
         </is>
       </c>
-      <c r="G56" s="6" t="n">
+      <c r="G56" s="8" t="n">
         <v>45739.79166666666</v>
       </c>
-      <c r="H56" s="6" t="n">
+      <c r="H56" s="8" t="n">
         <v>45823.79166666666</v>
       </c>
-      <c r="I56" s="6" t="n">
+      <c r="I56" s="8" t="n">
         <v>45937.60625</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -11649,13 +11690,13 @@
           <t>[Ver. 2.22]</t>
         </is>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="G57" s="8" t="n">
         <v>45724.79166666666</v>
       </c>
-      <c r="H57" s="6" t="n">
+      <c r="H57" s="8" t="n">
         <v>45725.79166666666</v>
       </c>
-      <c r="I57" s="6" t="n">
+      <c r="I57" s="8" t="n">
         <v>45810.79166666666</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -11726,13 +11767,13 @@
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" s="6" t="n">
+      <c r="G58" s="8" t="n">
         <v>46022.79166666666</v>
       </c>
-      <c r="H58" s="6" t="n">
+      <c r="H58" s="8" t="n">
         <v>46052.79166666666</v>
       </c>
-      <c r="I58" s="6" t="n">
+      <c r="I58" s="8" t="n">
         <v>46052.79166666666</v>
       </c>
       <c r="J58" t="inlineStr">
@@ -11803,13 +11844,13 @@
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" s="6" t="n">
+      <c r="G59" s="8" t="n">
         <v>45987.11875</v>
       </c>
-      <c r="H59" s="6" t="n">
+      <c r="H59" s="8" t="n">
         <v>45996.11875</v>
       </c>
-      <c r="I59" s="6" t="n">
+      <c r="I59" s="8" t="n">
         <v>45996.11875</v>
       </c>
       <c r="J59" t="inlineStr">
@@ -11884,13 +11925,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G60" s="6" t="n">
+      <c r="G60" s="8" t="n">
         <v>45762.79166666666</v>
       </c>
-      <c r="H60" s="6" t="n">
+      <c r="H60" s="8" t="n">
         <v>45823.79166666666</v>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" s="8" t="n"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>WAPSA web</t>
@@ -11963,13 +12004,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G61" s="6" t="n">
+      <c r="G61" s="8" t="n">
         <v>45739.79166666666</v>
       </c>
-      <c r="H61" s="6" t="n">
+      <c r="H61" s="8" t="n">
         <v>45822.79166666666</v>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" s="8" t="n"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -12042,13 +12083,13 @@
           <t>[Ver. 2.22]</t>
         </is>
       </c>
-      <c r="G62" s="6" t="n">
+      <c r="G62" s="8" t="n">
         <v>45713.79166666666</v>
       </c>
-      <c r="H62" s="6" t="n">
+      <c r="H62" s="8" t="n">
         <v>45726.79166666666</v>
       </c>
-      <c r="I62" s="6" t="n">
+      <c r="I62" s="8" t="n">
         <v>45810.79166666666</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -12119,13 +12160,13 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" s="6" t="n">
+      <c r="G63" s="8" t="n">
         <v>45864.14652777778</v>
       </c>
-      <c r="H63" s="6" t="n">
+      <c r="H63" s="8" t="n">
         <v>45873.79166666666</v>
       </c>
-      <c r="I63" s="6" t="n">
+      <c r="I63" s="8" t="n">
         <v>45873.79166666666</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -12192,13 +12233,13 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" s="6" t="n">
+      <c r="G64" s="8" t="n">
         <v>45886.79166666666</v>
       </c>
-      <c r="H64" s="6" t="n">
+      <c r="H64" s="8" t="n">
         <v>45931.79166666666</v>
       </c>
-      <c r="I64" s="6" t="n">
+      <c r="I64" s="8" t="n">
         <v>45930.79166666666</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -12265,13 +12306,13 @@
           <t>[Ver. 2.24.1]</t>
         </is>
       </c>
-      <c r="G65" s="6" t="n">
+      <c r="G65" s="8" t="n">
         <v>45926.29791666667</v>
       </c>
-      <c r="H65" s="6" t="n">
+      <c r="H65" s="8" t="n">
         <v>45927.79166666666</v>
       </c>
-      <c r="I65" s="6" t="n">
+      <c r="I65" s="8" t="n">
         <v>45959.2</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -12346,13 +12387,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G66" s="6" t="n">
+      <c r="G66" s="8" t="n">
         <v>45438.79166666666</v>
       </c>
-      <c r="H66" s="6" t="n">
+      <c r="H66" s="8" t="n">
         <v>45441.79166666666</v>
       </c>
-      <c r="I66" s="6" t="n">
+      <c r="I66" s="8" t="n">
         <v>45522.79166666666</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -12423,13 +12464,13 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" s="6" t="n">
+      <c r="G67" s="8" t="n">
         <v>45517.79166666666</v>
       </c>
-      <c r="H67" s="6" t="n">
+      <c r="H67" s="8" t="n">
         <v>45517.79166666666</v>
       </c>
-      <c r="I67" s="6" t="n">
+      <c r="I67" s="8" t="n">
         <v>45538.79166666666</v>
       </c>
       <c r="J67" t="inlineStr">
@@ -12502,13 +12543,13 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" s="6" t="n">
+      <c r="G68" s="8" t="n">
         <v>45546.79166666666</v>
       </c>
-      <c r="H68" s="6" t="n">
+      <c r="H68" s="8" t="n">
         <v>45546.79166666666</v>
       </c>
-      <c r="I68" s="6" t="n">
+      <c r="I68" s="8" t="n">
         <v>45574.79166666666</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -12581,13 +12622,13 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" s="6" t="n">
+      <c r="G69" s="8" t="n">
         <v>45540.79166666666</v>
       </c>
-      <c r="H69" s="6" t="n">
+      <c r="H69" s="8" t="n">
         <v>45540.79166666666</v>
       </c>
-      <c r="I69" s="6" t="n">
+      <c r="I69" s="8" t="n">
         <v>45540.79166666666</v>
       </c>
       <c r="J69" t="inlineStr">
@@ -12658,13 +12699,13 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" s="6" t="n">
+      <c r="G70" s="8" t="n">
         <v>45558.79166666666</v>
       </c>
-      <c r="H70" s="6" t="n">
+      <c r="H70" s="8" t="n">
         <v>45558.79166666666</v>
       </c>
-      <c r="I70" s="6" t="n">
+      <c r="I70" s="8" t="n">
         <v>45558.79166666666</v>
       </c>
       <c r="J70" t="inlineStr">
@@ -12739,13 +12780,13 @@
           <t>[Ver 2.25]; [Ver 4.1]</t>
         </is>
       </c>
-      <c r="G71" s="6" t="n">
+      <c r="G71" s="8" t="n">
         <v>45578.79166666666</v>
       </c>
-      <c r="H71" s="6" t="n">
+      <c r="H71" s="8" t="n">
         <v>45904.26666666667</v>
       </c>
-      <c r="I71" s="6" t="n">
+      <c r="I71" s="8" t="n">
         <v>45937.60625</v>
       </c>
       <c r="J71" t="inlineStr">
@@ -12820,13 +12861,13 @@
           <t>[Ver 4.1]</t>
         </is>
       </c>
-      <c r="G72" s="6" t="n">
+      <c r="G72" s="8" t="n">
         <v>45643.79166666666</v>
       </c>
-      <c r="H72" s="6" t="n">
+      <c r="H72" s="8" t="n">
         <v>45904.26111111111</v>
       </c>
-      <c r="I72" s="6" t="n">
+      <c r="I72" s="8" t="n">
         <v>45937.60625</v>
       </c>
       <c r="J72" t="inlineStr">
@@ -12901,13 +12942,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G73" s="6" t="n">
+      <c r="G73" s="8" t="n">
         <v>45915.33055555556</v>
       </c>
-      <c r="H73" s="6" t="n">
+      <c r="H73" s="8" t="n">
         <v>45932.30555555555</v>
       </c>
-      <c r="I73" s="6" t="n">
+      <c r="I73" s="8" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J73" t="inlineStr">
@@ -12974,13 +13015,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G74" s="6" t="n">
+      <c r="G74" s="8" t="n">
         <v>45915.33055555556</v>
       </c>
-      <c r="H74" s="6" t="n">
+      <c r="H74" s="8" t="n">
         <v>45932.60069444445</v>
       </c>
-      <c r="I74" s="6" t="n">
+      <c r="I74" s="8" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J74" t="inlineStr">
@@ -13051,13 +13092,13 @@
           <t>[Ver. 2.24.1]</t>
         </is>
       </c>
-      <c r="G75" s="6" t="n">
+      <c r="G75" s="8" t="n">
         <v>45924.79166666666</v>
       </c>
-      <c r="H75" s="6" t="n">
+      <c r="H75" s="8" t="n">
         <v>45926.29861111111</v>
       </c>
-      <c r="I75" s="6" t="n">
+      <c r="I75" s="8" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J75" t="inlineStr">
@@ -13132,13 +13173,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G76" s="6" t="n">
+      <c r="G76" s="8" t="n">
         <v>45547.79166666666</v>
       </c>
-      <c r="H76" s="6" t="n">
+      <c r="H76" s="8" t="n">
         <v>45558.79166666666</v>
       </c>
-      <c r="I76" s="6" t="n">
+      <c r="I76" s="8" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J76" t="inlineStr">
@@ -13215,13 +13256,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G77" s="6" t="n">
+      <c r="G77" s="8" t="n">
         <v>45545.79166666666</v>
       </c>
-      <c r="H77" s="6" t="n">
+      <c r="H77" s="8" t="n">
         <v>45545.79166666666</v>
       </c>
-      <c r="I77" s="6" t="n">
+      <c r="I77" s="8" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J77" t="inlineStr">
@@ -13299,13 +13340,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G78" s="6" t="n">
+      <c r="G78" s="8" t="n">
         <v>45540.79166666666</v>
       </c>
-      <c r="H78" s="6" t="n">
+      <c r="H78" s="8" t="n">
         <v>45543.79166666666</v>
       </c>
-      <c r="I78" s="6" t="n">
+      <c r="I78" s="8" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J78" t="inlineStr">
@@ -13383,13 +13424,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G79" s="6" t="n">
+      <c r="G79" s="8" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="H79" s="6" t="n">
+      <c r="H79" s="8" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="I79" s="6" t="n">
+      <c r="I79" s="8" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J79" t="inlineStr">
@@ -13460,13 +13501,13 @@
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" s="6" t="n">
+      <c r="G80" s="8" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="H80" s="6" t="n">
+      <c r="H80" s="8" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="I80" s="6" t="n">
+      <c r="I80" s="8" t="n">
         <v>45575.79166666666</v>
       </c>
       <c r="J80" t="inlineStr">
@@ -13543,13 +13584,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G81" s="6" t="n">
+      <c r="G81" s="8" t="n">
         <v>45559.79166666666</v>
       </c>
-      <c r="H81" s="6" t="n">
+      <c r="H81" s="8" t="n">
         <v>45564.79166666666</v>
       </c>
-      <c r="I81" s="6" t="n">
+      <c r="I81" s="8" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J81" t="inlineStr">
@@ -13620,13 +13661,13 @@
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" s="6" t="n">
+      <c r="G82" s="8" t="n">
         <v>45578.79166666666</v>
       </c>
-      <c r="H82" s="6" t="n">
+      <c r="H82" s="8" t="n">
         <v>45585.79166666666</v>
       </c>
-      <c r="I82" s="6" t="n">
+      <c r="I82" s="8" t="n">
         <v>45585.79166666666</v>
       </c>
       <c r="J82" t="inlineStr">
@@ -13697,13 +13738,13 @@
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" s="6" t="n">
+      <c r="G83" s="8" t="n">
         <v>45870.79166666666</v>
       </c>
-      <c r="H83" s="6" t="n">
+      <c r="H83" s="8" t="n">
         <v>45986.79166666666</v>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" s="8" t="n"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>WAPSA Web</t>
@@ -13768,13 +13809,13 @@
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" s="6" t="n">
+      <c r="G84" s="8" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="H84" s="6" t="n">
+      <c r="H84" s="8" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="I84" s="6" t="n">
+      <c r="I84" s="8" t="n">
         <v>45552.79166666666</v>
       </c>
       <c r="J84" t="inlineStr">
@@ -13845,13 +13886,13 @@
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" s="6" t="n">
+      <c r="G85" s="8" t="n">
         <v>45589.79166666666</v>
       </c>
-      <c r="H85" s="6" t="n">
+      <c r="H85" s="8" t="n">
         <v>45589.79166666666</v>
       </c>
-      <c r="I85" s="6" t="n">
+      <c r="I85" s="8" t="n">
         <v>45606.79166666666</v>
       </c>
       <c r="J85" t="inlineStr">
@@ -13928,13 +13969,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G86" s="6" t="n">
+      <c r="G86" s="8" t="n">
         <v>45592.79166666666</v>
       </c>
-      <c r="H86" s="6" t="n">
+      <c r="H86" s="8" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="I86" s="6" t="n">
+      <c r="I86" s="8" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J86" t="inlineStr">
@@ -14005,13 +14046,13 @@
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" s="6" t="n">
+      <c r="G87" s="8" t="n">
         <v>45595.79166666666</v>
       </c>
-      <c r="H87" s="6" t="n">
+      <c r="H87" s="8" t="n">
         <v>45595.79166666666</v>
       </c>
-      <c r="I87" s="6" t="n">
+      <c r="I87" s="8" t="n">
         <v>45616.79166666666</v>
       </c>
       <c r="J87" t="inlineStr">
@@ -14084,13 +14125,13 @@
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" s="6" t="n">
+      <c r="G88" s="8" t="n">
         <v>45595.79166666666</v>
       </c>
-      <c r="H88" s="6" t="n">
+      <c r="H88" s="8" t="n">
         <v>45614.79166666666</v>
       </c>
-      <c r="I88" s="6" t="n">
+      <c r="I88" s="8" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J88" t="inlineStr">
@@ -14161,13 +14202,13 @@
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" s="6" t="n">
+      <c r="G89" s="8" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="H89" s="6" t="n">
+      <c r="H89" s="8" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="I89" s="6" t="n">
+      <c r="I89" s="8" t="n">
         <v>45606.79166666666</v>
       </c>
       <c r="J89" t="inlineStr">
@@ -14238,13 +14279,13 @@
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" s="6" t="n">
+      <c r="G90" s="8" t="n">
         <v>45595.79166666666</v>
       </c>
-      <c r="H90" s="6" t="n">
+      <c r="H90" s="8" t="n">
         <v>45614.79166666666</v>
       </c>
-      <c r="I90" s="6" t="n">
+      <c r="I90" s="8" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J90" t="inlineStr">
@@ -14321,13 +14362,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G91" s="6" t="n">
+      <c r="G91" s="8" t="n">
         <v>45614.79166666666</v>
       </c>
-      <c r="H91" s="6" t="n">
+      <c r="H91" s="8" t="n">
         <v>45614.79166666666</v>
       </c>
-      <c r="I91" s="6" t="n">
+      <c r="I91" s="8" t="n">
         <v>45662.79166666666</v>
       </c>
       <c r="J91" t="inlineStr">
@@ -14398,13 +14439,13 @@
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" s="6" t="n">
+      <c r="G92" s="8" t="n">
         <v>45608.79166666666</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H92" s="8" t="n">
         <v>45617.79166666666</v>
       </c>
-      <c r="I92" s="6" t="n">
+      <c r="I92" s="8" t="n">
         <v>45621.79166666666</v>
       </c>
       <c r="J92" t="inlineStr">
@@ -14481,13 +14522,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G93" s="6" t="n">
+      <c r="G93" s="8" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H93" s="8" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="I93" s="6" t="n">
+      <c r="I93" s="8" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J93" t="inlineStr">
@@ -14562,13 +14603,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G94" s="6" t="n">
+      <c r="G94" s="8" t="n">
         <v>45617.79166666666</v>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H94" s="8" t="n">
         <v>45617.79166666666</v>
       </c>
-      <c r="I94" s="6" t="n">
+      <c r="I94" s="8" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J94" t="inlineStr">
@@ -14643,13 +14684,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G95" s="6" t="n">
+      <c r="G95" s="8" t="n">
         <v>45627.79166666666</v>
       </c>
-      <c r="H95" s="6" t="n">
+      <c r="H95" s="8" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="I95" s="6" t="n">
+      <c r="I95" s="8" t="n">
         <v>45671.79166666666</v>
       </c>
       <c r="J95" t="inlineStr">
@@ -14724,13 +14765,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G96" s="6" t="n">
+      <c r="G96" s="8" t="n">
         <v>45623.79166666666</v>
       </c>
-      <c r="H96" s="6" t="n">
+      <c r="H96" s="8" t="n">
         <v>45623.79166666666</v>
       </c>
-      <c r="I96" s="6" t="n">
+      <c r="I96" s="8" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J96" t="inlineStr">
@@ -14801,13 +14842,13 @@
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" s="6" t="n">
+      <c r="G97" s="8" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="H97" s="6" t="n">
+      <c r="H97" s="8" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="I97" s="6" t="n">
+      <c r="I97" s="8" t="n">
         <v>45680.79166666666</v>
       </c>
       <c r="J97" t="inlineStr">
@@ -14884,13 +14925,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G98" s="6" t="n">
+      <c r="G98" s="8" t="n">
         <v>45388.79166666666</v>
       </c>
-      <c r="H98" s="6" t="n">
+      <c r="H98" s="8" t="n">
         <v>45389.79166666666</v>
       </c>
-      <c r="I98" s="6" t="n">
+      <c r="I98" s="8" t="n">
         <v>45418.79166666666</v>
       </c>
       <c r="J98" t="inlineStr">
@@ -14961,13 +15002,13 @@
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" s="6" t="n">
+      <c r="G99" s="8" t="n">
         <v>45396.79166666666</v>
       </c>
-      <c r="H99" s="6" t="n">
+      <c r="H99" s="8" t="n">
         <v>45435.79166666666</v>
       </c>
-      <c r="I99" s="6" t="n">
+      <c r="I99" s="8" t="n">
         <v>45435.79166666666</v>
       </c>
       <c r="J99" t="inlineStr">
@@ -15044,13 +15085,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G100" s="6" t="n">
+      <c r="G100" s="8" t="n">
         <v>45399.79166666666</v>
       </c>
-      <c r="H100" s="6" t="n">
+      <c r="H100" s="8" t="n">
         <v>45399.79166666666</v>
       </c>
-      <c r="I100" s="6" t="n">
+      <c r="I100" s="8" t="n">
         <v>45418.79166666666</v>
       </c>
       <c r="J100" t="inlineStr">
@@ -15125,13 +15166,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G101" s="6" t="n">
+      <c r="G101" s="8" t="n">
         <v>45398.79166666666</v>
       </c>
-      <c r="H101" s="6" t="n">
+      <c r="H101" s="8" t="n">
         <v>45398.79166666666</v>
       </c>
-      <c r="I101" s="6" t="n">
+      <c r="I101" s="8" t="n">
         <v>45418.79166666666</v>
       </c>
       <c r="J101" t="inlineStr">
@@ -15206,13 +15247,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G102" s="6" t="n">
+      <c r="G102" s="8" t="n">
         <v>45424.79166666666</v>
       </c>
-      <c r="H102" s="6" t="n">
+      <c r="H102" s="8" t="n">
         <v>45425.79166666666</v>
       </c>
-      <c r="I102" s="6" t="n">
+      <c r="I102" s="8" t="n">
         <v>45427.79166666666</v>
       </c>
       <c r="J102" t="inlineStr">
@@ -15283,13 +15324,13 @@
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" s="6" t="n">
+      <c r="G103" s="8" t="n">
         <v>45405.79166666666</v>
       </c>
-      <c r="H103" s="6" t="n">
+      <c r="H103" s="8" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="I103" s="6" t="n">
+      <c r="I103" s="8" t="n">
         <v>45432.79166666666</v>
       </c>
       <c r="J103" t="inlineStr">
@@ -15360,13 +15401,13 @@
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" s="6" t="n">
+      <c r="G104" s="8" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="H104" s="6" t="n">
+      <c r="H104" s="8" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="I104" s="6" t="n">
+      <c r="I104" s="8" t="n">
         <v>45432.79166666666</v>
       </c>
       <c r="J104" t="inlineStr">
@@ -15441,13 +15482,13 @@
           <t>[2.16.1]</t>
         </is>
       </c>
-      <c r="G105" s="6" t="n">
+      <c r="G105" s="8" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="H105" s="6" t="n">
+      <c r="H105" s="8" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="I105" s="6" t="n">
+      <c r="I105" s="8" t="n">
         <v>45438.79166666666</v>
       </c>
       <c r="J105" t="inlineStr">
@@ -15522,13 +15563,13 @@
           <t>[2.16.1]</t>
         </is>
       </c>
-      <c r="G106" s="6" t="n">
+      <c r="G106" s="8" t="n">
         <v>45433.79166666666</v>
       </c>
-      <c r="H106" s="6" t="n">
+      <c r="H106" s="8" t="n">
         <v>45433.79166666666</v>
       </c>
-      <c r="I106" s="6" t="n">
+      <c r="I106" s="8" t="n">
         <v>45438.79166666666</v>
       </c>
       <c r="J106" t="inlineStr">
@@ -15599,13 +15640,13 @@
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" s="6" t="n">
+      <c r="G107" s="8" t="n">
         <v>45438.79166666666</v>
       </c>
-      <c r="H107" s="6" t="n">
+      <c r="H107" s="8" t="n">
         <v>45438.79166666666</v>
       </c>
-      <c r="I107" s="6" t="n">
+      <c r="I107" s="8" t="n">
         <v>45438.79166666666</v>
       </c>
       <c r="J107" t="inlineStr">
@@ -15680,13 +15721,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G108" s="6" t="n">
+      <c r="G108" s="8" t="n">
         <v>45342.79166666666</v>
       </c>
-      <c r="H108" s="6" t="n">
+      <c r="H108" s="8" t="n">
         <v>45342.79166666666</v>
       </c>
-      <c r="I108" s="6" t="n">
+      <c r="I108" s="8" t="n">
         <v>45369.79166666666</v>
       </c>
       <c r="J108" t="inlineStr">
@@ -15763,13 +15804,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G109" s="6" t="n">
+      <c r="G109" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="H109" s="6" t="n">
+      <c r="H109" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="I109" s="6" t="n">
+      <c r="I109" s="8" t="n">
         <v>45431.79166666666</v>
       </c>
       <c r="J109" t="inlineStr">
@@ -15844,13 +15885,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G110" s="6" t="n">
+      <c r="G110" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="H110" s="6" t="n">
+      <c r="H110" s="8" t="n">
         <v>45361.79166666666</v>
       </c>
-      <c r="I110" s="6" t="n">
+      <c r="I110" s="8" t="n">
         <v>45376.79166666666</v>
       </c>
       <c r="J110" t="inlineStr">
@@ -15923,13 +15964,13 @@
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" s="6" t="n">
+      <c r="G111" s="8" t="n">
         <v>45368.79166666666</v>
       </c>
-      <c r="H111" s="6" t="n">
+      <c r="H111" s="8" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="I111" s="6" t="n">
+      <c r="I111" s="8" t="n">
         <v>45376.79166666666</v>
       </c>
       <c r="J111" t="inlineStr">
@@ -16002,13 +16043,13 @@
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" s="6" t="n">
+      <c r="G112" s="8" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="H112" s="6" t="n">
+      <c r="H112" s="8" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="I112" s="6" t="n">
+      <c r="I112" s="8" t="n">
         <v>45376.79166666666</v>
       </c>
       <c r="J112" t="inlineStr">
@@ -16079,11 +16120,11 @@
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" s="6" t="n">
+      <c r="G113" s="8" t="n">
         <v>45951.79166666666</v>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="8" t="n"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16148,13 +16189,13 @@
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" s="6" t="n">
+      <c r="G114" s="8" t="n">
         <v>45642.79166666666</v>
       </c>
-      <c r="H114" s="6" t="n">
+      <c r="H114" s="8" t="n">
         <v>45642.79166666666</v>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" s="8" t="n"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16227,13 +16268,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G115" s="6" t="n">
+      <c r="G115" s="8" t="n">
         <v>45845.25347222222</v>
       </c>
-      <c r="H115" s="6" t="n">
+      <c r="H115" s="8" t="n">
         <v>45845.79166666666</v>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" s="8" t="n"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16310,13 +16351,13 @@
           <t>[Ver. 4.29]</t>
         </is>
       </c>
-      <c r="G116" s="6" t="n">
+      <c r="G116" s="8" t="n">
         <v>46047.79166666666</v>
       </c>
-      <c r="H116" s="6" t="n">
+      <c r="H116" s="8" t="n">
         <v>46104.26111111111</v>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" s="8" t="n"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16385,13 +16426,13 @@
           <t>[Ver. 2.29]</t>
         </is>
       </c>
-      <c r="G117" s="6" t="n">
+      <c r="G117" s="8" t="n">
         <v>46050.79166666666</v>
       </c>
-      <c r="H117" s="6" t="n">
+      <c r="H117" s="8" t="n">
         <v>46062.46458333333</v>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" s="8" t="n"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16460,13 +16501,13 @@
           <t>[Ver. 2.28]; SLA</t>
         </is>
       </c>
-      <c r="G118" s="6" t="n">
+      <c r="G118" s="8" t="n">
         <v>46090.20833333334</v>
       </c>
-      <c r="H118" s="6" t="n">
+      <c r="H118" s="8" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" s="8" t="n"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16543,11 +16584,11 @@
           <t>[Ver. 2.28]; SLA</t>
         </is>
       </c>
-      <c r="G119" s="6" t="n">
+      <c r="G119" s="8" t="n">
         <v>46089.79166666666</v>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="H119" s="8" t="n"/>
+      <c r="I119" s="8" t="n"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>WapsaWeb</t>
@@ -16612,13 +16653,13 @@
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" s="6" t="n">
+      <c r="G120" s="8" t="n">
         <v>46094.54930555556</v>
       </c>
-      <c r="H120" s="6" t="n">
+      <c r="H120" s="8" t="n">
         <v>46094.54930555556</v>
       </c>
-      <c r="I120" s="6" t="n">
+      <c r="I120" s="8" t="n">
         <v>46097.30972222222</v>
       </c>
       <c r="J120" t="inlineStr">
@@ -16693,13 +16734,13 @@
           <t>[Ver. 2.28]</t>
         </is>
       </c>
-      <c r="G121" s="6" t="n">
+      <c r="G121" s="8" t="n">
         <v>46096.71458333333</v>
       </c>
-      <c r="H121" s="6" t="n">
+      <c r="H121" s="8" t="n">
         <v>46096.71458333333</v>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" s="8" t="n"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>WAPSA</t>
@@ -16768,13 +16809,13 @@
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" s="6" t="n">
+      <c r="G122" s="8" t="n">
         <v>46097.56319444445</v>
       </c>
-      <c r="H122" s="6" t="n">
+      <c r="H122" s="8" t="n">
         <v>46097.56319444445</v>
       </c>
-      <c r="I122" s="6" t="n">
+      <c r="I122" s="8" t="n">
         <v>46097.56319444445</v>
       </c>
       <c r="J122" t="inlineStr">
@@ -16841,9 +16882,9 @@
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="G123" s="8" t="n"/>
+      <c r="H123" s="8" t="n"/>
+      <c r="I123" s="8" t="n"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
@@ -16896,13 +16937,13 @@
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" s="6" t="n">
+      <c r="G124" s="8" t="n">
         <v>45725.79166666666</v>
       </c>
-      <c r="H124" s="6" t="n">
+      <c r="H124" s="8" t="n">
         <v>45725.79166666666</v>
       </c>
-      <c r="I124" s="6" t="n">
+      <c r="I124" s="8" t="n">
         <v>45725.79166666666</v>
       </c>
       <c r="J124" t="inlineStr">
@@ -16973,13 +17014,13 @@
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" s="6" t="n">
+      <c r="G125" s="8" t="n">
         <v>45410.79166666666</v>
       </c>
-      <c r="H125" s="6" t="n">
+      <c r="H125" s="8" t="n">
         <v>45454.79166666666</v>
       </c>
-      <c r="I125" s="6" t="n">
+      <c r="I125" s="8" t="n">
         <v>45460.79166666666</v>
       </c>
       <c r="J125" t="inlineStr">
@@ -17052,13 +17093,13 @@
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" s="6" t="n">
+      <c r="G126" s="8" t="n">
         <v>45453.79166666666</v>
       </c>
-      <c r="H126" s="6" t="n">
+      <c r="H126" s="8" t="n">
         <v>45454.79166666666</v>
       </c>
-      <c r="I126" s="6" t="n">
+      <c r="I126" s="8" t="n">
         <v>45454.79166666666</v>
       </c>
       <c r="J126" t="inlineStr">
@@ -17129,13 +17170,13 @@
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" s="6" t="n">
+      <c r="G127" s="8" t="n">
         <v>45466.79166666666</v>
       </c>
-      <c r="H127" s="6" t="n">
+      <c r="H127" s="8" t="n">
         <v>45466.79166666666</v>
       </c>
-      <c r="I127" s="6" t="n">
+      <c r="I127" s="8" t="n">
         <v>45466.79166666666</v>
       </c>
       <c r="J127" t="inlineStr">
@@ -17206,13 +17247,13 @@
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" s="6" t="n">
+      <c r="G128" s="8" t="n">
         <v>45761.79166666666</v>
       </c>
-      <c r="H128" s="6" t="n">
+      <c r="H128" s="8" t="n">
         <v>45769.79166666666</v>
       </c>
-      <c r="I128" s="6" t="n">
+      <c r="I128" s="8" t="n">
         <v>45809.79166666666</v>
       </c>
       <c r="J128" t="inlineStr">
@@ -17285,13 +17326,13 @@
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" s="6" t="n">
+      <c r="G129" s="8" t="n">
         <v>45747.79166666666</v>
       </c>
-      <c r="H129" s="6" t="n">
+      <c r="H129" s="8" t="n">
         <v>45764.39930555555</v>
       </c>
-      <c r="I129" s="6" t="n">
+      <c r="I129" s="8" t="n">
         <v>45810.79166666666</v>
       </c>
       <c r="J129" t="inlineStr">
@@ -17356,13 +17397,13 @@
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" s="6" t="n">
+      <c r="G130" s="8" t="n">
         <v>45815.29375</v>
       </c>
-      <c r="H130" s="6" t="n">
+      <c r="H130" s="8" t="n">
         <v>45815.37708333333</v>
       </c>
-      <c r="I130" s="6" t="n">
+      <c r="I130" s="8" t="n">
         <v>45822.4375</v>
       </c>
       <c r="J130" t="inlineStr">
@@ -17433,13 +17474,13 @@
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" s="6" t="n">
+      <c r="G131" s="8" t="n">
         <v>45813.79166666666</v>
       </c>
-      <c r="H131" s="6" t="n">
+      <c r="H131" s="8" t="n">
         <v>45818.33819444444</v>
       </c>
-      <c r="I131" s="6" t="n">
+      <c r="I131" s="8" t="n">
         <v>45832.42916666667</v>
       </c>
       <c r="J131" t="inlineStr">
@@ -17510,13 +17551,13 @@
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" s="6" t="n">
+      <c r="G132" s="8" t="n">
         <v>45820.51458333333</v>
       </c>
-      <c r="H132" s="6" t="n">
+      <c r="H132" s="8" t="n">
         <v>45820.51458333333</v>
       </c>
-      <c r="I132" s="6" t="n">
+      <c r="I132" s="8" t="n">
         <v>45827.79166666666</v>
       </c>
       <c r="J132" t="inlineStr">
@@ -17587,13 +17628,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G133" s="6" t="n">
+      <c r="G133" s="8" t="n">
         <v>45851.79166666666</v>
       </c>
-      <c r="H133" s="6" t="n">
+      <c r="H133" s="8" t="n">
         <v>45859.42916666667</v>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" s="8" t="n"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -17662,13 +17703,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G134" s="6" t="n">
+      <c r="G134" s="8" t="n">
         <v>45856.60833333333</v>
       </c>
-      <c r="H134" s="6" t="n">
+      <c r="H134" s="8" t="n">
         <v>45856.60833333333</v>
       </c>
-      <c r="I134" s="6" t="n">
+      <c r="I134" s="8" t="n">
         <v>45859.375</v>
       </c>
       <c r="J134" t="inlineStr">
@@ -17739,13 +17780,13 @@
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" s="6" t="n">
+      <c r="G135" s="8" t="n">
         <v>45453.79166666666</v>
       </c>
-      <c r="H135" s="6" t="n">
+      <c r="H135" s="8" t="n">
         <v>45453.79166666666</v>
       </c>
-      <c r="I135" s="6" t="n">
+      <c r="I135" s="8" t="n">
         <v>45460.79166666666</v>
       </c>
       <c r="J135" t="inlineStr">
@@ -17818,13 +17859,13 @@
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" s="6" t="n">
+      <c r="G136" s="8" t="n">
         <v>45460.79166666666</v>
       </c>
-      <c r="H136" s="6" t="n">
+      <c r="H136" s="8" t="n">
         <v>45461.79166666666</v>
       </c>
-      <c r="I136" s="6" t="n">
+      <c r="I136" s="8" t="n">
         <v>45490.79166666666</v>
       </c>
       <c r="J136" t="inlineStr">
@@ -17897,13 +17938,13 @@
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" s="6" t="n">
+      <c r="G137" s="8" t="n">
         <v>45461.79166666666</v>
       </c>
-      <c r="H137" s="6" t="n">
+      <c r="H137" s="8" t="n">
         <v>45461.79166666666</v>
       </c>
-      <c r="I137" s="6" t="n">
+      <c r="I137" s="8" t="n">
         <v>45510.79166666666</v>
       </c>
       <c r="J137" t="inlineStr">
@@ -17976,13 +18017,13 @@
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" s="6" t="n">
+      <c r="G138" s="8" t="n">
         <v>45475.79166666666</v>
       </c>
-      <c r="H138" s="6" t="n">
+      <c r="H138" s="8" t="n">
         <v>45475.79166666666</v>
       </c>
-      <c r="I138" s="6" t="n">
+      <c r="I138" s="8" t="n">
         <v>45475.79166666666</v>
       </c>
       <c r="J138" t="inlineStr">
@@ -18053,13 +18094,13 @@
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" s="6" t="n">
+      <c r="G139" s="8" t="n">
         <v>45481.79166666666</v>
       </c>
-      <c r="H139" s="6" t="n">
+      <c r="H139" s="8" t="n">
         <v>45481.79166666666</v>
       </c>
-      <c r="I139" s="6" t="n">
+      <c r="I139" s="8" t="n">
         <v>45479.79166666666</v>
       </c>
       <c r="J139" t="inlineStr">
@@ -18130,13 +18171,13 @@
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" s="6" t="n">
+      <c r="G140" s="8" t="n">
         <v>45487.79166666666</v>
       </c>
-      <c r="H140" s="6" t="n">
+      <c r="H140" s="8" t="n">
         <v>45487.79166666666</v>
       </c>
-      <c r="I140" s="6" t="n">
+      <c r="I140" s="8" t="n">
         <v>45487.79166666666</v>
       </c>
       <c r="J140" t="inlineStr">
@@ -18207,13 +18248,13 @@
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" s="6" t="n">
+      <c r="G141" s="8" t="n">
         <v>45496.79166666666</v>
       </c>
-      <c r="H141" s="6" t="n">
+      <c r="H141" s="8" t="n">
         <v>45496.79166666666</v>
       </c>
-      <c r="I141" s="6" t="n">
+      <c r="I141" s="8" t="n">
         <v>45496.79166666666</v>
       </c>
       <c r="J141" t="inlineStr">
@@ -18288,13 +18329,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G142" s="6" t="n">
+      <c r="G142" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H142" s="6" t="n">
+      <c r="H142" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="I142" s="6" t="n">
+      <c r="I142" s="8" t="n">
         <v>45333.79166666666</v>
       </c>
       <c r="J142" t="inlineStr">
@@ -18369,13 +18410,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G143" s="6" t="n">
+      <c r="G143" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H143" s="6" t="n">
+      <c r="H143" s="8" t="n">
         <v>45334.79166666666</v>
       </c>
-      <c r="I143" s="6" t="n">
+      <c r="I143" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J143" t="inlineStr">
@@ -18450,13 +18491,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G144" s="6" t="n">
+      <c r="G144" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H144" s="6" t="n">
+      <c r="H144" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="I144" s="6" t="n">
+      <c r="I144" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J144" t="inlineStr">
@@ -18531,13 +18572,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G145" s="6" t="n">
+      <c r="G145" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H145" s="6" t="n">
+      <c r="H145" s="8" t="n">
         <v>45327.79166666666</v>
       </c>
-      <c r="I145" s="6" t="n">
+      <c r="I145" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J145" t="inlineStr">
@@ -18612,13 +18653,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G146" s="6" t="n">
+      <c r="G146" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H146" s="6" t="n">
+      <c r="H146" s="8" t="n">
         <v>45321.79166666666</v>
       </c>
-      <c r="I146" s="6" t="n">
+      <c r="I146" s="8" t="n">
         <v>45323.79166666666</v>
       </c>
       <c r="J146" t="inlineStr">
@@ -18695,13 +18736,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G147" s="6" t="n">
+      <c r="G147" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H147" s="6" t="n">
+      <c r="H147" s="8" t="n">
         <v>45327.79166666666</v>
       </c>
-      <c r="I147" s="6" t="n">
+      <c r="I147" s="8" t="n">
         <v>45330.79166666666</v>
       </c>
       <c r="J147" t="inlineStr">
@@ -18772,13 +18813,13 @@
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" s="6" t="n">
+      <c r="G148" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H148" s="6" t="n">
+      <c r="H148" s="8" t="n">
         <v>45327.79166666666</v>
       </c>
-      <c r="I148" s="6" t="n">
+      <c r="I148" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J148" t="inlineStr">
@@ -18853,13 +18894,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G149" s="6" t="n">
+      <c r="G149" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H149" s="6" t="n">
+      <c r="H149" s="8" t="n">
         <v>45322.79166666666</v>
       </c>
-      <c r="I149" s="6" t="n">
+      <c r="I149" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J149" t="inlineStr">
@@ -18934,13 +18975,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G150" s="6" t="n">
+      <c r="G150" s="8" t="n">
         <v>45320.79166666666</v>
       </c>
-      <c r="H150" s="6" t="n">
+      <c r="H150" s="8" t="n">
         <v>45321.79166666666</v>
       </c>
-      <c r="I150" s="6" t="n">
+      <c r="I150" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J150" t="inlineStr">
@@ -19015,13 +19056,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G151" s="6" t="n">
+      <c r="G151" s="8" t="n">
         <v>45322.79166666666</v>
       </c>
-      <c r="H151" s="6" t="n">
+      <c r="H151" s="8" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="I151" s="6" t="n">
+      <c r="I151" s="8" t="n">
         <v>45330.79166666666</v>
       </c>
       <c r="J151" t="inlineStr">
@@ -19098,13 +19139,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G152" s="6" t="n">
+      <c r="G152" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H152" s="6" t="n">
+      <c r="H152" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="I152" s="6" t="n">
+      <c r="I152" s="8" t="n">
         <v>45347.79166666666</v>
       </c>
       <c r="J152" t="inlineStr">
@@ -19181,13 +19222,13 @@
           <t>Consulta</t>
         </is>
       </c>
-      <c r="G153" s="6" t="n">
+      <c r="G153" s="8" t="n">
         <v>45326.79166666666</v>
       </c>
-      <c r="H153" s="6" t="n">
+      <c r="H153" s="8" t="n">
         <v>45326.79166666666</v>
       </c>
-      <c r="I153" s="6" t="n">
+      <c r="I153" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J153" t="inlineStr">
@@ -19268,13 +19309,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G154" s="6" t="n">
+      <c r="G154" s="8" t="n">
         <v>45328.79166666666</v>
       </c>
-      <c r="H154" s="6" t="n">
+      <c r="H154" s="8" t="n">
         <v>45328.79166666666</v>
       </c>
-      <c r="I154" s="6" t="n">
+      <c r="I154" s="8" t="n">
         <v>45328.79166666666</v>
       </c>
       <c r="J154" t="inlineStr">
@@ -19349,13 +19390,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G155" s="6" t="n">
+      <c r="G155" s="8" t="n">
         <v>45328.79166666666</v>
       </c>
-      <c r="H155" s="6" t="n">
+      <c r="H155" s="8" t="n">
         <v>45328.79166666666</v>
       </c>
-      <c r="I155" s="6" t="n">
+      <c r="I155" s="8" t="n">
         <v>45328.79166666666</v>
       </c>
       <c r="J155" t="inlineStr">
@@ -19434,13 +19475,13 @@
           <t>Consulta</t>
         </is>
       </c>
-      <c r="G156" s="6" t="n">
+      <c r="G156" s="8" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="H156" s="6" t="n">
+      <c r="H156" s="8" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="I156" s="6" t="n">
+      <c r="I156" s="8" t="n">
         <v>45330.79166666666</v>
       </c>
       <c r="J156" t="inlineStr">
@@ -19511,13 +19552,13 @@
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" s="6" t="n">
+      <c r="G157" s="8" t="n">
         <v>45333.79166666666</v>
       </c>
-      <c r="H157" s="6" t="n">
+      <c r="H157" s="8" t="n">
         <v>45333.79166666666</v>
       </c>
-      <c r="I157" s="6" t="n">
+      <c r="I157" s="8" t="n">
         <v>45340.79166666666</v>
       </c>
       <c r="J157" t="inlineStr">
@@ -19592,13 +19633,13 @@
           <t>Consulta</t>
         </is>
       </c>
-      <c r="G158" s="6" t="n">
+      <c r="G158" s="8" t="n">
         <v>45336.79166666666</v>
       </c>
-      <c r="H158" s="6" t="n">
+      <c r="H158" s="8" t="n">
         <v>45336.79166666666</v>
       </c>
-      <c r="I158" s="6" t="n">
+      <c r="I158" s="8" t="n">
         <v>45336.79166666666</v>
       </c>
       <c r="J158" t="inlineStr">
@@ -19669,13 +19710,13 @@
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" s="6" t="n">
+      <c r="G159" s="8" t="n">
         <v>45347.79166666666</v>
       </c>
-      <c r="H159" s="6" t="n">
+      <c r="H159" s="8" t="n">
         <v>45348.79166666666</v>
       </c>
-      <c r="I159" s="6" t="n">
+      <c r="I159" s="8" t="n">
         <v>45348.79166666666</v>
       </c>
       <c r="J159" t="inlineStr">
@@ -19746,13 +19787,13 @@
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" s="6" t="n">
+      <c r="G160" s="8" t="n">
         <v>46051.25902777778</v>
       </c>
-      <c r="H160" s="6" t="n">
+      <c r="H160" s="8" t="n">
         <v>46051.25902777778</v>
       </c>
-      <c r="I160" s="6" t="n">
+      <c r="I160" s="8" t="n">
         <v>46057.79166666666</v>
       </c>
       <c r="J160" t="inlineStr">
@@ -19819,13 +19860,13 @@
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" s="6" t="n">
+      <c r="G161" s="8" t="n">
         <v>46059.29791666667</v>
       </c>
-      <c r="H161" s="6" t="n">
+      <c r="H161" s="8" t="n">
         <v>46059.29791666667</v>
       </c>
-      <c r="I161" s="6" t="n">
+      <c r="I161" s="8" t="n">
         <v>46062.79166666666</v>
       </c>
       <c r="J161" t="inlineStr">
@@ -19898,13 +19939,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G162" s="6" t="n">
+      <c r="G162" s="8" t="n">
         <v>45652.79166666666</v>
       </c>
-      <c r="H162" s="6" t="n">
+      <c r="H162" s="8" t="n">
         <v>45670.79166666666</v>
       </c>
-      <c r="I162" s="6" t="n">
+      <c r="I162" s="8" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J162" t="inlineStr">
@@ -19979,13 +20020,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G163" s="6" t="n">
+      <c r="G163" s="8" t="n">
         <v>45669.79166666666</v>
       </c>
-      <c r="H163" s="6" t="n">
+      <c r="H163" s="8" t="n">
         <v>45669.79166666666</v>
       </c>
-      <c r="I163" s="6" t="n">
+      <c r="I163" s="8" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J163" t="inlineStr">
@@ -20060,13 +20101,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G164" s="6" t="n">
+      <c r="G164" s="8" t="n">
         <v>45669.79166666666</v>
       </c>
-      <c r="H164" s="6" t="n">
+      <c r="H164" s="8" t="n">
         <v>45669.79166666666</v>
       </c>
-      <c r="I164" s="6" t="n">
+      <c r="I164" s="8" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J164" t="inlineStr">
@@ -20141,13 +20182,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G165" s="6" t="n">
+      <c r="G165" s="8" t="n">
         <v>45674.79166666666</v>
       </c>
-      <c r="H165" s="6" t="n">
+      <c r="H165" s="8" t="n">
         <v>45674.79166666666</v>
       </c>
-      <c r="I165" s="6" t="n">
+      <c r="I165" s="8" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J165" t="inlineStr">
@@ -20222,13 +20263,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G166" s="6" t="n">
+      <c r="G166" s="8" t="n">
         <v>45680.79166666666</v>
       </c>
-      <c r="H166" s="6" t="n">
+      <c r="H166" s="8" t="n">
         <v>45680.79166666666</v>
       </c>
-      <c r="I166" s="6" t="n">
+      <c r="I166" s="8" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J166" t="inlineStr">
@@ -20303,13 +20344,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G167" s="6" t="n">
+      <c r="G167" s="8" t="n">
         <v>45313.79166666666</v>
       </c>
-      <c r="H167" s="6" t="n">
+      <c r="H167" s="8" t="n">
         <v>45316.79166666666</v>
       </c>
-      <c r="I167" s="6" t="n">
+      <c r="I167" s="8" t="n">
         <v>45316.79166666666</v>
       </c>
       <c r="J167" t="inlineStr">
@@ -20386,13 +20427,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G168" s="6" t="n">
+      <c r="G168" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H168" s="6" t="n">
+      <c r="H168" s="8" t="n">
         <v>45316.79166666666</v>
       </c>
-      <c r="I168" s="6" t="n">
+      <c r="I168" s="8" t="n">
         <v>45319.79166666666</v>
       </c>
       <c r="J168" t="inlineStr">
@@ -20467,13 +20508,13 @@
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" s="6" t="n">
+      <c r="G169" s="8" t="n">
         <v>45986.79166666666</v>
       </c>
-      <c r="H169" s="6" t="n">
+      <c r="H169" s="8" t="n">
         <v>45988.79166666666</v>
       </c>
-      <c r="I169" s="6" t="n">
+      <c r="I169" s="8" t="n">
         <v>46049.79166666666</v>
       </c>
       <c r="J169" t="inlineStr">
@@ -20540,13 +20581,13 @@
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" s="6" t="n">
+      <c r="G170" s="8" t="n">
         <v>46048.33472222222</v>
       </c>
-      <c r="H170" s="6" t="n">
+      <c r="H170" s="8" t="n">
         <v>46048.41805555556</v>
       </c>
-      <c r="I170" s="6" t="n">
+      <c r="I170" s="8" t="n">
         <v>46051.29166666666</v>
       </c>
       <c r="J170" t="inlineStr"/>
@@ -20615,13 +20656,13 @@
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" s="6" t="n">
+      <c r="G171" s="8" t="n">
         <v>45657.79166666666</v>
       </c>
-      <c r="H171" s="6" t="n">
+      <c r="H171" s="8" t="n">
         <v>45659.79166666666</v>
       </c>
-      <c r="I171" s="6" t="n">
+      <c r="I171" s="8" t="n">
         <v>45662.79166666666</v>
       </c>
       <c r="J171" t="inlineStr">
@@ -20692,13 +20733,13 @@
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" s="6" t="n">
+      <c r="G172" s="8" t="n">
         <v>45659.79166666666</v>
       </c>
-      <c r="H172" s="6" t="n">
+      <c r="H172" s="8" t="n">
         <v>45659.79166666666</v>
       </c>
-      <c r="I172" s="6" t="n">
+      <c r="I172" s="8" t="n">
         <v>45683.79166666666</v>
       </c>
       <c r="J172" t="inlineStr">
@@ -20771,13 +20812,13 @@
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" s="6" t="n">
+      <c r="G173" s="8" t="n">
         <v>45662.79166666666</v>
       </c>
-      <c r="H173" s="6" t="n">
+      <c r="H173" s="8" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="I173" s="6" t="n">
+      <c r="I173" s="8" t="n">
         <v>45665.79166666666</v>
       </c>
       <c r="J173" t="inlineStr">
@@ -20848,13 +20889,13 @@
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" s="6" t="n">
+      <c r="G174" s="8" t="n">
         <v>45659.79166666666</v>
       </c>
-      <c r="H174" s="6" t="n">
+      <c r="H174" s="8" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="I174" s="6" t="n">
+      <c r="I174" s="8" t="n">
         <v>45683.79166666666</v>
       </c>
       <c r="J174" t="inlineStr">
@@ -20921,13 +20962,13 @@
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" s="6" t="n">
+      <c r="G175" s="8" t="n">
         <v>45680.79166666666</v>
       </c>
-      <c r="H175" s="6" t="n">
+      <c r="H175" s="8" t="n">
         <v>45680.79166666666</v>
       </c>
-      <c r="I175" s="6" t="n">
+      <c r="I175" s="8" t="n">
         <v>45694.79166666666</v>
       </c>
       <c r="J175" t="inlineStr">
@@ -20998,13 +21039,13 @@
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" s="6" t="n">
+      <c r="G176" s="8" t="n">
         <v>45682.79166666666</v>
       </c>
-      <c r="H176" s="6" t="n">
+      <c r="H176" s="8" t="n">
         <v>45683.79166666666</v>
       </c>
-      <c r="I176" s="6" t="n">
+      <c r="I176" s="8" t="n">
         <v>45694.79166666666</v>
       </c>
       <c r="J176" t="inlineStr">
@@ -21077,13 +21118,13 @@
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" s="6" t="n">
+      <c r="G177" s="8" t="n">
         <v>45687.79166666666</v>
       </c>
-      <c r="H177" s="6" t="n">
+      <c r="H177" s="8" t="n">
         <v>45687.79166666666</v>
       </c>
-      <c r="I177" s="6" t="n">
+      <c r="I177" s="8" t="n">
         <v>45688.79166666666</v>
       </c>
       <c r="J177" t="inlineStr">
@@ -21156,13 +21197,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G178" s="6" t="n">
+      <c r="G178" s="8" t="n">
         <v>45963.79166666666</v>
       </c>
-      <c r="H178" s="6" t="n">
+      <c r="H178" s="8" t="n">
         <v>45987.43333333333</v>
       </c>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" s="8" t="n"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21235,13 +21276,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G179" s="6" t="n">
+      <c r="G179" s="8" t="n">
         <v>45944.79166666666</v>
       </c>
-      <c r="H179" s="6" t="n">
+      <c r="H179" s="8" t="n">
         <v>45951.79166666666</v>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" s="8" t="n"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21310,13 +21351,13 @@
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" s="6" t="n">
+      <c r="G180" s="8" t="n">
         <v>45963.79166666666</v>
       </c>
-      <c r="H180" s="6" t="n">
+      <c r="H180" s="8" t="n">
         <v>45979.79166666666</v>
       </c>
-      <c r="I180" s="6" t="n">
+      <c r="I180" s="8" t="n">
         <v>46008.79166666666</v>
       </c>
       <c r="J180" t="inlineStr">
@@ -21387,13 +21428,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G181" s="6" t="n">
+      <c r="G181" s="8" t="n">
         <v>45908.79166666666</v>
       </c>
-      <c r="H181" s="6" t="n">
+      <c r="H181" s="8" t="n">
         <v>45930.79166666666</v>
       </c>
-      <c r="I181" t="inlineStr"/>
+      <c r="I181" s="8" t="n"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21462,13 +21503,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G182" s="6" t="n">
+      <c r="G182" s="8" t="n">
         <v>45936.79166666666</v>
       </c>
-      <c r="H182" s="6" t="n">
+      <c r="H182" s="8" t="n">
         <v>45950.79166666666</v>
       </c>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" s="8" t="n"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21533,13 +21574,13 @@
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" s="6" t="n">
+      <c r="G183" s="8" t="n">
         <v>45995.79166666666</v>
       </c>
-      <c r="H183" s="6" t="n">
+      <c r="H183" s="8" t="n">
         <v>46006.29166666666</v>
       </c>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" s="8" t="n"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21608,13 +21649,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G184" s="6" t="n">
+      <c r="G184" s="8" t="n">
         <v>45970.79166666666</v>
       </c>
-      <c r="H184" s="6" t="n">
+      <c r="H184" s="8" t="n">
         <v>45974.51111111111</v>
       </c>
-      <c r="I184" t="inlineStr"/>
+      <c r="I184" s="8" t="n"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21683,13 +21724,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G185" s="6" t="n">
+      <c r="G185" s="8" t="n">
         <v>45981.79166666666</v>
       </c>
-      <c r="H185" s="6" t="n">
+      <c r="H185" s="8" t="n">
         <v>46006.43541666667</v>
       </c>
-      <c r="I185" t="inlineStr"/>
+      <c r="I185" s="8" t="n"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21754,13 +21795,13 @@
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" s="6" t="n">
+      <c r="G186" s="8" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="H186" s="6" t="n">
+      <c r="H186" s="8" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="I186" s="6" t="n">
+      <c r="I186" s="8" t="n">
         <v>45652.79166666666</v>
       </c>
       <c r="J186" t="inlineStr">
@@ -21833,13 +21874,13 @@
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" s="6" t="n">
+      <c r="G187" s="8" t="n">
         <v>45642.79166666666</v>
       </c>
-      <c r="H187" s="6" t="n">
+      <c r="H187" s="8" t="n">
         <v>45652.79166666666</v>
       </c>
-      <c r="I187" s="6" t="n">
+      <c r="I187" s="8" t="n">
         <v>45651.79166666666</v>
       </c>
       <c r="J187" t="inlineStr">
@@ -21916,13 +21957,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G188" s="6" t="n">
+      <c r="G188" s="8" t="n">
         <v>45652.79166666666</v>
       </c>
-      <c r="H188" s="6" t="n">
+      <c r="H188" s="8" t="n">
         <v>45652.79166666666</v>
       </c>
-      <c r="I188" s="6" t="n">
+      <c r="I188" s="8" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J188" t="inlineStr">
@@ -21997,13 +22038,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G189" s="6" t="n">
+      <c r="G189" s="8" t="n">
         <v>45820.79166666666</v>
       </c>
-      <c r="H189" s="6" t="n">
+      <c r="H189" s="8" t="n">
         <v>45823.79166666666</v>
       </c>
-      <c r="I189" t="inlineStr"/>
+      <c r="I189" s="8" t="n"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -22076,13 +22117,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G190" s="6" t="n">
+      <c r="G190" s="8" t="n">
         <v>45481.79166666666</v>
       </c>
-      <c r="H190" s="6" t="n">
+      <c r="H190" s="8" t="n">
         <v>45481.79166666666</v>
       </c>
-      <c r="I190" s="6" t="n">
+      <c r="I190" s="8" t="n">
         <v>45481.79166666666</v>
       </c>
       <c r="J190" t="inlineStr">
@@ -22153,13 +22194,13 @@
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" s="6" t="n">
+      <c r="G191" s="8" t="n">
         <v>45490.79166666666</v>
       </c>
-      <c r="H191" s="6" t="n">
+      <c r="H191" s="8" t="n">
         <v>45490.79166666666</v>
       </c>
-      <c r="I191" s="6" t="n">
+      <c r="I191" s="8" t="n">
         <v>45508.79166666666</v>
       </c>
       <c r="J191" t="inlineStr">
@@ -22232,13 +22273,13 @@
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" s="6" t="n">
+      <c r="G192" s="8" t="n">
         <v>45505.79166666666</v>
       </c>
-      <c r="H192" s="6" t="n">
+      <c r="H192" s="8" t="n">
         <v>45505.79166666666</v>
       </c>
-      <c r="I192" s="6" t="n">
+      <c r="I192" s="8" t="n">
         <v>45525.79166666666</v>
       </c>
       <c r="J192" t="inlineStr">
@@ -22311,13 +22352,13 @@
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" s="6" t="n">
+      <c r="G193" s="8" t="n">
         <v>45526.79166666666</v>
       </c>
-      <c r="H193" s="6" t="n">
+      <c r="H193" s="8" t="n">
         <v>45529.79166666666</v>
       </c>
-      <c r="I193" s="6" t="n">
+      <c r="I193" s="8" t="n">
         <v>45529.79166666666</v>
       </c>
       <c r="J193" t="inlineStr">
@@ -22388,13 +22429,13 @@
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" s="6" t="n">
+      <c r="G194" s="8" t="n">
         <v>45528.79166666666</v>
       </c>
-      <c r="H194" s="6" t="n">
+      <c r="H194" s="8" t="n">
         <v>45528.79166666666</v>
       </c>
-      <c r="I194" s="6" t="n">
+      <c r="I194" s="8" t="n">
         <v>45528.79166666666</v>
       </c>
       <c r="J194" t="inlineStr">
@@ -22465,13 +22506,13 @@
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
-      <c r="G195" s="6" t="n">
+      <c r="G195" s="8" t="n">
         <v>45388.79166666666</v>
       </c>
-      <c r="H195" s="6" t="n">
+      <c r="H195" s="8" t="n">
         <v>45388.79166666666</v>
       </c>
-      <c r="I195" s="6" t="n">
+      <c r="I195" s="8" t="n">
         <v>45397.79166666666</v>
       </c>
       <c r="J195" t="inlineStr">
@@ -22544,13 +22585,13 @@
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
-      <c r="G196" s="6" t="n">
+      <c r="G196" s="8" t="n">
         <v>45392.79166666666</v>
       </c>
-      <c r="H196" s="6" t="n">
+      <c r="H196" s="8" t="n">
         <v>45399.79166666666</v>
       </c>
-      <c r="I196" s="6" t="n">
+      <c r="I196" s="8" t="n">
         <v>45404.79166666666</v>
       </c>
       <c r="J196" t="inlineStr">
@@ -22623,13 +22664,13 @@
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
-      <c r="G197" s="6" t="n">
+      <c r="G197" s="8" t="n">
         <v>45397.79166666666</v>
       </c>
-      <c r="H197" s="6" t="n">
+      <c r="H197" s="8" t="n">
         <v>45397.79166666666</v>
       </c>
-      <c r="I197" s="6" t="n">
+      <c r="I197" s="8" t="n">
         <v>45404.79166666666</v>
       </c>
       <c r="J197" t="inlineStr">
@@ -22702,13 +22743,13 @@
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" s="6" t="n">
+      <c r="G198" s="8" t="n">
         <v>45407.79166666666</v>
       </c>
-      <c r="H198" s="6" t="n">
+      <c r="H198" s="8" t="n">
         <v>45407.79166666666</v>
       </c>
-      <c r="I198" s="6" t="n">
+      <c r="I198" s="8" t="n">
         <v>45413.79166666666</v>
       </c>
       <c r="J198" t="inlineStr">
@@ -22779,13 +22820,13 @@
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" s="6" t="n">
+      <c r="G199" s="8" t="n">
         <v>45407.79166666666</v>
       </c>
-      <c r="H199" s="6" t="n">
+      <c r="H199" s="8" t="n">
         <v>45413.79166666666</v>
       </c>
-      <c r="I199" s="6" t="n">
+      <c r="I199" s="8" t="n">
         <v>45413.79166666666</v>
       </c>
       <c r="J199" t="inlineStr">
@@ -22858,13 +22899,13 @@
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
-      <c r="G200" s="6" t="n">
+      <c r="G200" s="8" t="n">
         <v>45693.79166666666</v>
       </c>
-      <c r="H200" s="6" t="n">
+      <c r="H200" s="8" t="n">
         <v>45704.79166666666</v>
       </c>
-      <c r="I200" s="6" t="n">
+      <c r="I200" s="8" t="n">
         <v>45755.44861111111</v>
       </c>
       <c r="J200" t="inlineStr">
@@ -22935,13 +22976,13 @@
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" s="6" t="n">
+      <c r="G201" s="8" t="n">
         <v>45711.79166666666</v>
       </c>
-      <c r="H201" s="6" t="n">
+      <c r="H201" s="8" t="n">
         <v>45712.79166666666</v>
       </c>
-      <c r="I201" s="6" t="n">
+      <c r="I201" s="8" t="n">
         <v>45755.44861111111</v>
       </c>
       <c r="J201" t="inlineStr">
@@ -23016,13 +23057,13 @@
           <t>[Ver. 2.22]</t>
         </is>
       </c>
-      <c r="G202" s="6" t="n">
+      <c r="G202" s="8" t="n">
         <v>45768.79166666666</v>
       </c>
-      <c r="H202" s="6" t="n">
+      <c r="H202" s="8" t="n">
         <v>45770.79166666666</v>
       </c>
-      <c r="I202" s="6" t="n">
+      <c r="I202" s="8" t="n">
         <v>45771.79166666666</v>
       </c>
       <c r="J202" t="inlineStr">
@@ -23093,13 +23134,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G203" s="6" t="n">
+      <c r="G203" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H203" s="6" t="n">
+      <c r="H203" s="8" t="n">
         <v>45341.79166666666</v>
       </c>
-      <c r="I203" s="6" t="n">
+      <c r="I203" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J203" t="inlineStr">
@@ -23174,13 +23215,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G204" s="6" t="n">
+      <c r="G204" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H204" s="6" t="n">
+      <c r="H204" s="8" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="I204" s="6" t="n">
+      <c r="I204" s="8" t="n">
         <v>45372.79166666666</v>
       </c>
       <c r="J204" t="inlineStr">
@@ -23255,13 +23296,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G205" s="6" t="n">
+      <c r="G205" s="8" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="H205" s="6" t="n">
+      <c r="H205" s="8" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="I205" s="6" t="n">
+      <c r="I205" s="8" t="n">
         <v>45375.79166666666</v>
       </c>
       <c r="J205" t="inlineStr">
@@ -23336,13 +23377,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G206" s="6" t="n">
+      <c r="G206" s="8" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="H206" s="6" t="n">
+      <c r="H206" s="8" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="I206" s="6" t="n">
+      <c r="I206" s="8" t="n">
         <v>45375.79166666666</v>
       </c>
       <c r="J206" t="inlineStr">
@@ -23417,13 +23458,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G207" s="6" t="n">
+      <c r="G207" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="H207" s="6" t="n">
+      <c r="H207" s="8" t="n">
         <v>45361.79166666666</v>
       </c>
-      <c r="I207" s="6" t="n">
+      <c r="I207" s="8" t="n">
         <v>45372.79166666666</v>
       </c>
       <c r="J207" t="inlineStr">
@@ -23498,13 +23539,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G208" s="6" t="n">
+      <c r="G208" s="8" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="H208" s="6" t="n">
+      <c r="H208" s="8" t="n">
         <v>45375.79166666666</v>
       </c>
-      <c r="I208" s="6" t="n">
+      <c r="I208" s="8" t="n">
         <v>45372.79166666666</v>
       </c>
       <c r="J208" t="inlineStr">
@@ -23551,6 +23592,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S208"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,8 +77,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +99,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00106EBE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF106EBE"/>
       </patternFill>
     </fill>
   </fills>
@@ -124,7 +134,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -146,6 +156,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7241,97 +7257,97 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Work Item Type</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Iteration Path</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Estados</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Finish Date</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Finish Date Chinalco</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Aplicación</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Ticket Chinalco</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Ticket SyC</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Assigned To</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Tipo Caso</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Tipo Evento</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Tipo Estabilización</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -20,11 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,16 +73,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -94,11 +88,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF106EBE"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00106EBE"/>
       </patternFill>
     </fill>
     <fill>
@@ -134,7 +123,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -151,17 +140,10 @@
     <xf numFmtId="22" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7233,121 +7215,121 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S208"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.140625" defaultRowHeight="15"/>
   <cols>
     <col width="4.14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="77" customWidth="1" min="3" max="3"/>
     <col width="40.57" customWidth="1" min="4" max="4"/>
     <col width="19.57" customWidth="1" min="5" max="5"/>
     <col width="15.43" customWidth="1" min="6" max="6"/>
-    <col width="17.71" customWidth="1" min="7" max="7"/>
+    <col width="17.71" bestFit="1" customWidth="1" min="7" max="8"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15.71" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="9.289999999999999" customWidth="1" min="11" max="11"/>
-    <col width="17.71" customWidth="1" min="12" max="12"/>
-    <col width="47.71" customWidth="1" min="13" max="13"/>
-    <col width="255.71" customWidth="1" min="14" max="14"/>
+    <col width="15.71" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="13" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="9.289999999999999" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="17.71" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="47.71" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="255.71" bestFit="1" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="35.43" customWidth="1" min="16" max="16"/>
+    <col width="35.43" bestFit="1" customWidth="1" min="16" max="16"/>
     <col width="25" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="24.71" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Work Item Type</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Iteration Path</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Estados</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Finish Date</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Finish Date Chinalco</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Aplicación</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Ticket Chinalco</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Ticket SyC</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Assigned To</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Tipo Caso</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Tipo Evento</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Tipo Estabilización</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
@@ -7378,13 +7360,13 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="7" t="n">
         <v>45900.79166666666</v>
       </c>
-      <c r="H2" s="8" t="n">
+      <c r="H2" s="7" t="n">
         <v>45914.79166666666</v>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="I2" s="7" t="n">
         <v>46019.79166666666</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -7455,13 +7437,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="7" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="7" t="n">
         <v>45937.57916666667</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="7" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -7532,9 +7514,9 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" s="8" t="n"/>
-      <c r="H4" s="8" t="n"/>
-      <c r="I4" s="8" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>WAPSA web</t>
@@ -7599,9 +7581,9 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="8" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>WAPSA web</t>
@@ -7666,9 +7648,9 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>WAPSA web</t>
@@ -7733,11 +7715,11 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="7" t="n">
         <v>45391.79166666666</v>
       </c>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -7806,13 +7788,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
         <v>45810.79166666666</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="7" t="n">
         <v>45873.79166666666</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="7" t="n">
         <v>45937.57847222222</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -7887,13 +7869,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="G9" s="7" t="n">
         <v>45863.71805555555</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="7" t="n">
         <v>45863.71805555555</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="7" t="n">
         <v>45901.26458333333</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -7968,13 +7950,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="7" t="n">
         <v>45487.79166666666</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="7" t="n">
         <v>45487.79166666666</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I10" s="7" t="n">
         <v>45530.79166666666</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -8051,13 +8033,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="7" t="n">
         <v>45544.79166666666</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="7" t="n">
         <v>45544.79166666666</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="7" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -8134,13 +8116,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="7" t="n">
         <v>45933.35277777778</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="7" t="n">
         <v>45937.575</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="I12" s="7" t="n">
         <v>45959.20069444444</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -8215,13 +8197,13 @@
           <t>[Ver 4.1]</t>
         </is>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="7" t="n">
         <v>45937.58055555556</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="7" t="n">
         <v>45937.58055555556</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="7" t="n">
         <v>45959.20069444444</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -8296,13 +8278,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="7" t="n">
         <v>45414.79166666666</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="7" t="n">
         <v>45431.79166666666</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I14" s="7" t="n">
         <v>45426.79166666666</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -8377,13 +8359,13 @@
           <t>[2.16.1]</t>
         </is>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="7" t="n">
         <v>45414.79166666666</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="7" t="n">
         <v>45440.79166666666</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="7" t="n">
         <v>45438.79166666666</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -8458,13 +8440,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="7" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="H16" s="7" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="I16" s="7" t="n">
         <v>45372.79166666666</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -8542,11 +8524,11 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="7" t="n">
         <v>46073.42986111111</v>
       </c>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
@@ -8615,13 +8597,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="7" t="n">
         <v>45704.79166666666</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="7" t="n">
         <v>45715.79166666666</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="7" t="n">
         <v>45728.79166666666</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -8696,13 +8678,13 @@
           <t>[Ver. 2.22]</t>
         </is>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="7" t="n">
         <v>45771.79166666666</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="7" t="n">
         <v>45774.79166666666</v>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="7" t="n">
         <v>45810.79166666666</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -8777,13 +8759,13 @@
           <t>[Ver. 2.23]</t>
         </is>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="7" t="n">
         <v>45819.36388888889</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="7" t="n">
         <v>45819.36388888889</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="7" t="n">
         <v>45832.42916666667</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -8858,13 +8840,13 @@
           <t>[Ver 4.0]</t>
         </is>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="7" t="n">
         <v>45819.36388888889</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="7" t="n">
         <v>45819.36388888889</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="7" t="n">
         <v>45827.79166666666</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -8939,13 +8921,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="7" t="n">
         <v>45327.79166666666</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="7" t="n">
         <v>45354.79166666666</v>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I22" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -9036,13 +9018,13 @@
           <t>[Ver.2.4]</t>
         </is>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G23" s="7" t="n">
         <v>45337.79166666666</v>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H23" s="7" t="n">
         <v>45342.79166666666</v>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" s="7" t="n">
         <v>45343.79166666666</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -9113,13 +9095,13 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" s="8" t="n">
+      <c r="G24" s="7" t="n">
         <v>46019.79166666666</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="7" t="n">
         <v>46022.65347222222</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I24" s="7" t="n">
         <v>46045.65347222222</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -9192,13 +9174,13 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" s="8" t="n">
+      <c r="G25" s="7" t="n">
         <v>46019.79166666666</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H25" s="7" t="n">
         <v>46021.79166666666</v>
       </c>
-      <c r="I25" s="8" t="n">
+      <c r="I25" s="7" t="n">
         <v>46045.65555555555</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -9275,13 +9257,13 @@
           <t>v2.25.3</t>
         </is>
       </c>
-      <c r="G26" s="8" t="n">
+      <c r="G26" s="7" t="n">
         <v>45988.79166666666</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="7" t="n">
         <v>45992.59097222222</v>
       </c>
-      <c r="I26" s="8" t="n"/>
+      <c r="I26" s="7" t="n"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -9342,13 +9324,13 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" s="8" t="n">
+      <c r="G27" s="7" t="n">
         <v>45992.42916666667</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="7" t="n">
         <v>45991.79166666666</v>
       </c>
-      <c r="I27" s="8" t="n">
+      <c r="I27" s="7" t="n">
         <v>45995.79166666666</v>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -9419,13 +9401,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="7" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="7" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="I28" s="8" t="n">
+      <c r="I28" s="7" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -9502,13 +9484,13 @@
           <t>[Ver. 2.20]</t>
         </is>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G29" s="7" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="7" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I29" s="7" t="n">
         <v>45665.79166666666</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -9583,13 +9565,13 @@
           <t>[Ver. 1.1]</t>
         </is>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G30" s="7" t="n">
         <v>45490.79166666666</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="H30" s="7" t="n">
         <v>45490.79166666666</v>
       </c>
-      <c r="I30" s="8" t="n">
+      <c r="I30" s="7" t="n">
         <v>45511.79166666666</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -9660,13 +9642,13 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" s="8" t="n">
+      <c r="G31" s="7" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="7" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="I31" s="8" t="n">
+      <c r="I31" s="7" t="n">
         <v>45550.79166666666</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -9739,13 +9721,13 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" s="8" t="n">
+      <c r="G32" s="7" t="n">
         <v>45427.79166666666</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="7" t="n">
         <v>45439.79166666666</v>
       </c>
-      <c r="I32" s="8" t="n">
+      <c r="I32" s="7" t="n">
         <v>45440.79166666666</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -9818,13 +9800,13 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="7" t="n">
         <v>45348.79166666666</v>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I33" s="7" t="n">
         <v>45354.79166666666</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -9895,13 +9877,13 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="7" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="7" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="I34" s="8" t="n">
+      <c r="I34" s="7" t="n">
         <v>45369.79166666666</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -9974,13 +9956,13 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="7" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="7" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="I35" s="7" t="n">
         <v>45383.79166666666</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -10053,13 +10035,13 @@
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="7" t="n">
         <v>45396.79166666666</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="7" t="n">
         <v>45415.79166666666</v>
       </c>
-      <c r="I36" s="8" t="n">
+      <c r="I36" s="7" t="n">
         <v>45415.79166666666</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -10136,13 +10118,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="G37" s="7" t="n">
         <v>45911.30347222222</v>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="H37" s="7" t="n">
         <v>45937.57916666667</v>
       </c>
-      <c r="I37" s="8" t="n">
+      <c r="I37" s="7" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -10213,9 +10195,9 @@
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10284,13 +10266,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="7" t="n">
         <v>45930.79166666666</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="7" t="n">
         <v>45937.45138888889</v>
       </c>
-      <c r="I39" s="8" t="n">
+      <c r="I39" s="7" t="n">
         <v>45937.57986111111</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -10361,9 +10343,9 @@
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10432,11 +10414,11 @@
           <t>[Ver. 2.27]; [Ver. 2.28]</t>
         </is>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G41" s="7" t="n">
         <v>45991.79166666666</v>
       </c>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10505,13 +10487,13 @@
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="7" t="n">
         <v>45931.79166666666</v>
       </c>
-      <c r="H42" s="8" t="n">
+      <c r="H42" s="7" t="n">
         <v>46008.79166666666</v>
       </c>
-      <c r="I42" s="8" t="n">
+      <c r="I42" s="7" t="n">
         <v>46008.79166666666</v>
       </c>
       <c r="J42" t="inlineStr">
@@ -10586,13 +10568,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="7" t="n">
         <v>45854.72638888889</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="7" t="n">
         <v>45854.72638888889</v>
       </c>
-      <c r="I43" s="8" t="n"/>
+      <c r="I43" s="7" t="n"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10665,13 +10647,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G44" s="8" t="n">
+      <c r="G44" s="7" t="n">
         <v>45417.79166666666</v>
       </c>
-      <c r="H44" s="8" t="n">
+      <c r="H44" s="7" t="n">
         <v>45424.79166666666</v>
       </c>
-      <c r="I44" s="8" t="n">
+      <c r="I44" s="7" t="n">
         <v>45421.79166666666</v>
       </c>
       <c r="J44" t="inlineStr">
@@ -10746,13 +10728,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G45" s="8" t="n">
+      <c r="G45" s="7" t="n">
         <v>45426.79166666666</v>
       </c>
-      <c r="H45" s="8" t="n">
+      <c r="H45" s="7" t="n">
         <v>45476.79166666666</v>
       </c>
-      <c r="I45" s="8" t="n">
+      <c r="I45" s="7" t="n">
         <v>45538.79166666666</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -10827,13 +10809,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="G46" s="7" t="n">
         <v>45445.79166666666</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="7" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="I46" s="8" t="n">
+      <c r="I46" s="7" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -10908,13 +10890,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G47" s="8" t="n">
+      <c r="G47" s="7" t="n">
         <v>45382.79166666666</v>
       </c>
-      <c r="H47" s="8" t="n">
+      <c r="H47" s="7" t="n">
         <v>45388.79166666666</v>
       </c>
-      <c r="I47" s="8" t="n">
+      <c r="I47" s="7" t="n">
         <v>45418.79166666666</v>
       </c>
       <c r="J47" t="inlineStr">
@@ -10985,13 +10967,13 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" s="8" t="n">
+      <c r="G48" s="7" t="n">
         <v>45418.79166666666</v>
       </c>
-      <c r="H48" s="8" t="n">
+      <c r="H48" s="7" t="n">
         <v>45421.79166666666</v>
       </c>
-      <c r="I48" s="8" t="n">
+      <c r="I48" s="7" t="n">
         <v>45421.79166666666</v>
       </c>
       <c r="J48" t="inlineStr">
@@ -11062,13 +11044,13 @@
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" s="8" t="n">
+      <c r="G49" s="7" t="n">
         <v>45418.79166666666</v>
       </c>
-      <c r="H49" s="8" t="n">
+      <c r="H49" s="7" t="n">
         <v>45421.79166666666</v>
       </c>
-      <c r="I49" s="8" t="n">
+      <c r="I49" s="7" t="n">
         <v>45421.79166666666</v>
       </c>
       <c r="J49" t="inlineStr">
@@ -11143,11 +11125,11 @@
           <t>[Ver. 1.3]</t>
         </is>
       </c>
-      <c r="G50" s="8" t="n">
+      <c r="G50" s="7" t="n">
         <v>45446.79166666666</v>
       </c>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Wapsa ES</t>
@@ -11220,13 +11202,13 @@
           <t>[Ver. 1.3]</t>
         </is>
       </c>
-      <c r="G51" s="8" t="n">
+      <c r="G51" s="7" t="n">
         <v>45420.79166666666</v>
       </c>
-      <c r="H51" s="8" t="n">
+      <c r="H51" s="7" t="n">
         <v>45424.79166666666</v>
       </c>
-      <c r="I51" s="8" t="n">
+      <c r="I51" s="7" t="n">
         <v>45511.79166666666</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -11301,13 +11283,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G52" s="8" t="n">
+      <c r="G52" s="7" t="n">
         <v>45439.79166666666</v>
       </c>
-      <c r="H52" s="8" t="n">
+      <c r="H52" s="7" t="n">
         <v>45482.79166666666</v>
       </c>
-      <c r="I52" s="8" t="n">
+      <c r="I52" s="7" t="n">
         <v>45489.79166666666</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -11382,13 +11364,13 @@
           <t>[Ver. 1.1]</t>
         </is>
       </c>
-      <c r="G53" s="8" t="n">
+      <c r="G53" s="7" t="n">
         <v>45420.79166666666</v>
       </c>
-      <c r="H53" s="8" t="n">
+      <c r="H53" s="7" t="n">
         <v>45421.79166666666</v>
       </c>
-      <c r="I53" s="8" t="n">
+      <c r="I53" s="7" t="n">
         <v>45511.79166666666</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -11463,13 +11445,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G54" s="8" t="n">
+      <c r="G54" s="7" t="n">
         <v>45900.79166666666</v>
       </c>
-      <c r="H54" s="8" t="n">
+      <c r="H54" s="7" t="n">
         <v>45901.79166666666</v>
       </c>
-      <c r="I54" s="8" t="n">
+      <c r="I54" s="7" t="n">
         <v>45937.57847222222</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -11544,13 +11526,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G55" s="8" t="n">
+      <c r="G55" s="7" t="n">
         <v>45874.79166666666</v>
       </c>
-      <c r="H55" s="8" t="n">
+      <c r="H55" s="7" t="n">
         <v>45900.79166666666</v>
       </c>
-      <c r="I55" s="8" t="n">
+      <c r="I55" s="7" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -11625,13 +11607,13 @@
           <t>[Ver 4.1]</t>
         </is>
       </c>
-      <c r="G56" s="8" t="n">
+      <c r="G56" s="7" t="n">
         <v>45739.79166666666</v>
       </c>
-      <c r="H56" s="8" t="n">
+      <c r="H56" s="7" t="n">
         <v>45823.79166666666</v>
       </c>
-      <c r="I56" s="8" t="n">
+      <c r="I56" s="7" t="n">
         <v>45937.60625</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -11706,13 +11688,13 @@
           <t>[Ver. 2.22]</t>
         </is>
       </c>
-      <c r="G57" s="8" t="n">
+      <c r="G57" s="7" t="n">
         <v>45724.79166666666</v>
       </c>
-      <c r="H57" s="8" t="n">
+      <c r="H57" s="7" t="n">
         <v>45725.79166666666</v>
       </c>
-      <c r="I57" s="8" t="n">
+      <c r="I57" s="7" t="n">
         <v>45810.79166666666</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -11783,13 +11765,13 @@
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" s="8" t="n">
+      <c r="G58" s="7" t="n">
         <v>46022.79166666666</v>
       </c>
-      <c r="H58" s="8" t="n">
+      <c r="H58" s="7" t="n">
         <v>46052.79166666666</v>
       </c>
-      <c r="I58" s="8" t="n">
+      <c r="I58" s="7" t="n">
         <v>46052.79166666666</v>
       </c>
       <c r="J58" t="inlineStr">
@@ -11860,13 +11842,13 @@
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" s="8" t="n">
+      <c r="G59" s="7" t="n">
         <v>45987.11875</v>
       </c>
-      <c r="H59" s="8" t="n">
+      <c r="H59" s="7" t="n">
         <v>45996.11875</v>
       </c>
-      <c r="I59" s="8" t="n">
+      <c r="I59" s="7" t="n">
         <v>45996.11875</v>
       </c>
       <c r="J59" t="inlineStr">
@@ -11941,13 +11923,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G60" s="8" t="n">
+      <c r="G60" s="7" t="n">
         <v>45762.79166666666</v>
       </c>
-      <c r="H60" s="8" t="n">
+      <c r="H60" s="7" t="n">
         <v>45823.79166666666</v>
       </c>
-      <c r="I60" s="8" t="n"/>
+      <c r="I60" s="7" t="n"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>WAPSA web</t>
@@ -12020,13 +12002,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G61" s="8" t="n">
+      <c r="G61" s="7" t="n">
         <v>45739.79166666666</v>
       </c>
-      <c r="H61" s="8" t="n">
+      <c r="H61" s="7" t="n">
         <v>45822.79166666666</v>
       </c>
-      <c r="I61" s="8" t="n"/>
+      <c r="I61" s="7" t="n"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -12099,13 +12081,13 @@
           <t>[Ver. 2.22]</t>
         </is>
       </c>
-      <c r="G62" s="8" t="n">
+      <c r="G62" s="7" t="n">
         <v>45713.79166666666</v>
       </c>
-      <c r="H62" s="8" t="n">
+      <c r="H62" s="7" t="n">
         <v>45726.79166666666</v>
       </c>
-      <c r="I62" s="8" t="n">
+      <c r="I62" s="7" t="n">
         <v>45810.79166666666</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -12176,13 +12158,13 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" s="8" t="n">
+      <c r="G63" s="7" t="n">
         <v>45864.14652777778</v>
       </c>
-      <c r="H63" s="8" t="n">
+      <c r="H63" s="7" t="n">
         <v>45873.79166666666</v>
       </c>
-      <c r="I63" s="8" t="n">
+      <c r="I63" s="7" t="n">
         <v>45873.79166666666</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -12249,13 +12231,13 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" s="8" t="n">
+      <c r="G64" s="7" t="n">
         <v>45886.79166666666</v>
       </c>
-      <c r="H64" s="8" t="n">
+      <c r="H64" s="7" t="n">
         <v>45931.79166666666</v>
       </c>
-      <c r="I64" s="8" t="n">
+      <c r="I64" s="7" t="n">
         <v>45930.79166666666</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -12322,13 +12304,13 @@
           <t>[Ver. 2.24.1]</t>
         </is>
       </c>
-      <c r="G65" s="8" t="n">
+      <c r="G65" s="7" t="n">
         <v>45926.29791666667</v>
       </c>
-      <c r="H65" s="8" t="n">
+      <c r="H65" s="7" t="n">
         <v>45927.79166666666</v>
       </c>
-      <c r="I65" s="8" t="n">
+      <c r="I65" s="7" t="n">
         <v>45959.2</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -12403,13 +12385,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G66" s="8" t="n">
+      <c r="G66" s="7" t="n">
         <v>45438.79166666666</v>
       </c>
-      <c r="H66" s="8" t="n">
+      <c r="H66" s="7" t="n">
         <v>45441.79166666666</v>
       </c>
-      <c r="I66" s="8" t="n">
+      <c r="I66" s="7" t="n">
         <v>45522.79166666666</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -12480,13 +12462,13 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" s="8" t="n">
+      <c r="G67" s="7" t="n">
         <v>45517.79166666666</v>
       </c>
-      <c r="H67" s="8" t="n">
+      <c r="H67" s="7" t="n">
         <v>45517.79166666666</v>
       </c>
-      <c r="I67" s="8" t="n">
+      <c r="I67" s="7" t="n">
         <v>45538.79166666666</v>
       </c>
       <c r="J67" t="inlineStr">
@@ -12559,13 +12541,13 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" s="8" t="n">
+      <c r="G68" s="7" t="n">
         <v>45546.79166666666</v>
       </c>
-      <c r="H68" s="8" t="n">
+      <c r="H68" s="7" t="n">
         <v>45546.79166666666</v>
       </c>
-      <c r="I68" s="8" t="n">
+      <c r="I68" s="7" t="n">
         <v>45574.79166666666</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -12638,13 +12620,13 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" s="8" t="n">
+      <c r="G69" s="7" t="n">
         <v>45540.79166666666</v>
       </c>
-      <c r="H69" s="8" t="n">
+      <c r="H69" s="7" t="n">
         <v>45540.79166666666</v>
       </c>
-      <c r="I69" s="8" t="n">
+      <c r="I69" s="7" t="n">
         <v>45540.79166666666</v>
       </c>
       <c r="J69" t="inlineStr">
@@ -12715,13 +12697,13 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" s="8" t="n">
+      <c r="G70" s="7" t="n">
         <v>45558.79166666666</v>
       </c>
-      <c r="H70" s="8" t="n">
+      <c r="H70" s="7" t="n">
         <v>45558.79166666666</v>
       </c>
-      <c r="I70" s="8" t="n">
+      <c r="I70" s="7" t="n">
         <v>45558.79166666666</v>
       </c>
       <c r="J70" t="inlineStr">
@@ -12796,13 +12778,13 @@
           <t>[Ver 2.25]; [Ver 4.1]</t>
         </is>
       </c>
-      <c r="G71" s="8" t="n">
+      <c r="G71" s="7" t="n">
         <v>45578.79166666666</v>
       </c>
-      <c r="H71" s="8" t="n">
+      <c r="H71" s="7" t="n">
         <v>45904.26666666667</v>
       </c>
-      <c r="I71" s="8" t="n">
+      <c r="I71" s="7" t="n">
         <v>45937.60625</v>
       </c>
       <c r="J71" t="inlineStr">
@@ -12877,13 +12859,13 @@
           <t>[Ver 4.1]</t>
         </is>
       </c>
-      <c r="G72" s="8" t="n">
+      <c r="G72" s="7" t="n">
         <v>45643.79166666666</v>
       </c>
-      <c r="H72" s="8" t="n">
+      <c r="H72" s="7" t="n">
         <v>45904.26111111111</v>
       </c>
-      <c r="I72" s="8" t="n">
+      <c r="I72" s="7" t="n">
         <v>45937.60625</v>
       </c>
       <c r="J72" t="inlineStr">
@@ -12958,13 +12940,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G73" s="8" t="n">
+      <c r="G73" s="7" t="n">
         <v>45915.33055555556</v>
       </c>
-      <c r="H73" s="8" t="n">
+      <c r="H73" s="7" t="n">
         <v>45932.30555555555</v>
       </c>
-      <c r="I73" s="8" t="n">
+      <c r="I73" s="7" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J73" t="inlineStr">
@@ -13031,13 +13013,13 @@
           <t>[Ver 2.25]</t>
         </is>
       </c>
-      <c r="G74" s="8" t="n">
+      <c r="G74" s="7" t="n">
         <v>45915.33055555556</v>
       </c>
-      <c r="H74" s="8" t="n">
+      <c r="H74" s="7" t="n">
         <v>45932.60069444445</v>
       </c>
-      <c r="I74" s="8" t="n">
+      <c r="I74" s="7" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J74" t="inlineStr">
@@ -13108,13 +13090,13 @@
           <t>[Ver. 2.24.1]</t>
         </is>
       </c>
-      <c r="G75" s="8" t="n">
+      <c r="G75" s="7" t="n">
         <v>45924.79166666666</v>
       </c>
-      <c r="H75" s="8" t="n">
+      <c r="H75" s="7" t="n">
         <v>45926.29861111111</v>
       </c>
-      <c r="I75" s="8" t="n">
+      <c r="I75" s="7" t="n">
         <v>45937.57916666667</v>
       </c>
       <c r="J75" t="inlineStr">
@@ -13189,13 +13171,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G76" s="8" t="n">
+      <c r="G76" s="7" t="n">
         <v>45547.79166666666</v>
       </c>
-      <c r="H76" s="8" t="n">
+      <c r="H76" s="7" t="n">
         <v>45558.79166666666</v>
       </c>
-      <c r="I76" s="8" t="n">
+      <c r="I76" s="7" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J76" t="inlineStr">
@@ -13272,13 +13254,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G77" s="8" t="n">
+      <c r="G77" s="7" t="n">
         <v>45545.79166666666</v>
       </c>
-      <c r="H77" s="8" t="n">
+      <c r="H77" s="7" t="n">
         <v>45545.79166666666</v>
       </c>
-      <c r="I77" s="8" t="n">
+      <c r="I77" s="7" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J77" t="inlineStr">
@@ -13356,13 +13338,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G78" s="8" t="n">
+      <c r="G78" s="7" t="n">
         <v>45540.79166666666</v>
       </c>
-      <c r="H78" s="8" t="n">
+      <c r="H78" s="7" t="n">
         <v>45543.79166666666</v>
       </c>
-      <c r="I78" s="8" t="n">
+      <c r="I78" s="7" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J78" t="inlineStr">
@@ -13440,13 +13422,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G79" s="8" t="n">
+      <c r="G79" s="7" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="H79" s="8" t="n">
+      <c r="H79" s="7" t="n">
         <v>45539.79166666666</v>
       </c>
-      <c r="I79" s="8" t="n">
+      <c r="I79" s="7" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J79" t="inlineStr">
@@ -13517,13 +13499,13 @@
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" s="8" t="n">
+      <c r="G80" s="7" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="H80" s="8" t="n">
+      <c r="H80" s="7" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="I80" s="8" t="n">
+      <c r="I80" s="7" t="n">
         <v>45575.79166666666</v>
       </c>
       <c r="J80" t="inlineStr">
@@ -13600,13 +13582,13 @@
           <t>[Ver. 2.18]</t>
         </is>
       </c>
-      <c r="G81" s="8" t="n">
+      <c r="G81" s="7" t="n">
         <v>45559.79166666666</v>
       </c>
-      <c r="H81" s="8" t="n">
+      <c r="H81" s="7" t="n">
         <v>45564.79166666666</v>
       </c>
-      <c r="I81" s="8" t="n">
+      <c r="I81" s="7" t="n">
         <v>45579.79166666666</v>
       </c>
       <c r="J81" t="inlineStr">
@@ -13677,13 +13659,13 @@
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" s="8" t="n">
+      <c r="G82" s="7" t="n">
         <v>45578.79166666666</v>
       </c>
-      <c r="H82" s="8" t="n">
+      <c r="H82" s="7" t="n">
         <v>45585.79166666666</v>
       </c>
-      <c r="I82" s="8" t="n">
+      <c r="I82" s="7" t="n">
         <v>45585.79166666666</v>
       </c>
       <c r="J82" t="inlineStr">
@@ -13754,13 +13736,13 @@
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" s="8" t="n">
+      <c r="G83" s="7" t="n">
         <v>45870.79166666666</v>
       </c>
-      <c r="H83" s="8" t="n">
+      <c r="H83" s="7" t="n">
         <v>45986.79166666666</v>
       </c>
-      <c r="I83" s="8" t="n"/>
+      <c r="I83" s="7" t="n"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>WAPSA Web</t>
@@ -13825,13 +13807,13 @@
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" s="8" t="n">
+      <c r="G84" s="7" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="H84" s="8" t="n">
+      <c r="H84" s="7" t="n">
         <v>45552.79166666666</v>
       </c>
-      <c r="I84" s="8" t="n">
+      <c r="I84" s="7" t="n">
         <v>45552.79166666666</v>
       </c>
       <c r="J84" t="inlineStr">
@@ -13902,13 +13884,13 @@
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" s="8" t="n">
+      <c r="G85" s="7" t="n">
         <v>45589.79166666666</v>
       </c>
-      <c r="H85" s="8" t="n">
+      <c r="H85" s="7" t="n">
         <v>45589.79166666666</v>
       </c>
-      <c r="I85" s="8" t="n">
+      <c r="I85" s="7" t="n">
         <v>45606.79166666666</v>
       </c>
       <c r="J85" t="inlineStr">
@@ -13985,13 +13967,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G86" s="8" t="n">
+      <c r="G86" s="7" t="n">
         <v>45592.79166666666</v>
       </c>
-      <c r="H86" s="8" t="n">
+      <c r="H86" s="7" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="I86" s="8" t="n">
+      <c r="I86" s="7" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J86" t="inlineStr">
@@ -14062,13 +14044,13 @@
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" s="8" t="n">
+      <c r="G87" s="7" t="n">
         <v>45595.79166666666</v>
       </c>
-      <c r="H87" s="8" t="n">
+      <c r="H87" s="7" t="n">
         <v>45595.79166666666</v>
       </c>
-      <c r="I87" s="8" t="n">
+      <c r="I87" s="7" t="n">
         <v>45616.79166666666</v>
       </c>
       <c r="J87" t="inlineStr">
@@ -14141,13 +14123,13 @@
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" s="8" t="n">
+      <c r="G88" s="7" t="n">
         <v>45595.79166666666</v>
       </c>
-      <c r="H88" s="8" t="n">
+      <c r="H88" s="7" t="n">
         <v>45614.79166666666</v>
       </c>
-      <c r="I88" s="8" t="n">
+      <c r="I88" s="7" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J88" t="inlineStr">
@@ -14218,13 +14200,13 @@
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" s="8" t="n">
+      <c r="G89" s="7" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="H89" s="8" t="n">
+      <c r="H89" s="7" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="I89" s="8" t="n">
+      <c r="I89" s="7" t="n">
         <v>45606.79166666666</v>
       </c>
       <c r="J89" t="inlineStr">
@@ -14295,13 +14277,13 @@
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" s="8" t="n">
+      <c r="G90" s="7" t="n">
         <v>45595.79166666666</v>
       </c>
-      <c r="H90" s="8" t="n">
+      <c r="H90" s="7" t="n">
         <v>45614.79166666666</v>
       </c>
-      <c r="I90" s="8" t="n">
+      <c r="I90" s="7" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J90" t="inlineStr">
@@ -14378,13 +14360,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G91" s="8" t="n">
+      <c r="G91" s="7" t="n">
         <v>45614.79166666666</v>
       </c>
-      <c r="H91" s="8" t="n">
+      <c r="H91" s="7" t="n">
         <v>45614.79166666666</v>
       </c>
-      <c r="I91" s="8" t="n">
+      <c r="I91" s="7" t="n">
         <v>45662.79166666666</v>
       </c>
       <c r="J91" t="inlineStr">
@@ -14455,13 +14437,13 @@
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" s="8" t="n">
+      <c r="G92" s="7" t="n">
         <v>45608.79166666666</v>
       </c>
-      <c r="H92" s="8" t="n">
+      <c r="H92" s="7" t="n">
         <v>45617.79166666666</v>
       </c>
-      <c r="I92" s="8" t="n">
+      <c r="I92" s="7" t="n">
         <v>45621.79166666666</v>
       </c>
       <c r="J92" t="inlineStr">
@@ -14538,13 +14520,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G93" s="8" t="n">
+      <c r="G93" s="7" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="H93" s="8" t="n">
+      <c r="H93" s="7" t="n">
         <v>45606.79166666666</v>
       </c>
-      <c r="I93" s="8" t="n">
+      <c r="I93" s="7" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J93" t="inlineStr">
@@ -14619,13 +14601,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G94" s="8" t="n">
+      <c r="G94" s="7" t="n">
         <v>45617.79166666666</v>
       </c>
-      <c r="H94" s="8" t="n">
+      <c r="H94" s="7" t="n">
         <v>45617.79166666666</v>
       </c>
-      <c r="I94" s="8" t="n">
+      <c r="I94" s="7" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J94" t="inlineStr">
@@ -14700,13 +14682,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G95" s="8" t="n">
+      <c r="G95" s="7" t="n">
         <v>45627.79166666666</v>
       </c>
-      <c r="H95" s="8" t="n">
+      <c r="H95" s="7" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="I95" s="8" t="n">
+      <c r="I95" s="7" t="n">
         <v>45671.79166666666</v>
       </c>
       <c r="J95" t="inlineStr">
@@ -14781,13 +14763,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G96" s="8" t="n">
+      <c r="G96" s="7" t="n">
         <v>45623.79166666666</v>
       </c>
-      <c r="H96" s="8" t="n">
+      <c r="H96" s="7" t="n">
         <v>45623.79166666666</v>
       </c>
-      <c r="I96" s="8" t="n">
+      <c r="I96" s="7" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J96" t="inlineStr">
@@ -14858,13 +14840,13 @@
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" s="8" t="n">
+      <c r="G97" s="7" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="H97" s="8" t="n">
+      <c r="H97" s="7" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="I97" s="8" t="n">
+      <c r="I97" s="7" t="n">
         <v>45680.79166666666</v>
       </c>
       <c r="J97" t="inlineStr">
@@ -14941,13 +14923,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G98" s="8" t="n">
+      <c r="G98" s="7" t="n">
         <v>45388.79166666666</v>
       </c>
-      <c r="H98" s="8" t="n">
+      <c r="H98" s="7" t="n">
         <v>45389.79166666666</v>
       </c>
-      <c r="I98" s="8" t="n">
+      <c r="I98" s="7" t="n">
         <v>45418.79166666666</v>
       </c>
       <c r="J98" t="inlineStr">
@@ -15018,13 +15000,13 @@
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" s="8" t="n">
+      <c r="G99" s="7" t="n">
         <v>45396.79166666666</v>
       </c>
-      <c r="H99" s="8" t="n">
+      <c r="H99" s="7" t="n">
         <v>45435.79166666666</v>
       </c>
-      <c r="I99" s="8" t="n">
+      <c r="I99" s="7" t="n">
         <v>45435.79166666666</v>
       </c>
       <c r="J99" t="inlineStr">
@@ -15101,13 +15083,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G100" s="8" t="n">
+      <c r="G100" s="7" t="n">
         <v>45399.79166666666</v>
       </c>
-      <c r="H100" s="8" t="n">
+      <c r="H100" s="7" t="n">
         <v>45399.79166666666</v>
       </c>
-      <c r="I100" s="8" t="n">
+      <c r="I100" s="7" t="n">
         <v>45418.79166666666</v>
       </c>
       <c r="J100" t="inlineStr">
@@ -15182,13 +15164,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G101" s="8" t="n">
+      <c r="G101" s="7" t="n">
         <v>45398.79166666666</v>
       </c>
-      <c r="H101" s="8" t="n">
+      <c r="H101" s="7" t="n">
         <v>45398.79166666666</v>
       </c>
-      <c r="I101" s="8" t="n">
+      <c r="I101" s="7" t="n">
         <v>45418.79166666666</v>
       </c>
       <c r="J101" t="inlineStr">
@@ -15263,13 +15245,13 @@
           <t>[Ver. 2.16]</t>
         </is>
       </c>
-      <c r="G102" s="8" t="n">
+      <c r="G102" s="7" t="n">
         <v>45424.79166666666</v>
       </c>
-      <c r="H102" s="8" t="n">
+      <c r="H102" s="7" t="n">
         <v>45425.79166666666</v>
       </c>
-      <c r="I102" s="8" t="n">
+      <c r="I102" s="7" t="n">
         <v>45427.79166666666</v>
       </c>
       <c r="J102" t="inlineStr">
@@ -15340,13 +15322,13 @@
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" s="8" t="n">
+      <c r="G103" s="7" t="n">
         <v>45405.79166666666</v>
       </c>
-      <c r="H103" s="8" t="n">
+      <c r="H103" s="7" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="I103" s="8" t="n">
+      <c r="I103" s="7" t="n">
         <v>45432.79166666666</v>
       </c>
       <c r="J103" t="inlineStr">
@@ -15417,13 +15399,13 @@
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" s="8" t="n">
+      <c r="G104" s="7" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="H104" s="8" t="n">
+      <c r="H104" s="7" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="I104" s="8" t="n">
+      <c r="I104" s="7" t="n">
         <v>45432.79166666666</v>
       </c>
       <c r="J104" t="inlineStr">
@@ -15498,13 +15480,13 @@
           <t>[2.16.1]</t>
         </is>
       </c>
-      <c r="G105" s="8" t="n">
+      <c r="G105" s="7" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="H105" s="8" t="n">
+      <c r="H105" s="7" t="n">
         <v>45432.79166666666</v>
       </c>
-      <c r="I105" s="8" t="n">
+      <c r="I105" s="7" t="n">
         <v>45438.79166666666</v>
       </c>
       <c r="J105" t="inlineStr">
@@ -15579,13 +15561,13 @@
           <t>[2.16.1]</t>
         </is>
       </c>
-      <c r="G106" s="8" t="n">
+      <c r="G106" s="7" t="n">
         <v>45433.79166666666</v>
       </c>
-      <c r="H106" s="8" t="n">
+      <c r="H106" s="7" t="n">
         <v>45433.79166666666</v>
       </c>
-      <c r="I106" s="8" t="n">
+      <c r="I106" s="7" t="n">
         <v>45438.79166666666</v>
       </c>
       <c r="J106" t="inlineStr">
@@ -15656,13 +15638,13 @@
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" s="8" t="n">
+      <c r="G107" s="7" t="n">
         <v>45438.79166666666</v>
       </c>
-      <c r="H107" s="8" t="n">
+      <c r="H107" s="7" t="n">
         <v>45438.79166666666</v>
       </c>
-      <c r="I107" s="8" t="n">
+      <c r="I107" s="7" t="n">
         <v>45438.79166666666</v>
       </c>
       <c r="J107" t="inlineStr">
@@ -15737,13 +15719,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G108" s="8" t="n">
+      <c r="G108" s="7" t="n">
         <v>45342.79166666666</v>
       </c>
-      <c r="H108" s="8" t="n">
+      <c r="H108" s="7" t="n">
         <v>45342.79166666666</v>
       </c>
-      <c r="I108" s="8" t="n">
+      <c r="I108" s="7" t="n">
         <v>45369.79166666666</v>
       </c>
       <c r="J108" t="inlineStr">
@@ -15820,13 +15802,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G109" s="8" t="n">
+      <c r="G109" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="H109" s="8" t="n">
+      <c r="H109" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="I109" s="8" t="n">
+      <c r="I109" s="7" t="n">
         <v>45431.79166666666</v>
       </c>
       <c r="J109" t="inlineStr">
@@ -15901,13 +15883,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G110" s="8" t="n">
+      <c r="G110" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="H110" s="8" t="n">
+      <c r="H110" s="7" t="n">
         <v>45361.79166666666</v>
       </c>
-      <c r="I110" s="8" t="n">
+      <c r="I110" s="7" t="n">
         <v>45376.79166666666</v>
       </c>
       <c r="J110" t="inlineStr">
@@ -15980,13 +15962,13 @@
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" s="8" t="n">
+      <c r="G111" s="7" t="n">
         <v>45368.79166666666</v>
       </c>
-      <c r="H111" s="8" t="n">
+      <c r="H111" s="7" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="I111" s="8" t="n">
+      <c r="I111" s="7" t="n">
         <v>45376.79166666666</v>
       </c>
       <c r="J111" t="inlineStr">
@@ -16059,13 +16041,13 @@
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" s="8" t="n">
+      <c r="G112" s="7" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="H112" s="8" t="n">
+      <c r="H112" s="7" t="n">
         <v>45369.79166666666</v>
       </c>
-      <c r="I112" s="8" t="n">
+      <c r="I112" s="7" t="n">
         <v>45376.79166666666</v>
       </c>
       <c r="J112" t="inlineStr">
@@ -16136,11 +16118,11 @@
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" s="8" t="n">
+      <c r="G113" s="7" t="n">
         <v>45951.79166666666</v>
       </c>
-      <c r="H113" s="8" t="n"/>
-      <c r="I113" s="8" t="n"/>
+      <c r="H113" s="7" t="n"/>
+      <c r="I113" s="7" t="n"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16205,13 +16187,13 @@
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" s="8" t="n">
+      <c r="G114" s="7" t="n">
         <v>45642.79166666666</v>
       </c>
-      <c r="H114" s="8" t="n">
+      <c r="H114" s="7" t="n">
         <v>45642.79166666666</v>
       </c>
-      <c r="I114" s="8" t="n"/>
+      <c r="I114" s="7" t="n"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16284,13 +16266,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G115" s="8" t="n">
+      <c r="G115" s="7" t="n">
         <v>45845.25347222222</v>
       </c>
-      <c r="H115" s="8" t="n">
+      <c r="H115" s="7" t="n">
         <v>45845.79166666666</v>
       </c>
-      <c r="I115" s="8" t="n"/>
+      <c r="I115" s="7" t="n"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16367,13 +16349,13 @@
           <t>[Ver. 4.29]</t>
         </is>
       </c>
-      <c r="G116" s="8" t="n">
+      <c r="G116" s="7" t="n">
         <v>46047.79166666666</v>
       </c>
-      <c r="H116" s="8" t="n">
+      <c r="H116" s="7" t="n">
         <v>46104.26111111111</v>
       </c>
-      <c r="I116" s="8" t="n"/>
+      <c r="I116" s="7" t="n"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16442,13 +16424,13 @@
           <t>[Ver. 2.29]</t>
         </is>
       </c>
-      <c r="G117" s="8" t="n">
+      <c r="G117" s="7" t="n">
         <v>46050.79166666666</v>
       </c>
-      <c r="H117" s="8" t="n">
+      <c r="H117" s="7" t="n">
         <v>46062.46458333333</v>
       </c>
-      <c r="I117" s="8" t="n"/>
+      <c r="I117" s="7" t="n"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16517,13 +16499,13 @@
           <t>[Ver. 2.28]; SLA</t>
         </is>
       </c>
-      <c r="G118" s="8" t="n">
+      <c r="G118" s="7" t="n">
         <v>46090.20833333334</v>
       </c>
-      <c r="H118" s="8" t="n">
+      <c r="H118" s="7" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="I118" s="8" t="n"/>
+      <c r="I118" s="7" t="n"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -16600,11 +16582,11 @@
           <t>[Ver. 2.28]; SLA</t>
         </is>
       </c>
-      <c r="G119" s="8" t="n">
+      <c r="G119" s="7" t="n">
         <v>46089.79166666666</v>
       </c>
-      <c r="H119" s="8" t="n"/>
-      <c r="I119" s="8" t="n"/>
+      <c r="H119" s="7" t="n"/>
+      <c r="I119" s="7" t="n"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>WapsaWeb</t>
@@ -16669,13 +16651,13 @@
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" s="8" t="n">
+      <c r="G120" s="7" t="n">
         <v>46094.54930555556</v>
       </c>
-      <c r="H120" s="8" t="n">
+      <c r="H120" s="7" t="n">
         <v>46094.54930555556</v>
       </c>
-      <c r="I120" s="8" t="n">
+      <c r="I120" s="7" t="n">
         <v>46097.30972222222</v>
       </c>
       <c r="J120" t="inlineStr">
@@ -16750,13 +16732,13 @@
           <t>[Ver. 2.28]</t>
         </is>
       </c>
-      <c r="G121" s="8" t="n">
+      <c r="G121" s="7" t="n">
         <v>46096.71458333333</v>
       </c>
-      <c r="H121" s="8" t="n">
+      <c r="H121" s="7" t="n">
         <v>46096.71458333333</v>
       </c>
-      <c r="I121" s="8" t="n"/>
+      <c r="I121" s="7" t="n"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>WAPSA</t>
@@ -16825,13 +16807,13 @@
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" s="8" t="n">
+      <c r="G122" s="7" t="n">
         <v>46097.56319444445</v>
       </c>
-      <c r="H122" s="8" t="n">
+      <c r="H122" s="7" t="n">
         <v>46097.56319444445</v>
       </c>
-      <c r="I122" s="8" t="n">
+      <c r="I122" s="7" t="n">
         <v>46097.56319444445</v>
       </c>
       <c r="J122" t="inlineStr">
@@ -16898,9 +16880,9 @@
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" s="8" t="n"/>
-      <c r="H123" s="8" t="n"/>
-      <c r="I123" s="8" t="n"/>
+      <c r="G123" s="7" t="n"/>
+      <c r="H123" s="7" t="n"/>
+      <c r="I123" s="7" t="n"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
@@ -16953,13 +16935,13 @@
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" s="8" t="n">
+      <c r="G124" s="7" t="n">
         <v>45725.79166666666</v>
       </c>
-      <c r="H124" s="8" t="n">
+      <c r="H124" s="7" t="n">
         <v>45725.79166666666</v>
       </c>
-      <c r="I124" s="8" t="n">
+      <c r="I124" s="7" t="n">
         <v>45725.79166666666</v>
       </c>
       <c r="J124" t="inlineStr">
@@ -17030,13 +17012,13 @@
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" s="8" t="n">
+      <c r="G125" s="7" t="n">
         <v>45410.79166666666</v>
       </c>
-      <c r="H125" s="8" t="n">
+      <c r="H125" s="7" t="n">
         <v>45454.79166666666</v>
       </c>
-      <c r="I125" s="8" t="n">
+      <c r="I125" s="7" t="n">
         <v>45460.79166666666</v>
       </c>
       <c r="J125" t="inlineStr">
@@ -17109,13 +17091,13 @@
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" s="8" t="n">
+      <c r="G126" s="7" t="n">
         <v>45453.79166666666</v>
       </c>
-      <c r="H126" s="8" t="n">
+      <c r="H126" s="7" t="n">
         <v>45454.79166666666</v>
       </c>
-      <c r="I126" s="8" t="n">
+      <c r="I126" s="7" t="n">
         <v>45454.79166666666</v>
       </c>
       <c r="J126" t="inlineStr">
@@ -17186,13 +17168,13 @@
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" s="8" t="n">
+      <c r="G127" s="7" t="n">
         <v>45466.79166666666</v>
       </c>
-      <c r="H127" s="8" t="n">
+      <c r="H127" s="7" t="n">
         <v>45466.79166666666</v>
       </c>
-      <c r="I127" s="8" t="n">
+      <c r="I127" s="7" t="n">
         <v>45466.79166666666</v>
       </c>
       <c r="J127" t="inlineStr">
@@ -17263,13 +17245,13 @@
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" s="8" t="n">
+      <c r="G128" s="7" t="n">
         <v>45761.79166666666</v>
       </c>
-      <c r="H128" s="8" t="n">
+      <c r="H128" s="7" t="n">
         <v>45769.79166666666</v>
       </c>
-      <c r="I128" s="8" t="n">
+      <c r="I128" s="7" t="n">
         <v>45809.79166666666</v>
       </c>
       <c r="J128" t="inlineStr">
@@ -17342,13 +17324,13 @@
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" s="8" t="n">
+      <c r="G129" s="7" t="n">
         <v>45747.79166666666</v>
       </c>
-      <c r="H129" s="8" t="n">
+      <c r="H129" s="7" t="n">
         <v>45764.39930555555</v>
       </c>
-      <c r="I129" s="8" t="n">
+      <c r="I129" s="7" t="n">
         <v>45810.79166666666</v>
       </c>
       <c r="J129" t="inlineStr">
@@ -17413,13 +17395,13 @@
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" s="8" t="n">
+      <c r="G130" s="7" t="n">
         <v>45815.29375</v>
       </c>
-      <c r="H130" s="8" t="n">
+      <c r="H130" s="7" t="n">
         <v>45815.37708333333</v>
       </c>
-      <c r="I130" s="8" t="n">
+      <c r="I130" s="7" t="n">
         <v>45822.4375</v>
       </c>
       <c r="J130" t="inlineStr">
@@ -17490,13 +17472,13 @@
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" s="8" t="n">
+      <c r="G131" s="7" t="n">
         <v>45813.79166666666</v>
       </c>
-      <c r="H131" s="8" t="n">
+      <c r="H131" s="7" t="n">
         <v>45818.33819444444</v>
       </c>
-      <c r="I131" s="8" t="n">
+      <c r="I131" s="7" t="n">
         <v>45832.42916666667</v>
       </c>
       <c r="J131" t="inlineStr">
@@ -17567,13 +17549,13 @@
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" s="8" t="n">
+      <c r="G132" s="7" t="n">
         <v>45820.51458333333</v>
       </c>
-      <c r="H132" s="8" t="n">
+      <c r="H132" s="7" t="n">
         <v>45820.51458333333</v>
       </c>
-      <c r="I132" s="8" t="n">
+      <c r="I132" s="7" t="n">
         <v>45827.79166666666</v>
       </c>
       <c r="J132" t="inlineStr">
@@ -17644,13 +17626,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G133" s="8" t="n">
+      <c r="G133" s="7" t="n">
         <v>45851.79166666666</v>
       </c>
-      <c r="H133" s="8" t="n">
+      <c r="H133" s="7" t="n">
         <v>45859.42916666667</v>
       </c>
-      <c r="I133" s="8" t="n"/>
+      <c r="I133" s="7" t="n"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -17719,13 +17701,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G134" s="8" t="n">
+      <c r="G134" s="7" t="n">
         <v>45856.60833333333</v>
       </c>
-      <c r="H134" s="8" t="n">
+      <c r="H134" s="7" t="n">
         <v>45856.60833333333</v>
       </c>
-      <c r="I134" s="8" t="n">
+      <c r="I134" s="7" t="n">
         <v>45859.375</v>
       </c>
       <c r="J134" t="inlineStr">
@@ -17796,13 +17778,13 @@
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" s="8" t="n">
+      <c r="G135" s="7" t="n">
         <v>45453.79166666666</v>
       </c>
-      <c r="H135" s="8" t="n">
+      <c r="H135" s="7" t="n">
         <v>45453.79166666666</v>
       </c>
-      <c r="I135" s="8" t="n">
+      <c r="I135" s="7" t="n">
         <v>45460.79166666666</v>
       </c>
       <c r="J135" t="inlineStr">
@@ -17875,13 +17857,13 @@
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" s="8" t="n">
+      <c r="G136" s="7" t="n">
         <v>45460.79166666666</v>
       </c>
-      <c r="H136" s="8" t="n">
+      <c r="H136" s="7" t="n">
         <v>45461.79166666666</v>
       </c>
-      <c r="I136" s="8" t="n">
+      <c r="I136" s="7" t="n">
         <v>45490.79166666666</v>
       </c>
       <c r="J136" t="inlineStr">
@@ -17954,13 +17936,13 @@
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" s="8" t="n">
+      <c r="G137" s="7" t="n">
         <v>45461.79166666666</v>
       </c>
-      <c r="H137" s="8" t="n">
+      <c r="H137" s="7" t="n">
         <v>45461.79166666666</v>
       </c>
-      <c r="I137" s="8" t="n">
+      <c r="I137" s="7" t="n">
         <v>45510.79166666666</v>
       </c>
       <c r="J137" t="inlineStr">
@@ -18033,13 +18015,13 @@
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" s="8" t="n">
+      <c r="G138" s="7" t="n">
         <v>45475.79166666666</v>
       </c>
-      <c r="H138" s="8" t="n">
+      <c r="H138" s="7" t="n">
         <v>45475.79166666666</v>
       </c>
-      <c r="I138" s="8" t="n">
+      <c r="I138" s="7" t="n">
         <v>45475.79166666666</v>
       </c>
       <c r="J138" t="inlineStr">
@@ -18110,13 +18092,13 @@
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" s="8" t="n">
+      <c r="G139" s="7" t="n">
         <v>45481.79166666666</v>
       </c>
-      <c r="H139" s="8" t="n">
+      <c r="H139" s="7" t="n">
         <v>45481.79166666666</v>
       </c>
-      <c r="I139" s="8" t="n">
+      <c r="I139" s="7" t="n">
         <v>45479.79166666666</v>
       </c>
       <c r="J139" t="inlineStr">
@@ -18187,13 +18169,13 @@
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" s="8" t="n">
+      <c r="G140" s="7" t="n">
         <v>45487.79166666666</v>
       </c>
-      <c r="H140" s="8" t="n">
+      <c r="H140" s="7" t="n">
         <v>45487.79166666666</v>
       </c>
-      <c r="I140" s="8" t="n">
+      <c r="I140" s="7" t="n">
         <v>45487.79166666666</v>
       </c>
       <c r="J140" t="inlineStr">
@@ -18264,13 +18246,13 @@
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" s="8" t="n">
+      <c r="G141" s="7" t="n">
         <v>45496.79166666666</v>
       </c>
-      <c r="H141" s="8" t="n">
+      <c r="H141" s="7" t="n">
         <v>45496.79166666666</v>
       </c>
-      <c r="I141" s="8" t="n">
+      <c r="I141" s="7" t="n">
         <v>45496.79166666666</v>
       </c>
       <c r="J141" t="inlineStr">
@@ -18345,13 +18327,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G142" s="8" t="n">
+      <c r="G142" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H142" s="8" t="n">
+      <c r="H142" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="I142" s="8" t="n">
+      <c r="I142" s="7" t="n">
         <v>45333.79166666666</v>
       </c>
       <c r="J142" t="inlineStr">
@@ -18426,13 +18408,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G143" s="8" t="n">
+      <c r="G143" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H143" s="8" t="n">
+      <c r="H143" s="7" t="n">
         <v>45334.79166666666</v>
       </c>
-      <c r="I143" s="8" t="n">
+      <c r="I143" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J143" t="inlineStr">
@@ -18507,13 +18489,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G144" s="8" t="n">
+      <c r="G144" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H144" s="8" t="n">
+      <c r="H144" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="I144" s="8" t="n">
+      <c r="I144" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J144" t="inlineStr">
@@ -18588,13 +18570,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G145" s="8" t="n">
+      <c r="G145" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H145" s="8" t="n">
+      <c r="H145" s="7" t="n">
         <v>45327.79166666666</v>
       </c>
-      <c r="I145" s="8" t="n">
+      <c r="I145" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J145" t="inlineStr">
@@ -18669,13 +18651,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G146" s="8" t="n">
+      <c r="G146" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H146" s="8" t="n">
+      <c r="H146" s="7" t="n">
         <v>45321.79166666666</v>
       </c>
-      <c r="I146" s="8" t="n">
+      <c r="I146" s="7" t="n">
         <v>45323.79166666666</v>
       </c>
       <c r="J146" t="inlineStr">
@@ -18752,13 +18734,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G147" s="8" t="n">
+      <c r="G147" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H147" s="8" t="n">
+      <c r="H147" s="7" t="n">
         <v>45327.79166666666</v>
       </c>
-      <c r="I147" s="8" t="n">
+      <c r="I147" s="7" t="n">
         <v>45330.79166666666</v>
       </c>
       <c r="J147" t="inlineStr">
@@ -18829,13 +18811,13 @@
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" s="8" t="n">
+      <c r="G148" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H148" s="8" t="n">
+      <c r="H148" s="7" t="n">
         <v>45327.79166666666</v>
       </c>
-      <c r="I148" s="8" t="n">
+      <c r="I148" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J148" t="inlineStr">
@@ -18910,13 +18892,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G149" s="8" t="n">
+      <c r="G149" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H149" s="8" t="n">
+      <c r="H149" s="7" t="n">
         <v>45322.79166666666</v>
       </c>
-      <c r="I149" s="8" t="n">
+      <c r="I149" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J149" t="inlineStr">
@@ -18991,13 +18973,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G150" s="8" t="n">
+      <c r="G150" s="7" t="n">
         <v>45320.79166666666</v>
       </c>
-      <c r="H150" s="8" t="n">
+      <c r="H150" s="7" t="n">
         <v>45321.79166666666</v>
       </c>
-      <c r="I150" s="8" t="n">
+      <c r="I150" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J150" t="inlineStr">
@@ -19072,13 +19054,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G151" s="8" t="n">
+      <c r="G151" s="7" t="n">
         <v>45322.79166666666</v>
       </c>
-      <c r="H151" s="8" t="n">
+      <c r="H151" s="7" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="I151" s="8" t="n">
+      <c r="I151" s="7" t="n">
         <v>45330.79166666666</v>
       </c>
       <c r="J151" t="inlineStr">
@@ -19155,13 +19137,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G152" s="8" t="n">
+      <c r="G152" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H152" s="8" t="n">
+      <c r="H152" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="I152" s="8" t="n">
+      <c r="I152" s="7" t="n">
         <v>45347.79166666666</v>
       </c>
       <c r="J152" t="inlineStr">
@@ -19238,13 +19220,13 @@
           <t>Consulta</t>
         </is>
       </c>
-      <c r="G153" s="8" t="n">
+      <c r="G153" s="7" t="n">
         <v>45326.79166666666</v>
       </c>
-      <c r="H153" s="8" t="n">
+      <c r="H153" s="7" t="n">
         <v>45326.79166666666</v>
       </c>
-      <c r="I153" s="8" t="n">
+      <c r="I153" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J153" t="inlineStr">
@@ -19325,13 +19307,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G154" s="8" t="n">
+      <c r="G154" s="7" t="n">
         <v>45328.79166666666</v>
       </c>
-      <c r="H154" s="8" t="n">
+      <c r="H154" s="7" t="n">
         <v>45328.79166666666</v>
       </c>
-      <c r="I154" s="8" t="n">
+      <c r="I154" s="7" t="n">
         <v>45328.79166666666</v>
       </c>
       <c r="J154" t="inlineStr">
@@ -19406,13 +19388,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G155" s="8" t="n">
+      <c r="G155" s="7" t="n">
         <v>45328.79166666666</v>
       </c>
-      <c r="H155" s="8" t="n">
+      <c r="H155" s="7" t="n">
         <v>45328.79166666666</v>
       </c>
-      <c r="I155" s="8" t="n">
+      <c r="I155" s="7" t="n">
         <v>45328.79166666666</v>
       </c>
       <c r="J155" t="inlineStr">
@@ -19491,13 +19473,13 @@
           <t>Consulta</t>
         </is>
       </c>
-      <c r="G156" s="8" t="n">
+      <c r="G156" s="7" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="H156" s="8" t="n">
+      <c r="H156" s="7" t="n">
         <v>45330.79166666666</v>
       </c>
-      <c r="I156" s="8" t="n">
+      <c r="I156" s="7" t="n">
         <v>45330.79166666666</v>
       </c>
       <c r="J156" t="inlineStr">
@@ -19568,13 +19550,13 @@
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" s="8" t="n">
+      <c r="G157" s="7" t="n">
         <v>45333.79166666666</v>
       </c>
-      <c r="H157" s="8" t="n">
+      <c r="H157" s="7" t="n">
         <v>45333.79166666666</v>
       </c>
-      <c r="I157" s="8" t="n">
+      <c r="I157" s="7" t="n">
         <v>45340.79166666666</v>
       </c>
       <c r="J157" t="inlineStr">
@@ -19649,13 +19631,13 @@
           <t>Consulta</t>
         </is>
       </c>
-      <c r="G158" s="8" t="n">
+      <c r="G158" s="7" t="n">
         <v>45336.79166666666</v>
       </c>
-      <c r="H158" s="8" t="n">
+      <c r="H158" s="7" t="n">
         <v>45336.79166666666</v>
       </c>
-      <c r="I158" s="8" t="n">
+      <c r="I158" s="7" t="n">
         <v>45336.79166666666</v>
       </c>
       <c r="J158" t="inlineStr">
@@ -19726,13 +19708,13 @@
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" s="8" t="n">
+      <c r="G159" s="7" t="n">
         <v>45347.79166666666</v>
       </c>
-      <c r="H159" s="8" t="n">
+      <c r="H159" s="7" t="n">
         <v>45348.79166666666</v>
       </c>
-      <c r="I159" s="8" t="n">
+      <c r="I159" s="7" t="n">
         <v>45348.79166666666</v>
       </c>
       <c r="J159" t="inlineStr">
@@ -19803,13 +19785,13 @@
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" s="8" t="n">
+      <c r="G160" s="7" t="n">
         <v>46051.25902777778</v>
       </c>
-      <c r="H160" s="8" t="n">
+      <c r="H160" s="7" t="n">
         <v>46051.25902777778</v>
       </c>
-      <c r="I160" s="8" t="n">
+      <c r="I160" s="7" t="n">
         <v>46057.79166666666</v>
       </c>
       <c r="J160" t="inlineStr">
@@ -19876,13 +19858,13 @@
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" s="8" t="n">
+      <c r="G161" s="7" t="n">
         <v>46059.29791666667</v>
       </c>
-      <c r="H161" s="8" t="n">
+      <c r="H161" s="7" t="n">
         <v>46059.29791666667</v>
       </c>
-      <c r="I161" s="8" t="n">
+      <c r="I161" s="7" t="n">
         <v>46062.79166666666</v>
       </c>
       <c r="J161" t="inlineStr">
@@ -19955,13 +19937,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G162" s="8" t="n">
+      <c r="G162" s="7" t="n">
         <v>45652.79166666666</v>
       </c>
-      <c r="H162" s="8" t="n">
+      <c r="H162" s="7" t="n">
         <v>45670.79166666666</v>
       </c>
-      <c r="I162" s="8" t="n">
+      <c r="I162" s="7" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J162" t="inlineStr">
@@ -20036,13 +20018,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G163" s="8" t="n">
+      <c r="G163" s="7" t="n">
         <v>45669.79166666666</v>
       </c>
-      <c r="H163" s="8" t="n">
+      <c r="H163" s="7" t="n">
         <v>45669.79166666666</v>
       </c>
-      <c r="I163" s="8" t="n">
+      <c r="I163" s="7" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J163" t="inlineStr">
@@ -20117,13 +20099,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G164" s="8" t="n">
+      <c r="G164" s="7" t="n">
         <v>45669.79166666666</v>
       </c>
-      <c r="H164" s="8" t="n">
+      <c r="H164" s="7" t="n">
         <v>45669.79166666666</v>
       </c>
-      <c r="I164" s="8" t="n">
+      <c r="I164" s="7" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J164" t="inlineStr">
@@ -20198,13 +20180,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G165" s="8" t="n">
+      <c r="G165" s="7" t="n">
         <v>45674.79166666666</v>
       </c>
-      <c r="H165" s="8" t="n">
+      <c r="H165" s="7" t="n">
         <v>45674.79166666666</v>
       </c>
-      <c r="I165" s="8" t="n">
+      <c r="I165" s="7" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J165" t="inlineStr">
@@ -20279,13 +20261,13 @@
           <t>[Ver. 2.21]</t>
         </is>
       </c>
-      <c r="G166" s="8" t="n">
+      <c r="G166" s="7" t="n">
         <v>45680.79166666666</v>
       </c>
-      <c r="H166" s="8" t="n">
+      <c r="H166" s="7" t="n">
         <v>45680.79166666666</v>
       </c>
-      <c r="I166" s="8" t="n">
+      <c r="I166" s="7" t="n">
         <v>45729.79166666666</v>
       </c>
       <c r="J166" t="inlineStr">
@@ -20360,13 +20342,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G167" s="8" t="n">
+      <c r="G167" s="7" t="n">
         <v>45313.79166666666</v>
       </c>
-      <c r="H167" s="8" t="n">
+      <c r="H167" s="7" t="n">
         <v>45316.79166666666</v>
       </c>
-      <c r="I167" s="8" t="n">
+      <c r="I167" s="7" t="n">
         <v>45316.79166666666</v>
       </c>
       <c r="J167" t="inlineStr">
@@ -20443,13 +20425,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G168" s="8" t="n">
+      <c r="G168" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H168" s="8" t="n">
+      <c r="H168" s="7" t="n">
         <v>45316.79166666666</v>
       </c>
-      <c r="I168" s="8" t="n">
+      <c r="I168" s="7" t="n">
         <v>45319.79166666666</v>
       </c>
       <c r="J168" t="inlineStr">
@@ -20524,13 +20506,13 @@
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" s="8" t="n">
+      <c r="G169" s="7" t="n">
         <v>45986.79166666666</v>
       </c>
-      <c r="H169" s="8" t="n">
+      <c r="H169" s="7" t="n">
         <v>45988.79166666666</v>
       </c>
-      <c r="I169" s="8" t="n">
+      <c r="I169" s="7" t="n">
         <v>46049.79166666666</v>
       </c>
       <c r="J169" t="inlineStr">
@@ -20597,13 +20579,13 @@
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" s="8" t="n">
+      <c r="G170" s="7" t="n">
         <v>46048.33472222222</v>
       </c>
-      <c r="H170" s="8" t="n">
+      <c r="H170" s="7" t="n">
         <v>46048.41805555556</v>
       </c>
-      <c r="I170" s="8" t="n">
+      <c r="I170" s="7" t="n">
         <v>46051.29166666666</v>
       </c>
       <c r="J170" t="inlineStr"/>
@@ -20672,13 +20654,13 @@
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" s="8" t="n">
+      <c r="G171" s="7" t="n">
         <v>45657.79166666666</v>
       </c>
-      <c r="H171" s="8" t="n">
+      <c r="H171" s="7" t="n">
         <v>45659.79166666666</v>
       </c>
-      <c r="I171" s="8" t="n">
+      <c r="I171" s="7" t="n">
         <v>45662.79166666666</v>
       </c>
       <c r="J171" t="inlineStr">
@@ -20749,13 +20731,13 @@
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" s="8" t="n">
+      <c r="G172" s="7" t="n">
         <v>45659.79166666666</v>
       </c>
-      <c r="H172" s="8" t="n">
+      <c r="H172" s="7" t="n">
         <v>45659.79166666666</v>
       </c>
-      <c r="I172" s="8" t="n">
+      <c r="I172" s="7" t="n">
         <v>45683.79166666666</v>
       </c>
       <c r="J172" t="inlineStr">
@@ -20828,13 +20810,13 @@
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" s="8" t="n">
+      <c r="G173" s="7" t="n">
         <v>45662.79166666666</v>
       </c>
-      <c r="H173" s="8" t="n">
+      <c r="H173" s="7" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="I173" s="8" t="n">
+      <c r="I173" s="7" t="n">
         <v>45665.79166666666</v>
       </c>
       <c r="J173" t="inlineStr">
@@ -20905,13 +20887,13 @@
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" s="8" t="n">
+      <c r="G174" s="7" t="n">
         <v>45659.79166666666</v>
       </c>
-      <c r="H174" s="8" t="n">
+      <c r="H174" s="7" t="n">
         <v>45663.79166666666</v>
       </c>
-      <c r="I174" s="8" t="n">
+      <c r="I174" s="7" t="n">
         <v>45683.79166666666</v>
       </c>
       <c r="J174" t="inlineStr">
@@ -20978,13 +20960,13 @@
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" s="8" t="n">
+      <c r="G175" s="7" t="n">
         <v>45680.79166666666</v>
       </c>
-      <c r="H175" s="8" t="n">
+      <c r="H175" s="7" t="n">
         <v>45680.79166666666</v>
       </c>
-      <c r="I175" s="8" t="n">
+      <c r="I175" s="7" t="n">
         <v>45694.79166666666</v>
       </c>
       <c r="J175" t="inlineStr">
@@ -21055,13 +21037,13 @@
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" s="8" t="n">
+      <c r="G176" s="7" t="n">
         <v>45682.79166666666</v>
       </c>
-      <c r="H176" s="8" t="n">
+      <c r="H176" s="7" t="n">
         <v>45683.79166666666</v>
       </c>
-      <c r="I176" s="8" t="n">
+      <c r="I176" s="7" t="n">
         <v>45694.79166666666</v>
       </c>
       <c r="J176" t="inlineStr">
@@ -21134,13 +21116,13 @@
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" s="8" t="n">
+      <c r="G177" s="7" t="n">
         <v>45687.79166666666</v>
       </c>
-      <c r="H177" s="8" t="n">
+      <c r="H177" s="7" t="n">
         <v>45687.79166666666</v>
       </c>
-      <c r="I177" s="8" t="n">
+      <c r="I177" s="7" t="n">
         <v>45688.79166666666</v>
       </c>
       <c r="J177" t="inlineStr">
@@ -21213,13 +21195,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G178" s="8" t="n">
+      <c r="G178" s="7" t="n">
         <v>45963.79166666666</v>
       </c>
-      <c r="H178" s="8" t="n">
+      <c r="H178" s="7" t="n">
         <v>45987.43333333333</v>
       </c>
-      <c r="I178" s="8" t="n"/>
+      <c r="I178" s="7" t="n"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21292,13 +21274,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G179" s="8" t="n">
+      <c r="G179" s="7" t="n">
         <v>45944.79166666666</v>
       </c>
-      <c r="H179" s="8" t="n">
+      <c r="H179" s="7" t="n">
         <v>45951.79166666666</v>
       </c>
-      <c r="I179" s="8" t="n"/>
+      <c r="I179" s="7" t="n"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21367,13 +21349,13 @@
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" s="8" t="n">
+      <c r="G180" s="7" t="n">
         <v>45963.79166666666</v>
       </c>
-      <c r="H180" s="8" t="n">
+      <c r="H180" s="7" t="n">
         <v>45979.79166666666</v>
       </c>
-      <c r="I180" s="8" t="n">
+      <c r="I180" s="7" t="n">
         <v>46008.79166666666</v>
       </c>
       <c r="J180" t="inlineStr">
@@ -21444,13 +21426,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G181" s="8" t="n">
+      <c r="G181" s="7" t="n">
         <v>45908.79166666666</v>
       </c>
-      <c r="H181" s="8" t="n">
+      <c r="H181" s="7" t="n">
         <v>45930.79166666666</v>
       </c>
-      <c r="I181" s="8" t="n"/>
+      <c r="I181" s="7" t="n"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21519,13 +21501,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G182" s="8" t="n">
+      <c r="G182" s="7" t="n">
         <v>45936.79166666666</v>
       </c>
-      <c r="H182" s="8" t="n">
+      <c r="H182" s="7" t="n">
         <v>45950.79166666666</v>
       </c>
-      <c r="I182" s="8" t="n"/>
+      <c r="I182" s="7" t="n"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21590,13 +21572,13 @@
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" s="8" t="n">
+      <c r="G183" s="7" t="n">
         <v>45995.79166666666</v>
       </c>
-      <c r="H183" s="8" t="n">
+      <c r="H183" s="7" t="n">
         <v>46006.29166666666</v>
       </c>
-      <c r="I183" s="8" t="n"/>
+      <c r="I183" s="7" t="n"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21665,13 +21647,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G184" s="8" t="n">
+      <c r="G184" s="7" t="n">
         <v>45970.79166666666</v>
       </c>
-      <c r="H184" s="8" t="n">
+      <c r="H184" s="7" t="n">
         <v>45974.51111111111</v>
       </c>
-      <c r="I184" s="8" t="n"/>
+      <c r="I184" s="7" t="n"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21740,13 +21722,13 @@
           <t>[Ver 2.26]</t>
         </is>
       </c>
-      <c r="G185" s="8" t="n">
+      <c r="G185" s="7" t="n">
         <v>45981.79166666666</v>
       </c>
-      <c r="H185" s="8" t="n">
+      <c r="H185" s="7" t="n">
         <v>46006.43541666667</v>
       </c>
-      <c r="I185" s="8" t="n"/>
+      <c r="I185" s="7" t="n"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21811,13 +21793,13 @@
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" s="8" t="n">
+      <c r="G186" s="7" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="H186" s="8" t="n">
+      <c r="H186" s="7" t="n">
         <v>45628.79166666666</v>
       </c>
-      <c r="I186" s="8" t="n">
+      <c r="I186" s="7" t="n">
         <v>45652.79166666666</v>
       </c>
       <c r="J186" t="inlineStr">
@@ -21890,13 +21872,13 @@
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" s="8" t="n">
+      <c r="G187" s="7" t="n">
         <v>45642.79166666666</v>
       </c>
-      <c r="H187" s="8" t="n">
+      <c r="H187" s="7" t="n">
         <v>45652.79166666666</v>
       </c>
-      <c r="I187" s="8" t="n">
+      <c r="I187" s="7" t="n">
         <v>45651.79166666666</v>
       </c>
       <c r="J187" t="inlineStr">
@@ -21973,13 +21955,13 @@
           <t>[Ver. 2.19]</t>
         </is>
       </c>
-      <c r="G188" s="8" t="n">
+      <c r="G188" s="7" t="n">
         <v>45652.79166666666</v>
       </c>
-      <c r="H188" s="8" t="n">
+      <c r="H188" s="7" t="n">
         <v>45652.79166666666</v>
       </c>
-      <c r="I188" s="8" t="n">
+      <c r="I188" s="7" t="n">
         <v>45655.79166666666</v>
       </c>
       <c r="J188" t="inlineStr">
@@ -22054,13 +22036,13 @@
           <t>[Ver 2.24]</t>
         </is>
       </c>
-      <c r="G189" s="8" t="n">
+      <c r="G189" s="7" t="n">
         <v>45820.79166666666</v>
       </c>
-      <c r="H189" s="8" t="n">
+      <c r="H189" s="7" t="n">
         <v>45823.79166666666</v>
       </c>
-      <c r="I189" s="8" t="n"/>
+      <c r="I189" s="7" t="n"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -22133,13 +22115,13 @@
           <t>[Ver. 2.17]</t>
         </is>
       </c>
-      <c r="G190" s="8" t="n">
+      <c r="G190" s="7" t="n">
         <v>45481.79166666666</v>
       </c>
-      <c r="H190" s="8" t="n">
+      <c r="H190" s="7" t="n">
         <v>45481.79166666666</v>
       </c>
-      <c r="I190" s="8" t="n">
+      <c r="I190" s="7" t="n">
         <v>45481.79166666666</v>
       </c>
       <c r="J190" t="inlineStr">
@@ -22210,13 +22192,13 @@
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" s="8" t="n">
+      <c r="G191" s="7" t="n">
         <v>45490.79166666666</v>
       </c>
-      <c r="H191" s="8" t="n">
+      <c r="H191" s="7" t="n">
         <v>45490.79166666666</v>
       </c>
-      <c r="I191" s="8" t="n">
+      <c r="I191" s="7" t="n">
         <v>45508.79166666666</v>
       </c>
       <c r="J191" t="inlineStr">
@@ -22289,13 +22271,13 @@
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" s="8" t="n">
+      <c r="G192" s="7" t="n">
         <v>45505.79166666666</v>
       </c>
-      <c r="H192" s="8" t="n">
+      <c r="H192" s="7" t="n">
         <v>45505.79166666666</v>
       </c>
-      <c r="I192" s="8" t="n">
+      <c r="I192" s="7" t="n">
         <v>45525.79166666666</v>
       </c>
       <c r="J192" t="inlineStr">
@@ -22368,13 +22350,13 @@
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" s="8" t="n">
+      <c r="G193" s="7" t="n">
         <v>45526.79166666666</v>
       </c>
-      <c r="H193" s="8" t="n">
+      <c r="H193" s="7" t="n">
         <v>45529.79166666666</v>
       </c>
-      <c r="I193" s="8" t="n">
+      <c r="I193" s="7" t="n">
         <v>45529.79166666666</v>
       </c>
       <c r="J193" t="inlineStr">
@@ -22445,13 +22427,13 @@
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" s="8" t="n">
+      <c r="G194" s="7" t="n">
         <v>45528.79166666666</v>
       </c>
-      <c r="H194" s="8" t="n">
+      <c r="H194" s="7" t="n">
         <v>45528.79166666666</v>
       </c>
-      <c r="I194" s="8" t="n">
+      <c r="I194" s="7" t="n">
         <v>45528.79166666666</v>
       </c>
       <c r="J194" t="inlineStr">
@@ -22522,13 +22504,13 @@
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
-      <c r="G195" s="8" t="n">
+      <c r="G195" s="7" t="n">
         <v>45388.79166666666</v>
       </c>
-      <c r="H195" s="8" t="n">
+      <c r="H195" s="7" t="n">
         <v>45388.79166666666</v>
       </c>
-      <c r="I195" s="8" t="n">
+      <c r="I195" s="7" t="n">
         <v>45397.79166666666</v>
       </c>
       <c r="J195" t="inlineStr">
@@ -22601,13 +22583,13 @@
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
-      <c r="G196" s="8" t="n">
+      <c r="G196" s="7" t="n">
         <v>45392.79166666666</v>
       </c>
-      <c r="H196" s="8" t="n">
+      <c r="H196" s="7" t="n">
         <v>45399.79166666666</v>
       </c>
-      <c r="I196" s="8" t="n">
+      <c r="I196" s="7" t="n">
         <v>45404.79166666666</v>
       </c>
       <c r="J196" t="inlineStr">
@@ -22680,13 +22662,13 @@
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
-      <c r="G197" s="8" t="n">
+      <c r="G197" s="7" t="n">
         <v>45397.79166666666</v>
       </c>
-      <c r="H197" s="8" t="n">
+      <c r="H197" s="7" t="n">
         <v>45397.79166666666</v>
       </c>
-      <c r="I197" s="8" t="n">
+      <c r="I197" s="7" t="n">
         <v>45404.79166666666</v>
       </c>
       <c r="J197" t="inlineStr">
@@ -22759,13 +22741,13 @@
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" s="8" t="n">
+      <c r="G198" s="7" t="n">
         <v>45407.79166666666</v>
       </c>
-      <c r="H198" s="8" t="n">
+      <c r="H198" s="7" t="n">
         <v>45407.79166666666</v>
       </c>
-      <c r="I198" s="8" t="n">
+      <c r="I198" s="7" t="n">
         <v>45413.79166666666</v>
       </c>
       <c r="J198" t="inlineStr">
@@ -22836,13 +22818,13 @@
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" s="8" t="n">
+      <c r="G199" s="7" t="n">
         <v>45407.79166666666</v>
       </c>
-      <c r="H199" s="8" t="n">
+      <c r="H199" s="7" t="n">
         <v>45413.79166666666</v>
       </c>
-      <c r="I199" s="8" t="n">
+      <c r="I199" s="7" t="n">
         <v>45413.79166666666</v>
       </c>
       <c r="J199" t="inlineStr">
@@ -22915,13 +22897,13 @@
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
-      <c r="G200" s="8" t="n">
+      <c r="G200" s="7" t="n">
         <v>45693.79166666666</v>
       </c>
-      <c r="H200" s="8" t="n">
+      <c r="H200" s="7" t="n">
         <v>45704.79166666666</v>
       </c>
-      <c r="I200" s="8" t="n">
+      <c r="I200" s="7" t="n">
         <v>45755.44861111111</v>
       </c>
       <c r="J200" t="inlineStr">
@@ -22992,13 +22974,13 @@
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" s="8" t="n">
+      <c r="G201" s="7" t="n">
         <v>45711.79166666666</v>
       </c>
-      <c r="H201" s="8" t="n">
+      <c r="H201" s="7" t="n">
         <v>45712.79166666666</v>
       </c>
-      <c r="I201" s="8" t="n">
+      <c r="I201" s="7" t="n">
         <v>45755.44861111111</v>
       </c>
       <c r="J201" t="inlineStr">
@@ -23073,13 +23055,13 @@
           <t>[Ver. 2.22]</t>
         </is>
       </c>
-      <c r="G202" s="8" t="n">
+      <c r="G202" s="7" t="n">
         <v>45768.79166666666</v>
       </c>
-      <c r="H202" s="8" t="n">
+      <c r="H202" s="7" t="n">
         <v>45770.79166666666</v>
       </c>
-      <c r="I202" s="8" t="n">
+      <c r="I202" s="7" t="n">
         <v>45771.79166666666</v>
       </c>
       <c r="J202" t="inlineStr">
@@ -23150,13 +23132,13 @@
           <t>[Ver.2.14]</t>
         </is>
       </c>
-      <c r="G203" s="8" t="n">
+      <c r="G203" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H203" s="8" t="n">
+      <c r="H203" s="7" t="n">
         <v>45341.79166666666</v>
       </c>
-      <c r="I203" s="8" t="n">
+      <c r="I203" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
       <c r="J203" t="inlineStr">
@@ -23231,13 +23213,13 @@
           <t>[Ver.2.13]</t>
         </is>
       </c>
-      <c r="G204" s="8" t="n">
+      <c r="G204" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="H204" s="8" t="n">
+      <c r="H204" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
-      <c r="I204" s="8" t="n">
+      <c r="I204" s="7" t="n">
         <v>45372.79166666666</v>
       </c>
       <c r="J204" t="inlineStr">
@@ -23312,13 +23294,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G205" s="8" t="n">
+      <c r="G205" s="7" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="H205" s="8" t="n">
+      <c r="H205" s="7" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="I205" s="8" t="n">
+      <c r="I205" s="7" t="n">
         <v>45375.79166666666</v>
       </c>
       <c r="J205" t="inlineStr">
@@ -23393,13 +23375,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G206" s="8" t="n">
+      <c r="G206" s="7" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="H206" s="8" t="n">
+      <c r="H206" s="7" t="n">
         <v>45364.79166666666</v>
       </c>
-      <c r="I206" s="8" t="n">
+      <c r="I206" s="7" t="n">
         <v>45375.79166666666</v>
       </c>
       <c r="J206" t="inlineStr">
@@ -23474,13 +23456,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G207" s="8" t="n">
+      <c r="G207" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="H207" s="8" t="n">
+      <c r="H207" s="7" t="n">
         <v>45361.79166666666</v>
       </c>
-      <c r="I207" s="8" t="n">
+      <c r="I207" s="7" t="n">
         <v>45372.79166666666</v>
       </c>
       <c r="J207" t="inlineStr">
@@ -23555,13 +23537,13 @@
           <t>[Ver. 2.15]</t>
         </is>
       </c>
-      <c r="G208" s="8" t="n">
+      <c r="G208" s="7" t="n">
         <v>45355.79166666666</v>
       </c>
-      <c r="H208" s="8" t="n">
+      <c r="H208" s="7" t="n">
         <v>45375.79166666666</v>
       </c>
-      <c r="I208" s="8" t="n">
+      <c r="I208" s="7" t="n">
         <v>45372.79166666666</v>
       </c>
       <c r="J208" t="inlineStr">
@@ -23608,7 +23590,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S208"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:S208">
+    <sortState ref="A2:R194">
+      <sortCondition descending="1" ref="C1:C158"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -7491,7 +7491,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>183</v>
+        <v>248</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -7500,36 +7500,50 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ticket 304 - Proyecto WAPSA 2024 - 1 - Modificar Proceso Lista despacho</t>
+          <t>Ticket 355 Wapsa - General - Proyecto - Agregar grupos de Ensayo en Wapsa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Agosto - 2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[Ver 2.25]</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>45810.79166666666</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>45873.79166666666</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>45937.57847222222</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WAPSA web</t>
+          <t>Wapsa Web</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>304</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>355</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;1.1 Pesos Lista Despacho		&lt;br&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;	Modicar codigo en el momento que se modifiquen pesos se deben eliminar las leyes y humedades existentes.	&lt;/li&gt;&lt;li&gt;	Modificar UI para consumir nuevo proceso	&lt;/li&gt;&lt;li&gt;	Realizar pruebas	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;1.2 Humedades Lista Despacho		&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;	Modicar codigo en el momento que se modifiquen pesos se deben eliminar las leyes.	&lt;/li&gt;&lt;li&gt;	Modificar UI para consumir nuevo proceso	&lt;/li&gt;&lt;li&gt;	Realizar pruebas	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style="font-weight:bold;"&gt;		&lt;br&gt; &lt;/div&gt;&lt;b&gt;&lt;span&gt;&lt;/span&gt;&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Luis Casas solicita: &lt;/div&gt;&lt;div&gt;En la transmision de leyes de Cotecna e importacion: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;span&gt;- Habilitar 4 columnas de información en el reporte de H2OyLey Callao de Wapsa; grupos (G1,G2,G3,G4) para recibir la data de Cotecna&lt;br&gt;&lt;/span&gt;&lt;div&gt;- Generar el maestro: &amp;quot;Grupos de análisis&amp;quot; para seleccionar a qué grupo pertenece cada analito.&lt;br&gt; &lt;/div&gt;&lt;div&gt;- Actualizar el reporte en Excel de H2OyLey Callao incluyendo los Grupos.&lt;br&gt; &lt;/div&gt;&lt;div&gt;- Habilitar las 4 columnas en el dashboard (HumedadesyLeyes)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;28/05 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se adjunta documento resultante de la reunion &lt;/div&gt;&lt;span&gt;&lt;/span&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -7558,7 +7572,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -7567,12 +7581,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ticket 306 - Proyecto WAPSA 2024 - 1 - Mantenimiento Equipos-Pesajes</t>
+          <t>Ticket 304 - Proyecto WAPSA 2024 - 1 - Modificar Proceso Lista despacho</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7591,12 +7605,12 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Mantenimiento de tablas&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&amp;nbsp;			&lt;/b&gt;&lt;br&gt;&lt;div style=""&gt;&lt;b&gt;1.1 Registro de Equipos 		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;Registro de los equipos	&lt;/li&gt;&lt;li&gt;Configurar cuenta de correo	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;	1.2 Mantenimiento de tablas		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;		Tipos de mantenimiento	&lt;/li&gt;&lt;li&gt;		Tipos de averias	&lt;/li&gt;&lt;li&gt;		Empresas	&lt;/li&gt;&lt;li&gt;		Ubicación	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;Registro de la programación			&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;	2.1 Registro de programación		&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Registro de programación	&lt;/b&gt; &lt;/li&gt;&lt;li&gt;Registro de evidencias	&lt;/li&gt;&lt;li&gt;Envío de la notificación	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;	2.2 Registro de mantenimiento correctivo		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;Registro del evento 	&lt;/li&gt;&lt;li&gt;Registro de las evidencias	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;Reportes			&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;Reporte de programación		&lt;/li&gt;&lt;li&gt;&amp;nbsp;Reporte de Mantenimiento Correctivo		&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;b&gt;&lt;span&gt;&lt;/span&gt;&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;1.1 Pesos Lista Despacho		&lt;br&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;	Modicar codigo en el momento que se modifiquen pesos se deben eliminar las leyes y humedades existentes.	&lt;/li&gt;&lt;li&gt;	Modificar UI para consumir nuevo proceso	&lt;/li&gt;&lt;li&gt;	Realizar pruebas	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;1.2 Humedades Lista Despacho		&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;	Modicar codigo en el momento que se modifiquen pesos se deben eliminar las leyes.	&lt;/li&gt;&lt;li&gt;	Modificar UI para consumir nuevo proceso	&lt;/li&gt;&lt;li&gt;	Realizar pruebas	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style="font-weight:bold;"&gt;		&lt;br&gt; &lt;/div&gt;&lt;b&gt;&lt;span&gt;&lt;/span&gt;&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -7625,7 +7639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -7634,12 +7648,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ticket 310 - Proyecto WAPSA 2024 - 1 - Arribo a Mina y a Callao  con GPS</t>
+          <t>Ticket 306 - Proyecto WAPSA 2024 - 1 - Mantenimiento Equipos-Pesajes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7658,12 +7672,12 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;span&gt;&lt;b&gt;Crear una API			&lt;br&gt;&lt;/b&gt;&lt;/span&gt;&lt;div&gt;&lt;b&gt;	1.1 Crear proceso automatico para leer datos del GPS		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;ul&gt;&lt;li&gt;		Creacion de scripts	&lt;/li&gt;&lt;li&gt;		Desarrollo del codigo con logica	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;	1.2 Modificar el wapsa		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;ul&gt;&lt;li&gt;		Modificar el WAPSA para soportar una lectura del gps o manual	&lt;/li&gt;&lt;li&gt;		Realizar pruebas	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div&gt;			&lt;br&gt; &lt;/div&gt;&lt;div&gt;			&lt;br&gt; &lt;/div&gt;&lt;span&gt;&lt;/span&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Mantenimiento de tablas&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&amp;nbsp;			&lt;/b&gt;&lt;br&gt;&lt;div style=""&gt;&lt;b&gt;1.1 Registro de Equipos 		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;Registro de los equipos	&lt;/li&gt;&lt;li&gt;Configurar cuenta de correo	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;	1.2 Mantenimiento de tablas		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;		Tipos de mantenimiento	&lt;/li&gt;&lt;li&gt;		Tipos de averias	&lt;/li&gt;&lt;li&gt;		Empresas	&lt;/li&gt;&lt;li&gt;		Ubicación	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;Registro de la programación			&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;	2.1 Registro de programación		&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;Registro de programación	&lt;/b&gt; &lt;/li&gt;&lt;li&gt;Registro de evidencias	&lt;/li&gt;&lt;li&gt;Envío de la notificación	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;	2.2 Registro de mantenimiento correctivo		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;Registro del evento 	&lt;/li&gt;&lt;li&gt;Registro de las evidencias	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;b&gt;Reportes			&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div style=""&gt;&lt;ul&gt;&lt;li&gt;Reporte de programación		&lt;/li&gt;&lt;li&gt;&amp;nbsp;Reporte de Mantenimiento Correctivo		&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;b&gt;&lt;span&gt;&lt;/span&gt;&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -7692,7 +7706,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -7701,12 +7715,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ticket 333 - Wapsa - General - Proyecto Wapsa - Rountrip con GPS</t>
+          <t>Ticket 310 - Proyecto WAPSA 2024 - 1 - Arribo a Mina y a Callao  con GPS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -7715,24 +7729,22 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" s="7" t="n">
-        <v>45391.79166666666</v>
-      </c>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>333</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>WAPSA web</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>310</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>&lt;div&gt;10/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Reunion con el proveedor&amp;nbsp;CLS Peru en la cual se concretaron los siguientes puntos: &lt;/div&gt;&lt;div&gt;-En la aplicacion de CLS que le permite a MIna monitorear los vagones via GPS se registrar el Nro de Guia de Remision en el campo conductor, de momento manualmente lo hara el equipo de Edwin Rios MCP. &lt;/div&gt;&lt;div&gt;-El equipo de Edwin registrara la guias desde el Jueves 11/04 hasta el dia lunes&amp;nbsp; para que luego de eso SyC Sistemas podra 15/04 consultar utilizando el API. &lt;/div&gt;&lt;div&gt;-EL dia 15/04 SyC probara haciendo consultas utilizando el API para devolver los datos filtrando por el campo conductor-Guia de remision, &lt;/div&gt;&lt;div&gt;-La proxima reunion sera el dia 18 o 19/04 &lt;/div&gt;&lt;div&gt;-Se concretara una reunion con Wally a posterior para ver internamnete en Wapsa cuales seran las mejoras una vez podamos consultar la informacion correctamnete desde el API &lt;/div&gt;&lt;div&gt;-CLS indico cual es la documentacion que se debe consultar.&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;a href="https://sdk.wialon.com/wiki/en/sidebar/remoteapi/apiref/report/cleanup_result" target=_blank rel="noopener noreferrer"&gt;https://sdk.wialon.com/wiki/en/sidebar/remoteapi/apiref/report/cleanup_result&lt;/a&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Video de la reunion en los adjuntos del Ticket &lt;/div&gt;&lt;div&gt;15/04 Edwin Rios inidca que ya se esta cargando los Numeros de Guias desde Mina &lt;/div&gt;&lt;div&gt;16/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se envia consulta a la Empresa del GPS para consultar sobre como obtener los ID's para obtener lueo los reportes&amp;nbsp; &lt;/div&gt;&lt;div&gt;23/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;CLS responde mail enviando las credenciales de acceso &lt;/div&gt;&lt;div&gt;29/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se envia consulta a CLS porque no se puede obtener la informacion de los puntos del GPS ,&amp;nbsp; se solicita reunion &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;span&gt;&lt;b&gt;Crear una API			&lt;br&gt;&lt;/b&gt;&lt;/span&gt;&lt;div&gt;&lt;b&gt;	1.1 Crear proceso automatico para leer datos del GPS		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;ul&gt;&lt;li&gt;		Creacion de scripts	&lt;/li&gt;&lt;li&gt;		Desarrollo del codigo con logica	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;	1.2 Modificar el wapsa		&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;ul&gt;&lt;li&gt;		Modificar el WAPSA para soportar una lectura del gps o manual	&lt;/li&gt;&lt;li&gt;		Realizar pruebas	&lt;/li&gt; &lt;/ul&gt; &lt;/div&gt;&lt;div&gt;			&lt;br&gt; &lt;/div&gt;&lt;div&gt;			&lt;br&gt; &lt;/div&gt;&lt;span&gt;&lt;/span&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -7761,7 +7773,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -7770,50 +7782,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ticket 355 Wapsa - General - Proyecto - Agregar grupos de Ensayo en Wapsa</t>
+          <t>Ticket 333 - Wapsa - General - Proyecto Wapsa - Rountrip con GPS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Agosto - 2025</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[Ver 2.25]</t>
-        </is>
-      </c>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" s="7" t="n">
-        <v>45810.79166666666</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>45873.79166666666</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>45937.57847222222</v>
-      </c>
+        <v>45391.79166666666</v>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>355</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
+      <c r="K8" t="n">
+        <v>333</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Luis Casas solicita: &lt;/div&gt;&lt;div&gt;En la transmision de leyes de Cotecna e importacion: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;span&gt;- Habilitar 4 columnas de información en el reporte de H2OyLey Callao de Wapsa; grupos (G1,G2,G3,G4) para recibir la data de Cotecna&lt;br&gt;&lt;/span&gt;&lt;div&gt;- Generar el maestro: &amp;quot;Grupos de análisis&amp;quot; para seleccionar a qué grupo pertenece cada analito.&lt;br&gt; &lt;/div&gt;&lt;div&gt;- Actualizar el reporte en Excel de H2OyLey Callao incluyendo los Grupos.&lt;br&gt; &lt;/div&gt;&lt;div&gt;- Habilitar las 4 columnas en el dashboard (HumedadesyLeyes)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;28/05 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se adjunta documento resultante de la reunion &lt;/div&gt;&lt;span&gt;&lt;/span&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;10/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Reunion con el proveedor&amp;nbsp;CLS Peru en la cual se concretaron los siguientes puntos: &lt;/div&gt;&lt;div&gt;-En la aplicacion de CLS que le permite a MIna monitorear los vagones via GPS se registrar el Nro de Guia de Remision en el campo conductor, de momento manualmente lo hara el equipo de Edwin Rios MCP. &lt;/div&gt;&lt;div&gt;-El equipo de Edwin registrara la guias desde el Jueves 11/04 hasta el dia lunes&amp;nbsp; para que luego de eso SyC Sistemas podra 15/04 consultar utilizando el API. &lt;/div&gt;&lt;div&gt;-EL dia 15/04 SyC probara haciendo consultas utilizando el API para devolver los datos filtrando por el campo conductor-Guia de remision, &lt;/div&gt;&lt;div&gt;-La proxima reunion sera el dia 18 o 19/04 &lt;/div&gt;&lt;div&gt;-Se concretara una reunion con Wally a posterior para ver internamnete en Wapsa cuales seran las mejoras una vez podamos consultar la informacion correctamnete desde el API &lt;/div&gt;&lt;div&gt;-CLS indico cual es la documentacion que se debe consultar.&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;a href="https://sdk.wialon.com/wiki/en/sidebar/remoteapi/apiref/report/cleanup_result" target=_blank rel="noopener noreferrer"&gt;https://sdk.wialon.com/wiki/en/sidebar/remoteapi/apiref/report/cleanup_result&lt;/a&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Video de la reunion en los adjuntos del Ticket &lt;/div&gt;&lt;div&gt;15/04 Edwin Rios inidca que ya se esta cargando los Numeros de Guias desde Mina &lt;/div&gt;&lt;div&gt;16/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se envia consulta a la Empresa del GPS para consultar sobre como obtener los ID's para obtener lueo los reportes&amp;nbsp; &lt;/div&gt;&lt;div&gt;23/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;CLS responde mail enviando las credenciales de acceso &lt;/div&gt;&lt;div&gt;29/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se envia consulta a CLS porque no se puede obtener la informacion de los puntos del GPS ,&amp;nbsp; se solicita reunion &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -8520,15 +8520,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>En Proceso firmas</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" s="7" t="n">
         <v>46073.42986111111</v>
       </c>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
+      <c r="H17" s="7" t="n">
+        <v>46074.79166666666</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>46106.79166666666</v>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
@@ -10172,7 +10176,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -10181,7 +10185,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ticket 452 - Guia Remisión Electronica nuevos casos</t>
+          <t>Ticket 453 - Wapsa - Envio datos WAPSA-SAP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -10191,13 +10195,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>[Ver 2.25]</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>45930.79166666666</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>45937.45138888889</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>45937.57986111111</v>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10205,12 +10219,16 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>452</v>
-      </c>
-      <c r="M38" t="inlineStr"/>
+        <v>453</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/225fb9c5-e533-4606-9111-042ef763c56c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Mina:&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/63d719b2-06d8-4c83-884f-50e2ce343ba6?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/392f0895-d410-422e-9107-e47dbd4df527?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d71da09a-4188-4259-a9d4-7cafa283440e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Callao :&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/20d9850d-70fe-49d7-b2f3-9e2b8b1ba05c?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/f1c8ff88-3eec-49b6-9adc-8d745baf35d4?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Ejecución Manual Envió a SAP:&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/26feb9be-d0fd-4d53-9fc2-39f8c872e02e?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -10239,7 +10257,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -10248,7 +10266,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ticket 453 - Wapsa - Envio datos WAPSA-SAP</t>
+          <t>Ticket 471 - Wapsa - SAP Envio de datos</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -10258,22 +10276,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[Ver 2.25]</t>
+          <t>[Ver. 2.27]; [Ver. 2.28]</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>45930.79166666666</v>
+        <v>45991.79166666666</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>45937.45138888889</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>45937.57986111111</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -10282,7 +10300,7 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -10291,7 +10309,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Mina:&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/63d719b2-06d8-4c83-884f-50e2ce343ba6?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/392f0895-d410-422e-9107-e47dbd4df527?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d71da09a-4188-4259-a9d4-7cafa283440e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Callao :&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/20d9850d-70fe-49d7-b2f3-9e2b8b1ba05c?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/f1c8ff88-3eec-49b6-9adc-8d745baf35d4?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Ejecución Manual Envió a SAP:&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/26feb9be-d0fd-4d53-9fc2-39f8c872e02e?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/6fd9a9f1-f4d3-41d8-a8b0-630480829703?fileName=image.png" alt=Image style="box-sizing:border-box;max-width:100%;align-self:center;"&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -10320,7 +10338,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -10329,23 +10347,29 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ticket 454 - Guia Remisión Electronica nuevos casos</t>
+          <t>Ticket 455 - SAP FASE COMPLEMENTARIA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Diciembre - 2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Resuelto</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
+      <c r="G40" s="7" t="n">
+        <v>45931.79166666666</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>46008.79166666666</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>46008.79166666666</v>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10353,12 +10377,16 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>454</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
+        <v>455</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/27469beb-ea0f-4125-8ece-8774b4e8b960?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/6fd9a9f1-f4d3-41d8-a8b0-630480829703?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -10387,7 +10415,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>507</v>
+        <v>455</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -10396,28 +10424,30 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ticket 471 - Wapsa - SAP Envio de datos</t>
+          <t>Ticket 444- Wapsa - Mina - Pesaje - Lectura del peso utilizando api de PI Server</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Agosto - 2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[Ver. 2.27]; [Ver. 2.28]</t>
+          <t>[Ver 2.24]</t>
         </is>
       </c>
       <c r="G41" s="7" t="n">
-        <v>45991.79166666666</v>
-      </c>
-      <c r="H41" s="7" t="n"/>
+        <v>45854.72638888889</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>45854.72638888889</v>
+      </c>
       <c r="I41" s="7" t="n"/>
       <c r="J41" t="inlineStr">
         <is>
@@ -10426,16 +10456,16 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>471</v>
+        <v>444</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/6fd9a9f1-f4d3-41d8-a8b0-630480829703?fileName=image.png" alt=Image style="box-sizing:border-box;max-width:100%;align-self:center;"&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;span&gt;Detalles de la API:&lt;br&gt;&lt;/span&gt;&lt;div&gt;Endpoint: http://10.251.3.51:8081/last_value&lt;br&gt; &lt;/div&gt;&lt;div&gt;Método: POST&lt;br&gt; &lt;/div&gt;&lt;div&gt;Body :&lt;br&gt; &lt;/div&gt;&lt;div&gt;{&lt;br&gt; &lt;/div&gt;&lt;div&gt;&amp;nbsp; &amp;quot;tag&amp;quot;: &amp;quot;PL:245WIT0064_TON_DCS&amp;quot;&lt;br&gt; &lt;/div&gt;&lt;div&gt;}&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Credenciales (Basic Auth):&lt;br&gt; &lt;/div&gt;&lt;div&gt;Usuario: user_wapsa01&lt;br&gt; &lt;/div&gt;&lt;div&gt;Contraseña: GkXpLZ&amp;amp;d66LNAGGPyeS5&amp;amp;m&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Servidor: 10.251.3.51&lt;br&gt; &lt;/div&gt;&lt;div&gt;Puerto: 8081&lt;br&gt; &lt;/div&gt;&lt;span&gt;&lt;/span&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -10450,7 +10480,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -10464,7 +10494,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -10473,29 +10503,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ticket 455 - SAP FASE COMPLEMENTARIA</t>
+          <t>Ticket 452 - Guia Remisión Electronica nuevos casos</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2025</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Resuelto</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" s="7" t="n">
-        <v>45931.79166666666</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>46008.79166666666</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>46008.79166666666</v>
-      </c>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10503,16 +10527,12 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>455</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/6fd9a9f1-f4d3-41d8-a8b0-630480829703?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/225fb9c5-e533-4606-9111-042ef763c56c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -10541,7 +10561,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -10550,30 +10570,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ticket 444- Wapsa - Mina - Pesaje - Lectura del peso utilizando api de PI Server</t>
+          <t>Ticket 454 - Guia Remisión Electronica nuevos casos</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Agosto - 2025</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>[Ver 2.24]</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>45854.72638888889</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>45854.72638888889</v>
-      </c>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
       <c r="I43" s="7" t="n"/>
       <c r="J43" t="inlineStr">
         <is>
@@ -10582,16 +10594,12 @@
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>444</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;span&gt;Detalles de la API:&lt;br&gt;&lt;/span&gt;&lt;div&gt;Endpoint: http://10.251.3.51:8081/last_value&lt;br&gt; &lt;/div&gt;&lt;div&gt;Método: POST&lt;br&gt; &lt;/div&gt;&lt;div&gt;Body :&lt;br&gt; &lt;/div&gt;&lt;div&gt;{&lt;br&gt; &lt;/div&gt;&lt;div&gt;&amp;nbsp; &amp;quot;tag&amp;quot;: &amp;quot;PL:245WIT0064_TON_DCS&amp;quot;&lt;br&gt; &lt;/div&gt;&lt;div&gt;}&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Credenciales (Basic Auth):&lt;br&gt; &lt;/div&gt;&lt;div&gt;Usuario: user_wapsa01&lt;br&gt; &lt;/div&gt;&lt;div&gt;Contraseña: GkXpLZ&amp;amp;d66LNAGGPyeS5&amp;amp;m&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Servidor: 10.251.3.51&lt;br&gt; &lt;/div&gt;&lt;div&gt;Puerto: 8081&lt;br&gt; &lt;/div&gt;&lt;span&gt;&lt;/span&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/27469beb-ea0f-4125-8ece-8774b4e8b960?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -10606,7 +10614,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -16095,7 +16103,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>340</v>
+        <v>524</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -16104,7 +16112,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ticket 384 - Wapsa - General - Configuracion -  Crear Modulo para guardar las plantilla de importacion de datos</t>
+          <t>Ticket 483 - Wapsa - Lista de Despacho - Error de formato de fechas al exportar detalle de despachos de pesos de una IE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16114,30 +16122,38 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>[Ver. 2.28]; SLA</t>
+        </is>
+      </c>
       <c r="G113" s="7" t="n">
-        <v>45951.79166666666</v>
-      </c>
-      <c r="H113" s="7" t="n"/>
-      <c r="I113" s="7" t="n"/>
+        <v>46089.79166666666</v>
+      </c>
+      <c r="H113" s="7" t="n">
+        <v>46089.79166666666</v>
+      </c>
+      <c r="I113" s="7" t="n">
+        <v>46089.79166666666</v>
+      </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WapsaWeb</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
-        <v>384</v>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
+        <v>483</v>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Al importar información como Guías/Pesos a una IE de la Lista de Despacho el formato de fecha esta errado, WAPSA interpreta erróneamente la info y graba la fecha con un formato distinto al del Excel de importación, favor corregir ya que no esta quedando grabada correctamente la información en WAPSA.&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -16145,7 +16161,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Omisión del usuario</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -16164,7 +16180,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>377</v>
+        <v>525</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -16173,7 +16189,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ticket 402 - Wapsa - Callao - E. Shipments - Cuando ocurre un bloqueo al obtener data del Trader Wapsa no muestra el error</t>
+          <t>Ticket 484 - Wapsa - Asignacion - No llegan los mails de aprobación de Asignacion de Ruma/IE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16183,36 +16199,38 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" s="7" t="n">
-        <v>45642.79166666666</v>
+        <v>46094.54930555556</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>45642.79166666666</v>
-      </c>
-      <c r="I114" s="7" t="n"/>
+        <v>46094.54930555556</v>
+      </c>
+      <c r="I114" s="7" t="n">
+        <v>46097.30972222222</v>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>SLA</t>
+        </is>
+      </c>
       <c r="L114" t="n">
-        <v>402</v>
+        <v>484</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Cuando se obtienen datos desde el Trader y se genrea algun tipo de error de bloqueo o comunicacion entra ambas Bd's no se muestra: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/c3f5d344-76e8-4365-9a52-10b27bb70854?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -16220,12 +16238,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>Servidor MCP</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R114" t="n">
@@ -16239,7 +16257,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>450</v>
+        <v>526</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -16248,7 +16266,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ticket 442 - Wapsa - Stock Callao - Error en calculo de TMH en listado detalle por día</t>
+          <t>Ticket 485 - WAPSA - Ajuste Final no deja registrar debido a validacion</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16263,24 +16281,24 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>[Ver 2.24]</t>
+          <t>[Ver. 2.28]</t>
         </is>
       </c>
       <c r="G115" s="7" t="n">
-        <v>45845.25347222222</v>
+        <v>46096.71458333333</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>45845.79166666666</v>
+        <v>46096.71458333333</v>
       </c>
       <c r="I115" s="7" t="n"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WAPSA</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
-        <v>442</v>
+        <v>485</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -16289,11 +16307,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;p style="margin:0cm;font-size:11pt;font-family:Calibri, sans-serif;"&gt;Este ticket tiene como objetivo atender el requerimiento de
-Diego Cárdenas el cual ha detecto que se debe cambiar la fecha que utiliza el
-Wapsa para obtener el listado de stock por día, ahora debe utilizar la fecha de
-proceso según calendario; para que los valores de TMH cuadren correctamente con
-la de otros reportes. &lt;/p&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;He registrado el ultimo movimiento de esa ruma a las 23:00 hrs del 14/03, el ajuste lo estoy poniendo como 14/03 23:59, por que si le pongo 15/03 que fue en realidad la operación me sale otro error que dice que la fecha no puede ser posterior a la fecha de resumen&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/9970cbf3-cd07-41b8-8c16-d3ff09d6b2f6?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -16308,7 +16322,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -16322,7 +16336,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -16331,7 +16345,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ticket 476 - Wapsa -Varios - Mejora Listado para elegir vagones en Arribo, Entrega y Salida</t>
+          <t>Ticket 486 - Wapsa - Ajuste Mensual - Muestra erroneamente los ingresos de la ruma R26-001</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16341,34 +16355,36 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Resuelto</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>[Ver. 4.29]</t>
-        </is>
-      </c>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" s="7" t="n">
-        <v>46047.79166666666</v>
+        <v>46097.56319444445</v>
       </c>
       <c r="H116" s="7" t="n">
-        <v>46104.26111111111</v>
-      </c>
-      <c r="I116" s="7" t="n"/>
+        <v>46097.56319444445</v>
+      </c>
+      <c r="I116" s="7" t="n">
+        <v>46097.56319444445</v>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WAPSA Web</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
-        <v>476</v>
-      </c>
-      <c r="M116" t="inlineStr"/>
+        <v>486</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/8562dbaa-6874-4c02-b55e-12a8ad13591f?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/a6f748b8-2d6a-423d-b875-20010a0b164e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Solución: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;El usuario no recordo que no esta contemplado en el lógica moviemientos internos por lo que lo cambio a junta y todo funciono como lo esperado &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -16378,7 +16394,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Error del usuario</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -16397,7 +16413,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -16406,7 +16422,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ticket 478 - Wapsa - Configuracion - Restringir que no se puede crear un hora cierre de lote diferente a las 06:59</t>
+          <t>Ticket 478 - Spike - Wapsa  - Lista de Dspachos - Documentar como se generan las GRE's para Embarques</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16416,26 +16432,14 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Resuelto</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>[Ver. 2.29]</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="n">
-        <v>46050.79166666666</v>
-      </c>
-      <c r="H117" s="7" t="n">
-        <v>46062.46458333333</v>
-      </c>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" s="7" t="n"/>
+      <c r="H117" s="7" t="n"/>
       <c r="I117" s="7" t="n"/>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
         <v>478</v>
@@ -16451,16 +16455,8 @@
           <t>Nuevo</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>S&amp;C Sistemas</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>No implica estabilización</t>
-        </is>
-      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
       <c r="R117" t="n">
         <v>161</v>
       </c>
@@ -16472,7 +16468,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>522</v>
+        <v>362</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -16481,43 +16477,37 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ticket 482 - Wapsa - Lista de Despacho - No muestra la informacion del campo Almacen vacíos al ver la IE</t>
+          <t>Ticket 397 - Wapsa - Callao - Evidence Of Shipments - Evidence of Shipment nuevo caso NC</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Marzo - 2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Resuelto</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>[Ver. 2.28]; SLA</t>
-        </is>
-      </c>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" s="7" t="n">
-        <v>46090.20833333334</v>
+        <v>45725.79166666666</v>
       </c>
       <c r="H118" s="7" t="n">
-        <v>46090.33333333334</v>
-      </c>
-      <c r="I118" s="7" t="n"/>
+        <v>45725.79166666666</v>
+      </c>
+      <c r="I118" s="7" t="n">
+        <v>45725.79166666666</v>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>SLA</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
-        <v>482</v>
+        <v>397</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -16526,7 +16516,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/0caa4914-6dfb-43dc-acba-dc8d7e950b43?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Corregido siguiente pase &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Se requiere considerar nuevo caso que viene de la vista del Trader para ser consumido por el modulo del wapsa Evidence of shipment.&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Nicolas se hará cargo de la modificación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Luego tenemos que importar y ver esta operación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -16541,7 +16531,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R118" t="n">
@@ -16555,7 +16545,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>524</v>
+        <v>234</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -16564,57 +16554,63 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ticket 483 - Wapsa - Lista de Despacho - Error de formato de fechas al exportar detalle de despachos de pesos de una IE</t>
+          <t>Ticket 344 - Wapsa - Callao - Lista Despacho - Alerta despachos pesos 0 no manda datos sobre las IE's</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Junio 2024</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Resuelto</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>[Ver. 2.28]; SLA</t>
-        </is>
-      </c>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" s="7" t="n">
-        <v>46089.79166666666</v>
-      </c>
-      <c r="H119" s="7" t="n"/>
-      <c r="I119" s="7" t="n"/>
+        <v>45410.79166666666</v>
+      </c>
+      <c r="H119" s="7" t="n">
+        <v>45454.79166666666</v>
+      </c>
+      <c r="I119" s="7" t="n">
+        <v>45460.79166666666</v>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>WapsaWeb</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>109586</v>
+      </c>
       <c r="L119" t="n">
-        <v>483</v>
-      </c>
-      <c r="M119" t="inlineStr"/>
+        <v>344</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Al importar información como Guías/Pesos a una IE de la Lista de Despacho el formato de fecha esta errado, WAPSA interpreta erróneamente la info y graba la fecha con un formato distinto al del Excel de importación, favor corregir ya que no esta quedando grabada correctamente la información en WAPSA.&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/83c9d948-689e-4ab1-88be-3336f3a5a233?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;la IE en cuestion no ha cumplido los 7 dias de registrada hasta la fecha y pos eso no sale en el listado &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/12b0b23a-f9f8-4862-ba1c-6120f6c4bdf5?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;04/06&amp;nbsp;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se corrige listado para que filtre correctamnete utilizando los lotes actual y el anterior. &lt;/div&gt;&lt;div&gt;Se enviara como tikcet. Se envia un formato para firma de AM &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;AM Envia docuemento firmado. Se adjunta &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Wally solicita en reunion del 11/06, que el listado incluya un lote mas hacia atras del tiempo. Se haran los cambios. S emueve Ticket a estado en Desarrollo &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se agrega cambio al script y se envia a TICA 12/06/2023 13:24 pm &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Repetitivo-en-proceso</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Omisión del usuario</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R119" t="n">
@@ -16628,7 +16624,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>525</v>
+        <v>255</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -16637,12 +16633,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ticket 484 - Wapsa - Asignacion - No llegan los mails de aprobación de Asignacion de Ruma/IE</t>
+          <t>Ticket 358 - Wapsa - General - Informacion sobre propuesta de mejoras para los Pases a produccion, tickets y ambientes de pruebas</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Junio 2024</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -16652,33 +16648,33 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" s="7" t="n">
-        <v>46094.54930555556</v>
+        <v>45453.79166666666</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>46094.54930555556</v>
+        <v>45454.79166666666</v>
       </c>
       <c r="I120" s="7" t="n">
-        <v>46097.30972222222</v>
+        <v>45454.79166666666</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>SLA</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
-        <v>484</v>
+        <v>358</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Nicolas solicitar completar infromacion resulotante de uan reunion con Chnalco sobre propuestas de mejoras acerca de los Pases a produccion, tickets y ambientes de pruebas &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/5ee0bb74-9fda-4771-adab-e78824534323?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Reunion con NV y DM para revisar propuestas de mejoras. &lt;/div&gt;&lt;div&gt;12/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se envian propuestas a evaluacion de NV &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -16686,7 +16682,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Servidor MCP</t>
+          <t>Externos</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -16705,7 +16701,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>526</v>
+        <v>268</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -16714,48 +16710,46 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ticket 485 - WAPSA - Ajuste Final no deja registrar debido a validacion</t>
+          <t>Ticket 361 - Wapsa - Callao - Ajuste Mensual - Problema en  ajuste en línea R24-013 - JUNIO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Junio 2024</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Resuelto</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>[Ver. 2.28]</t>
-        </is>
-      </c>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" s="7" t="n">
-        <v>46096.71458333333</v>
+        <v>45466.79166666666</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>46096.71458333333</v>
-      </c>
-      <c r="I121" s="7" t="n"/>
+        <v>45466.79166666666</v>
+      </c>
+      <c r="I121" s="7" t="n">
+        <v>45466.79166666666</v>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>WAPSA</t>
+          <t>Wapsa Web</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
-        <v>485</v>
+        <v>361</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;He registrado el ultimo movimiento de esa ruma a las 23:00 hrs del 14/03, el ajuste lo estoy poniendo como 14/03 23:59, por que si le pongo 15/03 que fue en realidad la operación me sale otro error que dice que la fecha no puede ser posterior a la fecha de resumen&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/9970cbf3-cd07-41b8-8c16-d3ff09d6b2f6?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Diego Cardenas reporta&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/b7318f47-b451-4aa8-b5d8-729247a0d339?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;24/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se detecta un repeso total duplicado: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/0b3e7192-c054-4a41-a921-7f64bd67bee5?fileName=WhatsApp%20Image%202024-06-24%20at%2016.49.35.jpeg" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;&amp;nbsp;Responde via mail &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/51ef8424-2061-4f19-9ade-d42b9a5351cf?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -16765,12 +16759,12 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Error del usuario</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R121" t="n">
@@ -16784,7 +16778,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>527</v>
+        <v>426</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -16793,12 +16787,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ticket 486 - Wapsa - Ajuste Mensual - Muestra erroneamente los ingresos de la ruma R26-001</t>
+          <t>Ticket 430 - Wapsa - Mina -  C.Stock - Email de advertencia de carga de Stock debe inidcar faltante sobre al dia Chinalco inmediato anterior</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Junio - 2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -16808,31 +16802,33 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" s="7" t="n">
-        <v>46097.56319444445</v>
+        <v>45761.79166666666</v>
       </c>
       <c r="H122" s="7" t="n">
-        <v>46097.56319444445</v>
+        <v>45769.79166666666</v>
       </c>
       <c r="I122" s="7" t="n">
-        <v>46097.56319444445</v>
+        <v>45809.79166666666</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>WAPSA Web</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>135966</v>
+      </c>
       <c r="L122" t="n">
-        <v>486</v>
+        <v>430</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/a6f748b8-2d6a-423d-b875-20010a0b164e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Solución: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;El usuario no recordo que no esta contemplado en el lógica moviemientos internos por lo que lo cambio a junta y todo funciono como lo esperado &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Carlos Zenteno solicita: &lt;/div&gt;&lt;div&gt;El mail de Faltante Stock Mina debe indicar que falta por cargar Stock del dia Chinalco inmediato anterior y no del actual.&lt;br&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -16842,7 +16838,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -16861,7 +16857,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>528</v>
+        <v>433</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -16870,23 +16866,39 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ticket 478 - Spike - Wapsa  - Lista de Dspachos - Documentar como se generan las GRE's para Embarques</t>
+          <t>Ticket 432- Wapsa - Mina - Despacho - Se muestra duplicado un vagón porque tiene dos aprobaciones de dif de tara del supervisor en curso</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>WAPSA\Sprint - Junio - 2025</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" s="7" t="n"/>
-      <c r="H123" s="7" t="n"/>
-      <c r="I123" s="7" t="n"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+      <c r="G123" s="7" t="n">
+        <v>45747.79166666666</v>
+      </c>
+      <c r="H123" s="7" t="n">
+        <v>45764.39930555555</v>
+      </c>
+      <c r="I123" s="7" t="n">
+        <v>45810.79166666666</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Wasa Web</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>135966</v>
+      </c>
       <c r="L123" t="n">
-        <v>478</v>
+        <v>432</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -16899,7 +16911,11 @@
           <t>Nuevo</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Error del usuario</t>
+        </is>
+      </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="n">
         <v>161</v>
@@ -16912,7 +16928,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>362</v>
+        <v>437</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -16921,12 +16937,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ticket 397 - Wapsa - Callao - Evidence Of Shipments - Evidence of Shipment nuevo caso NC</t>
+          <t>Ticket 435 - Wapsa - Error Asignacion Callao no permite asignar</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2025</t>
+          <t>WAPSA\Sprint - Junio - 2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -16936,31 +16952,31 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" s="7" t="n">
-        <v>45725.79166666666</v>
+        <v>45815.29375</v>
       </c>
       <c r="H124" s="7" t="n">
-        <v>45725.79166666666</v>
+        <v>45815.37708333333</v>
       </c>
       <c r="I124" s="7" t="n">
-        <v>45725.79166666666</v>
+        <v>45822.4375</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WAPSA</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Se requiere considerar nuevo caso que viene de la vista del Trader para ser consumido por el modulo del wapsa Evidence of shipment.&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Nicolas se hará cargo de la modificación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Luego tenemos que importar y ver esta operación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Error no se puede asignar &amp;quot;T018-0030057&amp;quot; esta guia debido a que el registro en el &amp;quot;Pesaje&amp;quot; no tiene &amp;quot;Producto&amp;quot; asignado debido al sistema &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mandar un script para actualizar el idproducto del registro y permita Asignar. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -16970,12 +16986,12 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R124" t="n">
@@ -16989,7 +17005,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>234</v>
+        <v>440</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -16998,63 +17014,61 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ticket 344 - Wapsa - Callao - Lista Despacho - Alerta despachos pesos 0 no manda datos sobre las IE's</t>
+          <t>Ticket 436 - Implementar nuevo caso GRE "Otros"</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio 2024</t>
+          <t>WAPSA\Sprint - Junio - 2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>Resuelto</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" s="7" t="n">
-        <v>45410.79166666666</v>
+        <v>45813.79166666666</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>45454.79166666666</v>
+        <v>45818.33819444444</v>
       </c>
       <c r="I125" s="7" t="n">
-        <v>45460.79166666666</v>
+        <v>45832.42916666667</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K125" t="n">
-        <v>109586</v>
-      </c>
+          <t>External API</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
-        <v>344</v>
+        <v>436</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/83c9d948-689e-4ab1-88be-3336f3a5a233?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;la IE en cuestion no ha cumplido los 7 dias de registrada hasta la fecha y pos eso no sale en el listado &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/12b0b23a-f9f8-4862-ba1c-6120f6c4bdf5?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;04/06&amp;nbsp;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se corrige listado para que filtre correctamnete utilizando los lotes actual y el anterior. &lt;/div&gt;&lt;div&gt;Se enviara como tikcet. Se envia un formato para firma de AM &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;AM Envia docuemento firmado. Se adjunta &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Wally solicita en reunion del 11/06, que el listado incluya un lote mas hacia atras del tiempo. Se haran los cambios. S emueve Ticket a estado en Desarrollo &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se agrega cambio al script y se envia a TICA 12/06/2023 13:24 pm &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El usuario requiere implementar nuevo caso para las GRE &amp;quot;Otros&amp;quot; que será generado por impala via &amp;quot;API&amp;quot; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se implementa código para soportar el caso &amp;quot;Otros&amp;quot; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Repetitivo-en-proceso</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R125" t="n">
@@ -17068,7 +17082,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>255</v>
+        <v>443</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -17077,12 +17091,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ticket 358 - Wapsa - General - Informacion sobre propuesta de mejoras para los Pases a produccion, tickets y ambientes de pruebas</t>
+          <t>Ticket 439 - Wapsa - Ajuste Mensual - El Reporte excluya del historico de rumas aquellas involucradas en Mezcla y Junta simultánemente</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio 2024</t>
+          <t>WAPSA\Sprint - Junio - 2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -17092,33 +17106,29 @@
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" s="7" t="n">
-        <v>45453.79166666666</v>
+        <v>45820.51458333333</v>
       </c>
       <c r="H126" s="7" t="n">
-        <v>45454.79166666666</v>
+        <v>45820.51458333333</v>
       </c>
       <c r="I126" s="7" t="n">
-        <v>45454.79166666666</v>
+        <v>45827.79166666666</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>Wapsa</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
-        <v>358</v>
+        <v>439</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Nicolas solicitar completar infromacion resulotante de uan reunion con Chnalco sobre propuestas de mejoras acerca de los Pases a produccion, tickets y ambientes de pruebas &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/5ee0bb74-9fda-4771-adab-e78824534323?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Reunion con NV y DM para revisar propuestas de mejoras. &lt;/div&gt;&lt;div&gt;12/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se envian propuestas a evaluacion de NV &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -17126,12 +17136,12 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Externos</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R126" t="n">
@@ -17145,7 +17155,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>268</v>
+        <v>446</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -17154,12 +17164,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ticket 361 - Wapsa - Callao - Ajuste Mensual - Problema en  ajuste en línea R24-013 - JUNIO</t>
+          <t>Ticket 441- Wapsa - Mina - Stock - Revisión Lentitud Listado</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio 2024</t>
+          <t>WAPSA\Sprint - Julio - 2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -17167,16 +17177,18 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>[Ver 2.24]</t>
+        </is>
+      </c>
       <c r="G127" s="7" t="n">
-        <v>45466.79166666666</v>
+        <v>45851.79166666666</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>45466.79166666666</v>
-      </c>
-      <c r="I127" s="7" t="n">
-        <v>45466.79166666666</v>
-      </c>
+        <v>45859.42916666667</v>
+      </c>
+      <c r="I127" s="7" t="n"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -17184,18 +17196,14 @@
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
-        <v>361</v>
+        <v>441</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Diego Cardenas reporta&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/b7318f47-b451-4aa8-b5d8-729247a0d339?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;24/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se detecta un repeso total duplicado: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/0b3e7192-c054-4a41-a921-7f64bd67bee5?fileName=WhatsApp%20Image%202024-06-24%20at%2016.49.35.jpeg" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;&amp;nbsp;Responde via mail &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/51ef8424-2061-4f19-9ade-d42b9a5351cf?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -17203,12 +17211,12 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R127" t="n">
@@ -17222,7 +17230,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -17231,12 +17239,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ticket 430 - Wapsa - Mina -  C.Stock - Email de advertencia de carga de Stock debe inidcar faltante sobre al dia Chinalco inmediato anterior</t>
+          <t>Ticket 443 - Error al listar vagones en arribo mina en el detalle</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio - 2025</t>
+          <t>WAPSA\Sprint - Julio - 2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -17244,26 +17252,28 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>[Ver 2.24]</t>
+        </is>
+      </c>
       <c r="G128" s="7" t="n">
-        <v>45761.79166666666</v>
+        <v>45856.60833333333</v>
       </c>
       <c r="H128" s="7" t="n">
-        <v>45769.79166666666</v>
+        <v>45856.60833333333</v>
       </c>
       <c r="I128" s="7" t="n">
-        <v>45809.79166666666</v>
+        <v>45859.375</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K128" t="n">
-        <v>135966</v>
-      </c>
+          <t>WAPSA</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -17272,7 +17282,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Carlos Zenteno solicita: &lt;/div&gt;&lt;div&gt;El mail de Faltante Stock Mina debe indicar que falta por cargar Stock del dia Chinalco inmediato anterior y no del actual.&lt;br&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El usuario detecto que al guardar unos de los vagones en el arribo mina se ve triplicado en el detalle&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/4b704854-c497-4128-89b2-cf06ce05fdcc?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Esto es ocasiado porque el SP que se encarga de mostrar el detalle de los vagones no esta filtrando correctamente por las guias activas por lo que se ven esas dos guías demás &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;SP a modificar:&amp;nbsp;&lt;span style="font-weight:400;display:inline !important;"&gt;[dp].[DP_OrdenTrabajoArriboDetalle_Paginado_pa]&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;span style="font-weight:400;display:inline !important;"&gt;&lt;br&gt;&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;span style="font-weight:400;display:inline !important;"&gt;Agregar en la condicional &amp;quot;Dg.IdEstado = 1&amp;quot;&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;span style="font-weight:400;display:inline !important;"&gt;&lt;br&gt;&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;span style="font-weight:400;display:inline !important;"&gt;&lt;br&gt;&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -17282,7 +17292,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -17301,7 +17311,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>433</v>
+        <v>254</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -17310,12 +17320,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ticket 432- Wapsa - Mina - Despacho - Se muestra duplicado un vagón porque tiene dos aprobaciones de dif de tara del supervisor en curso</t>
+          <t>Ticket 357 - Wapsa BI - General - Revisar datos del Reporte de Leyes del BI para los meses de Mayo y Junio</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio - 2025</t>
+          <t>WAPSA\Sprint - Julio - 2024</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -17325,42 +17335,50 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" s="7" t="n">
-        <v>45747.79166666666</v>
+        <v>45453.79166666666</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>45764.39930555555</v>
+        <v>45453.79166666666</v>
       </c>
       <c r="I129" s="7" t="n">
-        <v>45810.79166666666</v>
+        <v>45460.79166666666</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Wasa Web</t>
+          <t>Wapsa BI</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>135966</v>
+        <v>109586</v>
       </c>
       <c r="L129" t="n">
-        <v>432</v>
+        <v>357</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Luis Casas indica en la reunion de 11/06 que el reporte de Mayo no le muestra informacion y para Junio le faltan datos de leyes sobre algunas guias. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;12/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; &lt;/div&gt;&lt;div&gt;Se revisa Mayo y Junio y no se muestra la informacion completa porque el script filtra solo por Guias en estado 1 y debe hacerlo para 1 y 2 (preasignado y con Peso Bruto). &lt;/div&gt;&lt;div&gt;Se corrige scripit en BI &lt;/div&gt;&lt;div&gt;Se corrige script para ejecucion manual en Wapsa se enviara a TICA cambios dentro del Ticket 360&amp;nbsp;&amp;nbsp;&lt;a href="https://dev.azure.com/SycSistemas/WAPSA/_boards/board/t/WAPSA%20Team/Stories/?workitem=257"&gt;https://dev.azure.com/SycSistemas/WAPSA/_boards/board/t/WAPSA%20Team/Stories/?workitem=257&lt;/a&gt; &lt;/div&gt;&lt;div&gt;08/07 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Enviado a TICA &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Repetitivo-en-proceso</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr"/>
+          <t>S&amp;C Sistemas</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Estabilización por proyecto</t>
+        </is>
+      </c>
       <c r="R129" t="n">
         <v>161</v>
       </c>
@@ -17372,7 +17390,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>437</v>
+        <v>256</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -17381,12 +17399,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ticket 435 - Wapsa - Error Asignacion Callao no permite asignar</t>
+          <t>Ticket 359 - Wapsa - Callao - Lista Despacho - Error al listar pesos de IE's de tipo Contenedor Directo</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio - 2025</t>
+          <t>WAPSA\Sprint - Julio - 2024</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -17396,31 +17414,33 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" s="7" t="n">
-        <v>45815.29375</v>
+        <v>45460.79166666666</v>
       </c>
       <c r="H130" s="7" t="n">
-        <v>45815.37708333333</v>
+        <v>45461.79166666666</v>
       </c>
       <c r="I130" s="7" t="n">
-        <v>45822.4375</v>
+        <v>45490.79166666666</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>WAPSA</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>112573</v>
+      </c>
       <c r="L130" t="n">
-        <v>435</v>
+        <v>359</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Error no se puede asignar &amp;quot;T018-0030057&amp;quot; esta guia debido a que el registro en el &amp;quot;Pesaje&amp;quot; no tiene &amp;quot;Producto&amp;quot; asignado debido al sistema &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mandar un script para actualizar el idproducto del registro y permita Asignar. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;El listado de Pesos de este tipo de IE's de queda cargando &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/22c0e199-4ac9-4148-97eb-876e7061b6d8?fileName=image.png" alt=undefined&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;17/16 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se debe corregir script&amp;nbsp;[eq].[EQ_VerDetallexLote_pa] Error: Division By Zero. A la espera de usuario citrix para pruebas TC #109995. &lt;/div&gt;&lt;div&gt;18/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Correccion realizada a la espera de formato para firmas. Adjunto al Ticket el script &lt;/div&gt;&lt;div&gt;&lt;span style="display:inline !important;"&gt;08/07&lt;span&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;a href="https://dev.azure.com/SycSistemas/WAPSA/_boards/board/t/WAPSA%20Team/Stories/?workitem=254#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc" style="box-sizing:border-box;text-decoration:underline;cursor:pointer;"&gt;@Cristian Pastor Artigas&lt;/a&gt;&lt;span style="display:inline !important;"&gt;&amp;nbsp;Enviado a TICA&lt;/span&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -17430,12 +17450,12 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R130" t="n">
@@ -17449,7 +17469,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>440</v>
+        <v>257</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -17458,46 +17478,48 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ticket 436 - Implementar nuevo caso GRE "Otros"</t>
+          <t>Ticket 360 - Wapsa - Callao - Lista Despacho - Alerta despachos pesos 0 no manda datos sobre todas las IE's</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio - 2025</t>
+          <t>WAPSA\Sprint - Julio - 2024</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Resuelto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" s="7" t="n">
-        <v>45813.79166666666</v>
+        <v>45461.79166666666</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>45818.33819444444</v>
+        <v>45461.79166666666</v>
       </c>
       <c r="I131" s="7" t="n">
-        <v>45832.42916666667</v>
+        <v>45510.79166666666</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>External API</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>114413</v>
+      </c>
       <c r="L131" t="n">
-        <v>436</v>
+        <v>360</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El usuario requiere implementar nuevo caso para las GRE &amp;quot;Otros&amp;quot; que será generado por impala via &amp;quot;API&amp;quot; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se implementa código para soportar el caso &amp;quot;Otros&amp;quot; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Wally reporta&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/a81ef737-787a-467b-abde-596fc669aa60?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Poner IES en una misma lista &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;19/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se corrige el script quitando restriccion de dias para atras para que utilice los lotes.&amp;nbsp; &lt;/div&gt;&lt;div&gt;Adjunto script. queda a la espera de formato para enviarlo. &lt;/div&gt;&lt;div&gt;&lt;span style="display:inline !important;"&gt;08/07&lt;span&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;a href="https://dev.azure.com/SycSistemas/WAPSA/_boards/board/t/WAPSA%20Team/Stories/?workitem=254#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc" style="box-sizing:border-box;text-decoration:underline;cursor:pointer;"&gt;@Cristian Pastor Artigas&lt;/a&gt;&lt;span style="display:inline !important;"&gt;&amp;nbsp;Enviado a TICA&lt;/span&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;span style="display:inline !important;"&gt;18/07 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; El correo no muestra el numero de IE&lt;/span&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -17507,12 +17529,12 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R131" t="n">
@@ -17526,7 +17548,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>443</v>
+        <v>276</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -17535,12 +17557,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ticket 439 - Wapsa - Ajuste Mensual - El Reporte excluya del historico de rumas aquellas involucradas en Mezcla y Junta simultánemente</t>
+          <t>Ticket 362 - Wapsa - Callao - Lista Despacho - No se puede Cerrar IE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio - 2025</t>
+          <t>WAPSA\Sprint - Julio - 2024</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -17550,29 +17572,33 @@
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" s="7" t="n">
-        <v>45820.51458333333</v>
+        <v>45475.79166666666</v>
       </c>
       <c r="H132" s="7" t="n">
-        <v>45820.51458333333</v>
+        <v>45475.79166666666</v>
       </c>
       <c r="I132" s="7" t="n">
-        <v>45827.79166666666</v>
+        <v>45475.79166666666</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Wapsa</t>
+          <t>Wapsa Web</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="n">
-        <v>439</v>
+        <v>362</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Wally reporta: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/408f985f-3dbc-4823-899d-0d634139e3ce?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O132" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -17599,7 +17625,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>446</v>
+        <v>281</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -17608,12 +17634,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ticket 441- Wapsa - Mina - Stock - Revisión Lentitud Listado</t>
+          <t>Ticket 363 - Wapsa - Mina - Pesaje -  Despachos - Columna Estado Diferencia muestra datos no relacionados entre si</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Julio - 2025</t>
+          <t>WAPSA\Sprint - Julio - 2024</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -17621,33 +17647,35 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>[Ver 2.24]</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" s="7" t="n">
-        <v>45851.79166666666</v>
+        <v>45481.79166666666</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>45859.42916666667</v>
-      </c>
-      <c r="I133" s="7" t="n"/>
+        <v>45481.79166666666</v>
+      </c>
+      <c r="I133" s="7" t="n">
+        <v>45479.79166666666</v>
+      </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>Wapsa web</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="n">
-        <v>441</v>
+        <v>363</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Wally Reporta: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/3b38811d-3eb0-45bf-83a9-4566498270fa?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;SI no hay diferencias no deberia indicar&amp;nbsp;&lt;span style="display:inline !important;"&gt;ESTADO DIF PESO TARA = Aprobado deberia decir&amp;nbsp;&lt;span style="display:inline !important;"&gt;DENTRO DEL RANGO&lt;/span&gt;&lt;/span&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -17655,12 +17683,12 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R133" t="n">
@@ -17674,7 +17702,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>456</v>
+        <v>284</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -17683,12 +17711,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ticket 443 - Error al listar vagones en arribo mina en el detalle</t>
+          <t>Ticket 365 - Wapsa - Callao - Lista Despacho - Alerta envio correo IE diferencias pesos TMH Solo envia 1 IE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Julio - 2025</t>
+          <t>WAPSA\Sprint - Julio - 2024</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -17696,28 +17724,24 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>[Ver 2.24]</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" s="7" t="n">
-        <v>45856.60833333333</v>
+        <v>45487.79166666666</v>
       </c>
       <c r="H134" s="7" t="n">
-        <v>45856.60833333333</v>
+        <v>45487.79166666666</v>
       </c>
       <c r="I134" s="7" t="n">
-        <v>45859.375</v>
+        <v>45487.79166666666</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>WAPSA</t>
+          <t>Wapsa Web</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="n">
-        <v>443</v>
+        <v>365</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -17726,7 +17750,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El usuario detecto que al guardar unos de los vagones en el arribo mina se ve triplicado en el detalle&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/4b704854-c497-4128-89b2-cf06ce05fdcc?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Esto es ocasiado porque el SP que se encarga de mostrar el detalle de los vagones no esta filtrando correctamente por las guias activas por lo que se ven esas dos guías demás &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;SP a modificar:&amp;nbsp;&lt;span style="font-weight:400;display:inline !important;"&gt;[dp].[DP_OrdenTrabajoArriboDetalle_Paginado_pa]&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;span style="font-weight:400;display:inline !important;"&gt;&lt;br&gt;&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;span style="font-weight:400;display:inline !important;"&gt;Agregar en la condicional &amp;quot;Dg.IdEstado = 1&amp;quot;&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;span style="font-weight:400;display:inline !important;"&gt;&lt;br&gt;&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;span style="font-weight:400;display:inline !important;"&gt;&lt;br&gt;&lt;/span&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Wally Moscoso Reporta &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/08117d40-581e-48b4-ac15-02067d0d151b?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -17741,7 +17765,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R134" t="n">
@@ -17755,7 +17779,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -17764,7 +17788,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ticket 357 - Wapsa BI - General - Revisar datos del Reporte de Leyes del BI para los meses de Mayo y Junio</t>
+          <t>Ticket 369 - Wapsa - Mina - Pesaje - Error de bloqueo de algunas tablas de la base de datos Wapsa (Lock)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17779,24 +17803,22 @@
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" s="7" t="n">
-        <v>45453.79166666666</v>
+        <v>45496.79166666666</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>45453.79166666666</v>
+        <v>45496.79166666666</v>
       </c>
       <c r="I135" s="7" t="n">
-        <v>45460.79166666666</v>
+        <v>45496.79166666666</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Wapsa BI</t>
-        </is>
-      </c>
-      <c r="K135" t="n">
-        <v>109586</v>
-      </c>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="n">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -17805,22 +17827,22 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Luis Casas indica en la reunion de 11/06 que el reporte de Mayo no le muestra informacion y para Junio le faltan datos de leyes sobre algunas guias. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;12/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; &lt;/div&gt;&lt;div&gt;Se revisa Mayo y Junio y no se muestra la informacion completa porque el script filtra solo por Guias en estado 1 y debe hacerlo para 1 y 2 (preasignado y con Peso Bruto). &lt;/div&gt;&lt;div&gt;Se corrige scripit en BI &lt;/div&gt;&lt;div&gt;Se corrige script para ejecucion manual en Wapsa se enviara a TICA cambios dentro del Ticket 360&amp;nbsp;&amp;nbsp;&lt;a href="https://dev.azure.com/SycSistemas/WAPSA/_boards/board/t/WAPSA%20Team/Stories/?workitem=257"&gt;https://dev.azure.com/SycSistemas/WAPSA/_boards/board/t/WAPSA%20Team/Stories/?workitem=257&lt;/a&gt; &lt;/div&gt;&lt;div&gt;08/07 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Enviado a TICA &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Los usuario inidcan que no pueden realizar transacciones sobre el Wapsa. &lt;/div&gt;&lt;div&gt;En reunion con se detecta que un usuario que accedio al parece tiene un proceso bloqueado lo que ocasiona bloqueo sobre los demas. EL DBA desbloquea los accesos para que puedan contiuar operando &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Repetitivo-en-proceso</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Servidor MCP</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R135" t="n">
@@ -17834,7 +17856,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>256</v>
+        <v>162</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -17843,12 +17865,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ticket 359 - Wapsa - Callao - Lista Despacho - Error al listar pesos de IE's de tipo Contenedor Directo</t>
+          <t>Ticket 292 - Wapsa - Mina - Pesaje - Error proceso aprobación pesaje Manual - Mina</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Julio - 2024</t>
+          <t>WAPSA\Sprint - Febrero 2024</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -17856,26 +17878,28 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>[Ver.2.14]</t>
+        </is>
+      </c>
       <c r="G136" s="7" t="n">
-        <v>45460.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>45461.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="I136" s="7" t="n">
-        <v>45490.79166666666</v>
+        <v>45333.79166666666</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K136" t="n">
-        <v>112573</v>
-      </c>
+          <t>WAPSA web</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -17884,7 +17908,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>&lt;div&gt;El listado de Pesos de este tipo de IE's de queda cargando &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/22c0e199-4ac9-4148-97eb-876e7061b6d8?fileName=image.png" alt=undefined&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;17/16 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se debe corregir script&amp;nbsp;[eq].[EQ_VerDetallexLote_pa] Error: Division By Zero. A la espera de usuario citrix para pruebas TC #109995. &lt;/div&gt;&lt;div&gt;18/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Correccion realizada a la espera de formato para firmas. Adjunto al Ticket el script &lt;/div&gt;&lt;div&gt;&lt;span style="display:inline !important;"&gt;08/07&lt;span&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;a href="https://dev.azure.com/SycSistemas/WAPSA/_boards/board/t/WAPSA%20Team/Stories/?workitem=254#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc" style="box-sizing:border-box;text-decoration:underline;cursor:pointer;"&gt;@Cristian Pastor Artigas&lt;/a&gt;&lt;span style="display:inline !important;"&gt;&amp;nbsp;Enviado a TICA&lt;/span&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;No se puede aprobar o rechazar desde el mail el pesaje manual automático (no funciona al dar click de aprobar o rechazar)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -17894,12 +17918,12 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R136" t="n">
@@ -17913,7 +17937,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>257</v>
+        <v>164</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -17922,12 +17946,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ticket 360 - Wapsa - Callao - Lista Despacho - Alerta despachos pesos 0 no manda datos sobre todas las IE's</t>
+          <t>Ticket 293 - Wapsa - Mina - Pesaje - Los adjuntos para Diferencia de peso tara se estan guardando mal</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Julio - 2024</t>
+          <t>WAPSA\Sprint - Febrero 2024</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -17935,26 +17959,28 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>[Ver.2.14]</t>
+        </is>
+      </c>
       <c r="G137" s="7" t="n">
-        <v>45461.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>45461.79166666666</v>
+        <v>45334.79166666666</v>
       </c>
       <c r="I137" s="7" t="n">
-        <v>45510.79166666666</v>
+        <v>45355.79166666666</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K137" t="n">
-        <v>114413</v>
-      </c>
+          <t>WAPSA web</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="n">
-        <v>360</v>
+        <v>293</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -17963,7 +17989,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Wally reporta&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/a81ef737-787a-467b-abde-596fc669aa60?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Poner IES en una misma lista &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;19/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se corrige el script quitando restriccion de dias para atras para que utilice los lotes.&amp;nbsp; &lt;/div&gt;&lt;div&gt;Adjunto script. queda a la espera de formato para enviarlo. &lt;/div&gt;&lt;div&gt;&lt;span style="display:inline !important;"&gt;08/07&lt;span&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;a href="https://dev.azure.com/SycSistemas/WAPSA/_boards/board/t/WAPSA%20Team/Stories/?workitem=254#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc" style="box-sizing:border-box;text-decoration:underline;cursor:pointer;"&gt;@Cristian Pastor Artigas&lt;/a&gt;&lt;span style="display:inline !important;"&gt;&amp;nbsp;Enviado a TICA&lt;/span&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;span style="display:inline !important;"&gt;18/07 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; El correo no muestra el numero de IE&lt;/span&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mina/despacho: Los casos revisados son de diferencia de peso Tara, los adjuntos se están grabando en Peso Bruto (corregir)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se realiza correccion &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;13/02&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Pendiente revisión &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -17973,12 +17999,12 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R137" t="n">
@@ -17992,7 +18018,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -18001,12 +18027,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ticket 362 - Wapsa - Callao - Lista Despacho - No se puede Cerrar IE</t>
+          <t>Ticket 294 - Wapsa - Mina - Pesaje - Vista de Vagones observados no filtra ni exporta correctamente</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Julio - 2024</t>
+          <t>WAPSA\Sprint - Febrero 2024</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -18014,24 +18040,28 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>[Ver.2.14]</t>
+        </is>
+      </c>
       <c r="G138" s="7" t="n">
-        <v>45475.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="H138" s="7" t="n">
-        <v>45475.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="I138" s="7" t="n">
-        <v>45475.79166666666</v>
+        <v>45355.79166666666</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WAPSA web</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
-        <v>362</v>
+        <v>294</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -18040,7 +18070,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Wally reporta: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/408f985f-3dbc-4823-899d-0d634139e3ce?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mina/despacho, vagones observados: No se exporta por completo la lista de vagones despachados observados &amp;nbsp;// vista de aprobación de pesaje manual bruto y tara&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Correccion realizada&lt;b&gt; &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -18050,7 +18080,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -18069,7 +18099,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>281</v>
+        <v>167</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -18078,12 +18108,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ticket 363 - Wapsa - Mina - Pesaje -  Despachos - Columna Estado Diferencia muestra datos no relacionados entre si</t>
+          <t>Ticket 296 - Wapsa - Callao - Lista Despacho - Corregir "ITEM" cuando das click en ver "Detalle" por una IE</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Julio - 2024</t>
+          <t>WAPSA\Sprint - Febrero 2024</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -18091,33 +18121,37 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>[Ver.2.14]</t>
+        </is>
+      </c>
       <c r="G139" s="7" t="n">
-        <v>45481.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>45481.79166666666</v>
+        <v>45327.79166666666</v>
       </c>
       <c r="I139" s="7" t="n">
-        <v>45479.79166666666</v>
+        <v>45355.79166666666</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Wapsa web</t>
+          <t>WAPSA web</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="n">
-        <v>363</v>
+        <v>296</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Wally Reporta: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/3b38811d-3eb0-45bf-83a9-4566498270fa?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;SI no hay diferencias no deberia indicar&amp;nbsp;&lt;span style="display:inline !important;"&gt;ESTADO DIF PESO TARA = Aprobado deberia decir&amp;nbsp;&lt;span style="display:inline !important;"&gt;DENTRO DEL RANGO&lt;/span&gt;&lt;/span&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Corregir el ITEM para cuando se despliega el “VER DETALLE” de pesos en traslados externos y contenedores en la lista de despacho&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -18127,12 +18161,12 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R139" t="n">
@@ -18146,7 +18180,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -18155,12 +18189,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ticket 365 - Wapsa - Callao - Lista Despacho - Alerta envio correo IE diferencias pesos TMH Solo envia 1 IE</t>
+          <t>Ticket 297 - Wapsa - Callao - C.Stock - Error valores en TMS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Julio - 2024</t>
+          <t>WAPSA\Sprint - Febrero 2024</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -18168,24 +18202,30 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>[Ver.2.13]</t>
+        </is>
+      </c>
       <c r="G140" s="7" t="n">
-        <v>45487.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="H140" s="7" t="n">
-        <v>45487.79166666666</v>
+        <v>45321.79166666666</v>
       </c>
       <c r="I140" s="7" t="n">
-        <v>45487.79166666666</v>
+        <v>45323.79166666666</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr"/>
+          <t>WAPSA web</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>96077</v>
+      </c>
       <c r="L140" t="n">
-        <v>365</v>
+        <v>297</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -18194,7 +18234,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Wally Moscoso Reporta &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/08117d40-581e-48b4-ac15-02067d0d151b?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;/Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Stock Callao (revisará MM).&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Pendiente Michael tiene que enviar los valores correctos&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Actualización&amp;nbsp; 29/01: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Michael reviso testing, comenta que el resumen en TMS la suma de las rumas no da el resultado total. &lt;/div&gt;&lt;div&gt;El Valor final que sale del TMS se debe ver reflejado como valor inicial en el siguiente mes &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;b style="box-sizing:border-box;"&gt;31/01/2024&amp;nbsp;&lt;/b&gt;Se tiene solucion&amp;nbsp; del ticket.&lt;/b&gt;&lt;b&gt;&amp;nbsp;Se envia formato para firma de Alejandro &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;31/10/2023 En firmas Por TICA&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -18204,7 +18244,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -18223,7 +18263,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>292</v>
+        <v>171</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -18232,12 +18272,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ticket 369 - Wapsa - Mina - Pesaje - Error de bloqueo de algunas tablas de la base de datos Wapsa (Lock)</t>
+          <t>Ticket 299 - Wapsa - Callao - Volteo -  No llega el mail de vagones con diferencia de pesos brutos en Callao / Volteo (pendiente notificación)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Julio - 2024</t>
+          <t>WAPSA\Sprint - Febrero 2024</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -18245,24 +18285,28 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>[Ver.2.13]</t>
+        </is>
+      </c>
       <c r="G141" s="7" t="n">
-        <v>45496.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="H141" s="7" t="n">
-        <v>45496.79166666666</v>
+        <v>45327.79166666666</v>
       </c>
       <c r="I141" s="7" t="n">
-        <v>45496.79166666666</v>
+        <v>45330.79166666666</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WAPSA web</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="n">
-        <v>369</v>
+        <v>299</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -18271,7 +18315,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Los usuario inidcan que no pueden realizar transacciones sobre el Wapsa. &lt;/div&gt;&lt;div&gt;En reunion con se detecta que un usuario que accedio al parece tiene un proceso bloqueado lo que ocasiona bloqueo sobre los demas. EL DBA desbloquea los accesos para que puedan contiuar operando &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;No llega el mail de vagones con diferencia de pesos brutos en Callao / Volteo (pendiente notificación)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;30/01:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Sigue pendiente crear la notificación - Cristian SYC &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b style="box-sizing:border-box;"&gt;02/02:&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Pendiente Wally crear la notifiación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -18286,7 +18330,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R141" t="n">
@@ -18300,7 +18344,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -18309,7 +18353,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ticket 292 - Wapsa - Mina - Pesaje - Error proceso aprobación pesaje Manual - Mina</t>
+          <t>Ticket 300 - Wapsa - Callao - Lista Despacho - Cierre de IE's</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18322,19 +18366,15 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>[Ver.2.14]</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
       <c r="H142" s="7" t="n">
-        <v>45314.79166666666</v>
+        <v>45327.79166666666</v>
       </c>
       <c r="I142" s="7" t="n">
-        <v>45333.79166666666</v>
+        <v>45355.79166666666</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -18343,16 +18383,16 @@
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;No se puede aprobar o rechazar desde el mail el pesaje manual automático (no funciona al dar click de aprobar o rechazar)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Cierre de IE’s – Hay 3 IE’s que la leyes están de color amarillo en la lista de despacho y el usuario indica que ya tiene todas las guías importadas&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Tieene que volver a importar las leyes por estos casos debido a que el WAPSA no guardo las leyes de todas las guías &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -18362,12 +18402,12 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R142" t="n">
@@ -18381,7 +18421,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -18390,7 +18430,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ticket 293 - Wapsa - Mina - Pesaje - Los adjuntos para Diferencia de peso tara se estan guardando mal</t>
+          <t>Ticket 301 - Wapsa - Callao - Volteo - DIFERENCIA DE PESOS BRUTOS CALLAO</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18412,7 +18452,7 @@
         <v>45314.79166666666</v>
       </c>
       <c r="H143" s="7" t="n">
-        <v>45334.79166666666</v>
+        <v>45322.79166666666</v>
       </c>
       <c r="I143" s="7" t="n">
         <v>45355.79166666666</v>
@@ -18424,7 +18464,7 @@
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -18433,7 +18473,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mina/despacho: Los casos revisados son de diferencia de peso Tara, los adjuntos se están grabando en Peso Bruto (corregir)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se realiza correccion &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;13/02&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Pendiente revisión &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;/b&gt; &lt;/div&gt;&lt;span&gt;Hola Cristian después del primer caso de diferencia de pesos (marcado en amarillo), el Wapsa no ha reconocido lo 03 siguientes que figuran en la siguiente lista. Pf revisar urgente que paso.&lt;br&gt;&lt;/span&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Nota: veo que la única diferencia es la guía electrónica (T)..&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d7222d4d-4946-4ca6-8f9a-b55eb33616be?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/ce47f763-4315-43ae-af0e-e9ec6b4f8467?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;br&gt; &lt;/div&gt;&lt;span&gt;&lt;/span&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Se fuerza el cambio del valor iDisplayLength a = 10000 para el método ObtenerListaVolteoObsAlmacenDetallePaginado&amp;nbsp;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -18443,12 +18483,12 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R143" t="n">
@@ -18462,7 +18502,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -18471,7 +18511,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ticket 294 - Wapsa - Mina - Pesaje - Vista de Vagones observados no filtra ni exporta correctamente</t>
+          <t>Ticket 316 - Wapsa - Mina - Pesaje - No deja adjuntar las evidencias para duplicidad de precintos</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18490,10 +18530,10 @@
         </is>
       </c>
       <c r="G144" s="7" t="n">
-        <v>45314.79166666666</v>
+        <v>45320.79166666666</v>
       </c>
       <c r="H144" s="7" t="n">
-        <v>45314.79166666666</v>
+        <v>45321.79166666666</v>
       </c>
       <c r="I144" s="7" t="n">
         <v>45355.79166666666</v>
@@ -18505,7 +18545,7 @@
       </c>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="n">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -18514,7 +18554,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mina/despacho, vagones observados: No se exporta por completo la lista de vagones despachados observados &amp;nbsp;// vista de aprobación de pesaje manual bruto y tara&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Correccion realizada&lt;b&gt; &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Modulo Mina - No deja adjuntar las evidencias para duplicidad de precintos&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se implementa el cambio, en espera de programar pase&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -18529,7 +18569,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R144" t="n">
@@ -18543,7 +18583,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -18552,7 +18592,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ticket 296 - Wapsa - Callao - Lista Despacho - Corregir "ITEM" cuando das click en ver "Detalle" por una IE</t>
+          <t>Ticket 317 - Wapsa - Mina - Inspección - En la lista de observados el orden de los checks no es igual al que se guardó</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -18567,35 +18607,37 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>[Ver.2.14]</t>
+          <t>[Ver.2.13]</t>
         </is>
       </c>
       <c r="G145" s="7" t="n">
-        <v>45314.79166666666</v>
+        <v>45322.79166666666</v>
       </c>
       <c r="H145" s="7" t="n">
-        <v>45327.79166666666</v>
+        <v>45330.79166666666</v>
       </c>
       <c r="I145" s="7" t="n">
-        <v>45355.79166666666</v>
+        <v>45330.79166666666</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>WAPSA web</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="n">
+        <v>98637</v>
+      </c>
       <c r="L145" t="n">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Corregir el ITEM para cuando se despliega el “VER DETALLE” de pesos en traslados externos y contenedores en la lista de despacho&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Modulo Mina y Callao - Inspeccion En la lista de observados no se muestra el check de inspeccion en el orden que se guardo&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se corrige&amp;nbsp; script para ajustar ordenamiento al mostrar los valores de la inspeccion &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -18605,12 +18647,12 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R145" t="n">
@@ -18624,7 +18666,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -18633,7 +18675,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ticket 297 - Wapsa - Callao - C.Stock - Error valores en TMS</t>
+          <t>Ticket 319 - Wapsa - Mina - Inspección - Mover opciones de aprobacion por guia a la pestaña de observados</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -18648,17 +18690,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>[Ver.2.13]</t>
+          <t>[Ver.2.14]</t>
         </is>
       </c>
       <c r="G146" s="7" t="n">
         <v>45314.79166666666</v>
       </c>
       <c r="H146" s="7" t="n">
-        <v>45321.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="I146" s="7" t="n">
-        <v>45323.79166666666</v>
+        <v>45347.79166666666</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -18666,10 +18708,10 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>96077</v>
+        <v>100230</v>
       </c>
       <c r="L146" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -18678,7 +18720,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;/Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Stock Callao (revisará MM).&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Pendiente Michael tiene que enviar los valores correctos&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Actualización&amp;nbsp; 29/01: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Michael reviso testing, comenta que el resumen en TMS la suma de las rumas no da el resultado total. &lt;/div&gt;&lt;div&gt;El Valor final que sale del TMS se debe ver reflejado como valor inicial en el siguiente mes &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;b style="box-sizing:border-box;"&gt;31/01/2024&amp;nbsp;&lt;/b&gt;Se tiene solucion&amp;nbsp; del ticket.&lt;/b&gt;&lt;b&gt;&amp;nbsp;Se envia formato para firma de Alejandro &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;31/10/2023 En firmas Por TICA&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mina/despacho: mover las opciones de click derecho referidas a&amp;nbsp; aprobaciones a la pestaña de observados&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se mueven botones de de aprobaciones a pestaña de observados &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -18688,12 +18730,12 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R146" t="n">
@@ -18707,7 +18749,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -18716,7 +18758,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ticket 299 - Wapsa - Callao - Volteo -  No llega el mail de vagones con diferencia de pesos brutos en Callao / Volteo (pendiente notificación)</t>
+          <t>Ticket 318 - Wapsa - Callao- Inspección - Aprobacion Inspeccion Vagones</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -18731,17 +18773,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>[Ver.2.13]</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="G147" s="7" t="n">
-        <v>45314.79166666666</v>
+        <v>45326.79166666666</v>
       </c>
       <c r="H147" s="7" t="n">
-        <v>45327.79166666666</v>
+        <v>45326.79166666666</v>
       </c>
       <c r="I147" s="7" t="n">
-        <v>45330.79166666666</v>
+        <v>45355.79166666666</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -18750,500 +18792,14 @@
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;No llega el mail de vagones con diferencia de pesos brutos en Callao / Volteo (pendiente notificación)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;30/01:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Sigue pendiente crear la notificación - Cristian SYC &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b style="box-sizing:border-box;"&gt;02/02:&lt;/b&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Pendiente Wally crear la notifiación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Servidor MCP</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>Estabilización por proyecto</t>
-        </is>
-      </c>
-      <c r="R147" t="n">
-        <v>161</v>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>173</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Ticket 300 - Wapsa - Callao - Lista Despacho - Cierre de IE's</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" s="7" t="n">
-        <v>45314.79166666666</v>
-      </c>
-      <c r="H148" s="7" t="n">
-        <v>45327.79166666666</v>
-      </c>
-      <c r="I148" s="7" t="n">
-        <v>45355.79166666666</v>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>WAPSA web</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="n">
-        <v>300</v>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Cierre de IE’s – Hay 3 IE’s que la leyes están de color amarillo en la lista de despacho y el usuario indica que ya tiene todas las guías importadas&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Tieene que volver a importar las leyes por estos casos debido a que el WAPSA no guardo las leyes de todas las guías &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>A&amp;S</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>Estabilización de req. de Mantenimiento</t>
-        </is>
-      </c>
-      <c r="R148" t="n">
-        <v>161</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>174</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Ticket 301 - Wapsa - Callao - Volteo - DIFERENCIA DE PESOS BRUTOS CALLAO</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>[Ver.2.14]</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="n">
-        <v>45314.79166666666</v>
-      </c>
-      <c r="H149" s="7" t="n">
-        <v>45322.79166666666</v>
-      </c>
-      <c r="I149" s="7" t="n">
-        <v>45355.79166666666</v>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>WAPSA web</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="n">
-        <v>301</v>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;/b&gt; &lt;/div&gt;&lt;span&gt;Hola Cristian después del primer caso de diferencia de pesos (marcado en amarillo), el Wapsa no ha reconocido lo 03 siguientes que figuran en la siguiente lista. Pf revisar urgente que paso.&lt;br&gt;&lt;/span&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Nota: veo que la única diferencia es la guía electrónica (T)..&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d7222d4d-4946-4ca6-8f9a-b55eb33616be?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/ce47f763-4315-43ae-af0e-e9ec6b4f8467?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;br&gt; &lt;/div&gt;&lt;span&gt;&lt;/span&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Se fuerza el cambio del valor iDisplayLength a = 10000 para el método ObtenerListaVolteoObsAlmacenDetallePaginado&amp;nbsp;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>A&amp;S</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>Estabilización de req. de Mantenimiento</t>
-        </is>
-      </c>
-      <c r="R149" t="n">
-        <v>161</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>195</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Ticket 316 - Wapsa - Mina - Pesaje - No deja adjuntar las evidencias para duplicidad de precintos</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>[Ver.2.14]</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="n">
-        <v>45320.79166666666</v>
-      </c>
-      <c r="H150" s="7" t="n">
-        <v>45321.79166666666</v>
-      </c>
-      <c r="I150" s="7" t="n">
-        <v>45355.79166666666</v>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>WAPSA web</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="n">
-        <v>316</v>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Modulo Mina - No deja adjuntar las evidencias para duplicidad de precintos&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se implementa el cambio, en espera de programar pase&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>S&amp;C Sistemas</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>Estabilización por proyecto</t>
-        </is>
-      </c>
-      <c r="R150" t="n">
-        <v>161</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>196</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Ticket 317 - Wapsa - Mina - Inspección - En la lista de observados el orden de los checks no es igual al que se guardó</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>[Ver.2.13]</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="n">
-        <v>45322.79166666666</v>
-      </c>
-      <c r="H151" s="7" t="n">
-        <v>45330.79166666666</v>
-      </c>
-      <c r="I151" s="7" t="n">
-        <v>45330.79166666666</v>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>WAPSA web</t>
-        </is>
-      </c>
-      <c r="K151" t="n">
-        <v>98637</v>
-      </c>
-      <c r="L151" t="n">
-        <v>317</v>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Modulo Mina y Callao - Inspeccion En la lista de observados no se muestra el check de inspeccion en el orden que se guardo&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se corrige&amp;nbsp; script para ajustar ordenamiento al mostrar los valores de la inspeccion &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>S&amp;C Sistemas</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>Estabilización por proyecto</t>
-        </is>
-      </c>
-      <c r="R151" t="n">
-        <v>161</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>198</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Ticket 319 - Wapsa - Mina - Inspección - Mover opciones de aprobacion por guia a la pestaña de observados</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>[Ver.2.14]</t>
-        </is>
-      </c>
-      <c r="G152" s="7" t="n">
-        <v>45314.79166666666</v>
-      </c>
-      <c r="H152" s="7" t="n">
-        <v>45314.79166666666</v>
-      </c>
-      <c r="I152" s="7" t="n">
-        <v>45347.79166666666</v>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>WAPSA web</t>
-        </is>
-      </c>
-      <c r="K152" t="n">
-        <v>100230</v>
-      </c>
-      <c r="L152" t="n">
-        <v>296</v>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mina/despacho: mover las opciones de click derecho referidas a&amp;nbsp; aprobaciones a la pestaña de observados&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se mueven botones de de aprobaciones a pestaña de observados &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>No implica estabilización</t>
-        </is>
-      </c>
-      <c r="R152" t="n">
-        <v>161</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>199</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Ticket 318 - Wapsa - Callao- Inspección - Aprobacion Inspeccion Vagones</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Consulta</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="n">
-        <v>45326.79166666666</v>
-      </c>
-      <c r="H153" s="7" t="n">
-        <v>45326.79166666666</v>
-      </c>
-      <c r="I153" s="7" t="n">
-        <v>45355.79166666666</v>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>WAPSA web</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="n">
-        <v>318</v>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
         <is>
           <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;p style="margin:0cm;font-size:11pt;font-family:Calibri, sans-serif;"&gt;&lt;span lang=ES style=""&gt;El sgte vagón fue
 aprobado por Edwin Rios, sin embargo, sale mi usuario como si hubiese aprobado
@@ -19254,6 +18810,488 @@
 correctamente.&lt;/span&gt; &lt;/p&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Error del usuario</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>No implica estabilización</t>
+        </is>
+      </c>
+      <c r="R147" t="n">
+        <v>161</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>201</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ticket 320 - Wapsa - Mina - Pesaje - Diferencia pesos tara no esta evaluando correctamente cuando es mayor al factor</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Febrero 2024</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>[Ver.2.14]</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="n">
+        <v>45328.79166666666</v>
+      </c>
+      <c r="H148" s="7" t="n">
+        <v>45328.79166666666</v>
+      </c>
+      <c r="I148" s="7" t="n">
+        <v>45328.79166666666</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>WAPSA web</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>320</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Modulo Mina - pesaje - Diferencia pesos tara no esta evaluando correctamente cuando es mayor al factor &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se cambio lógica para corregir este error &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Repetitivo-por-resolver</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>S&amp;C Sistemas</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Estabilización de req. de Mantenimiento</t>
+        </is>
+      </c>
+      <c r="R148" t="n">
+        <v>161</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>202</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ticket 321 - Wapsa - Callao - Volteo - Diferencia pesos brutosMina-Callao no esta evaluando correctamente cuando es mayor al factor</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Febrero 2024</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>[Ver.2.14]</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="n">
+        <v>45328.79166666666</v>
+      </c>
+      <c r="H149" s="7" t="n">
+        <v>45328.79166666666</v>
+      </c>
+      <c r="I149" s="7" t="n">
+        <v>45328.79166666666</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>WAPSA web</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>WAPSA web</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>320</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Modulo Callao - Volteo- Diferencia pesos brutosMina-Callao no esta evaluando correctamente cuando es mayor al factor &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se cambio lógica para corregir este error &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>S&amp;C Sistemas</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Estabilización por proyecto</t>
+        </is>
+      </c>
+      <c r="R149" t="n">
+        <v>161</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>204</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ticket 323 - Wapsa - Callao - Impresión de Guías ED - Modulo impresion ED anulación error</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Febrero 2024</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Consulta</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="n">
+        <v>45330.79166666666</v>
+      </c>
+      <c r="H150" s="7" t="n">
+        <v>45330.79166666666</v>
+      </c>
+      <c r="I150" s="7" t="n">
+        <v>45330.79166666666</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>WAPSA web</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="n">
+        <v>323</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El usuario indica que se tiene una guía en el modulo de entrega directa que se genero correctamente la GRE pero visualmente se ve en el wapsa como estado anulado y sin fecha de impresión &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;font color="#2a2a2a" face="Segoe UI Bold, Segoe UI Semibold, Segoe UI, Helvetica Neue Medium, Arial, sans-serif"&gt;Se verifico el caso y el usuario dio dos veces click ocasionando un error en el WAPSA&lt;/font&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>S&amp;C Sistemas</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Estabilización por proyecto</t>
+        </is>
+      </c>
+      <c r="R150" t="n">
+        <v>161</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>205</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ticket 323-1 - Wapsa - Callao - Reporte Asignación - Muestra el valor incorrecto de  TMH Guia T018-0001621</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Febrero 2024</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" s="7" t="n">
+        <v>45333.79166666666</v>
+      </c>
+      <c r="H151" s="7" t="n">
+        <v>45333.79166666666</v>
+      </c>
+      <c r="I151" s="7" t="n">
+        <v>45340.79166666666</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>323</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Ticket 323 - Wapsa Reporte Asignacion - Muestra el valor incorrecto de &amp;nbsp;TMH Guia T018-0001621&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;-El reporte suma de forma incorrecta el TMS por esta duplicada la Guia&amp;nbsp;T018-0001621 en Entregas directas. &lt;/div&gt;&lt;div&gt;-Se corrige modificando en entrega directa la Guia&amp;nbsp;T018-0001621 a estado =0 &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Error del usuario</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Estabilización de req. de Mantenimiento</t>
+        </is>
+      </c>
+      <c r="R151" t="n">
+        <v>161</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>206</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ticket 323-2 - Wapsa - Callao - Muestreo - Se registaron guias con lote CC2402 en vez de CC2401</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Febrero 2024</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Consulta</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="n">
+        <v>45336.79166666666</v>
+      </c>
+      <c r="H152" s="7" t="n">
+        <v>45336.79166666666</v>
+      </c>
+      <c r="I152" s="7" t="n">
+        <v>45336.79166666666</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="n">
+        <v>323</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d259f3d5-3b11-4660-ace4-6fd3e97a17c7?fileName=image.png" alt=Image style="width:803px;height:235px;" width=803 height=235&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;i&gt;15/05: Revisar listado de guia; LC inidca que tiene fecha de muestreo del lote CC2402 pero el sistema asigno lote CC2402&lt;/i&gt; &lt;/div&gt;&lt;div&gt;&lt;i&gt;15/05: Se revisa el listado y el muestreo se grabo entre las 8 y 8:30 am del dia 26/04 por ende el sistema le asigno el lote 2402&lt;/i&gt; &lt;/div&gt;&lt;div&gt;&lt;i&gt;&lt;br&gt;&lt;/i&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Error del usuario</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>No implica estabilización</t>
+        </is>
+      </c>
+      <c r="R152" t="n">
+        <v>161</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>209</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ticket 326 - Wapsa - Mina - C.Stock - la lista demora aprox 8 mintos para mostrar la informacion</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Febrero 2024</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" s="7" t="n">
+        <v>45347.79166666666</v>
+      </c>
+      <c r="H153" s="7" t="n">
+        <v>45348.79166666666</v>
+      </c>
+      <c r="I153" s="7" t="n">
+        <v>45348.79166666666</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="n">
+        <v>326</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Jorge Garcia reporta que no carga la pantalla del stock Diario. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;26/02 Se revisa listado se valida indexado y se envia correo a Jorge para verficar si ya se corrgió el listado &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O153" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -19261,12 +19299,12 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R153" t="n">
@@ -19280,7 +19318,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>201</v>
+        <v>519</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -19289,12 +19327,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ticket 320 - Wapsa - Mina - Pesaje - Diferencia pesos tara no esta evaluando correctamente cuando es mayor al factor</t>
+          <t>Ticket 477 - Wapasa - Callao - Cambiar fechas de lote CT2601 y CT2602</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
+          <t>WAPSA\Sprint - Febrero - 2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -19302,52 +19340,44 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>[Ver.2.14]</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" s="7" t="n">
-        <v>45328.79166666666</v>
+        <v>46051.25902777778</v>
       </c>
       <c r="H154" s="7" t="n">
-        <v>45328.79166666666</v>
+        <v>46051.25902777778</v>
       </c>
       <c r="I154" s="7" t="n">
-        <v>45328.79166666666</v>
+        <v>46057.79166666666</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>WAPSA web</t>
+          <t>Wapsa Web</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="n">
-        <v>320</v>
+        <v>477</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Modulo Mina - pesaje - Diferencia pesos tara no esta evaluando correctamente cuando es mayor al factor &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se cambio lógica para corregir este error &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Repetitivo-por-resolver</t>
+          <t>Repetitivo-en-proceso</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Error del usuario</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R154" t="n">
@@ -19361,7 +19391,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>202</v>
+        <v>521</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -19370,12 +19400,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ticket 321 - Wapsa - Callao - Volteo - Diferencia pesos brutosMina-Callao no esta evaluando correctamente cuando es mayor al factor</t>
+          <t>Ticket 479 - Wapsa - Vagón de Inspeccion Callao no se muestra en el listado</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
+          <t>WAPSA\Sprint - Febrero - 2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -19383,43 +19413,33 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>[Ver.2.14]</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" s="7" t="n">
-        <v>45328.79166666666</v>
+        <v>46059.29791666667</v>
       </c>
       <c r="H155" s="7" t="n">
-        <v>45328.79166666666</v>
+        <v>46059.29791666667</v>
       </c>
       <c r="I155" s="7" t="n">
-        <v>45328.79166666666</v>
+        <v>46062.79166666666</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>WAPSA web</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>WAPSA web</t>
-        </is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>168258</v>
       </c>
       <c r="L155" t="n">
-        <v>320</v>
+        <v>479</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Modulo Callao - Volteo- Diferencia pesos brutosMina-Callao no esta evaluando correctamente cuando es mayor al factor &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se cambio lógica para corregir este error &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -19427,12 +19447,12 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Error del usuario</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R155" t="n">
@@ -19446,7 +19466,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>204</v>
+        <v>380</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -19455,12 +19475,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ticket 323 - Wapsa - Callao - Impresión de Guías ED - Modulo impresion ED anulación error</t>
+          <t>Ticket 404- Wapsa - Mina- Despacho - Correo de Dif Peso Tara del Supervisor debe indicar la palabra Supervisor en el asunto</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
+          <t>WAPSA\Sprint - Febrero - 2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -19470,26 +19490,26 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>[Ver. 2.21]</t>
         </is>
       </c>
       <c r="G156" s="7" t="n">
-        <v>45330.79166666666</v>
+        <v>45652.79166666666</v>
       </c>
       <c r="H156" s="7" t="n">
-        <v>45330.79166666666</v>
+        <v>45670.79166666666</v>
       </c>
       <c r="I156" s="7" t="n">
-        <v>45330.79166666666</v>
+        <v>45729.79166666666</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>WAPSA web</t>
+          <t>Wapsa Web</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="n">
-        <v>323</v>
+        <v>404</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -19498,7 +19518,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El usuario indica que se tiene una guía en el modulo de entrega directa que se genero correctamente la GRE pero visualmente se ve en el wapsa como estado anulado y sin fecha de impresión &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;font color="#2a2a2a" face="Segoe UI Bold, Segoe UI Semibold, Segoe UI, Helvetica Neue Medium, Arial, sans-serif"&gt;Se verifico el caso y el usuario dio dos veces click ocasionando un error en el WAPSA&lt;/font&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Carlos Zenteno: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/239e17e7-f934-47a2-b07a-30038130d4c9?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -19508,12 +19528,12 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R156" t="n">
@@ -19527,7 +19547,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>205</v>
+        <v>391</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -19536,12 +19556,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ticket 323-1 - Wapsa - Callao - Reporte Asignación - Muestra el valor incorrecto de  TMH Guia T018-0001621</t>
+          <t>Ticket 412 - Wapsa - Mina - Inspeccion - Cambiar orden de detalle de convoy para que se muestre por fecha de inspeccion</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
+          <t>WAPSA\Sprint - Febrero - 2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -19549,15 +19569,19 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>[Ver. 2.21]</t>
+        </is>
+      </c>
       <c r="G157" s="7" t="n">
-        <v>45333.79166666666</v>
+        <v>45669.79166666666</v>
       </c>
       <c r="H157" s="7" t="n">
-        <v>45333.79166666666</v>
+        <v>45669.79166666666</v>
       </c>
       <c r="I157" s="7" t="n">
-        <v>45340.79166666666</v>
+        <v>45729.79166666666</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -19566,7 +19590,7 @@
       </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="n">
-        <v>323</v>
+        <v>412</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -19575,7 +19599,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Ticket 323 - Wapsa Reporte Asignacion - Muestra el valor incorrecto de &amp;nbsp;TMH Guia T018-0001621&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;-El reporte suma de forma incorrecta el TMS por esta duplicada la Guia&amp;nbsp;T018-0001621 en Entregas directas. &lt;/div&gt;&lt;div&gt;-Se corrige modificando en entrega directa la Guia&amp;nbsp;T018-0001621 a estado =0 &lt;/div&gt;</t>
+          <t>&lt;div&gt;Requerimiento de Jorge Garcia &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/591421cb-3eaf-47ae-843a-b788b121d79b?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -19585,12 +19609,12 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R157" t="n">
@@ -19604,7 +19628,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>206</v>
+        <v>392</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -19613,12 +19637,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ticket 323-2 - Wapsa - Callao - Muestreo - Se registaron guias con lote CC2402 en vez de CC2401</t>
+          <t>Ticket 413 - Wapsa - Mina - Pesaje - Agregar columna en la vista y excel que se muestre el precinto de salida Callao (Precinto Cotecna)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
+          <t>WAPSA\Sprint - Febrero - 2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -19628,17 +19652,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>[Ver. 2.21]</t>
         </is>
       </c>
       <c r="G158" s="7" t="n">
-        <v>45336.79166666666</v>
+        <v>45669.79166666666</v>
       </c>
       <c r="H158" s="7" t="n">
-        <v>45336.79166666666</v>
+        <v>45669.79166666666</v>
       </c>
       <c r="I158" s="7" t="n">
-        <v>45336.79166666666</v>
+        <v>45729.79166666666</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -19647,7 +19671,7 @@
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="n">
-        <v>323</v>
+        <v>412</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -19656,7 +19680,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d259f3d5-3b11-4660-ace4-6fd3e97a17c7?fileName=image.png" alt=Image style="width:803px;height:235px;" width=803 height=235&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;i&gt;15/05: Revisar listado de guia; LC inidca que tiene fecha de muestreo del lote CC2402 pero el sistema asigno lote CC2402&lt;/i&gt; &lt;/div&gt;&lt;div&gt;&lt;i&gt;15/05: Se revisa el listado y el muestreo se grabo entre las 8 y 8:30 am del dia 26/04 por ende el sistema le asigno el lote 2402&lt;/i&gt; &lt;/div&gt;&lt;div&gt;&lt;i&gt;&lt;br&gt;&lt;/i&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Requerimiento de Jorge Garcia &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/22acfbbe-c860-40f1-b967-cb1c9276aba5?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -19666,7 +19690,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -19685,7 +19709,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>209</v>
+        <v>397</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -19694,12 +19718,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ticket 326 - Wapsa - Mina - C.Stock - la lista demora aprox 8 mintos para mostrar la informacion</t>
+          <t>Ticket 414 - Wapsa - Mina - Pesaje - Despacho - Error al intentar al preasignar despacho (Bloqueo de tablas)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero 2024</t>
+          <t>WAPSA\Sprint - Febrero - 2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -19707,15 +19731,19 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>[Ver. 2.21]</t>
+        </is>
+      </c>
       <c r="G159" s="7" t="n">
-        <v>45347.79166666666</v>
+        <v>45674.79166666666</v>
       </c>
       <c r="H159" s="7" t="n">
-        <v>45348.79166666666</v>
+        <v>45674.79166666666</v>
       </c>
       <c r="I159" s="7" t="n">
-        <v>45348.79166666666</v>
+        <v>45729.79166666666</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -19724,7 +19752,7 @@
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="n">
-        <v>326</v>
+        <v>414</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -19733,12 +19761,12 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Jorge Garcia reporta que no carga la pantalla del stock Diario. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;26/02 Se revisa listado se valida indexado y se envia correo a Jorge para verficar si ya se corrgió el listado &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;El usaurio reporta: &lt;/div&gt;&lt;div&gt;En ocasiones al&amp;nbsp; intentar preasigna un despacho el sistema tarda mas de los comun, y al final le salta una ventana de error. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/7c904542-a451-432b-95fe-d30e75e6544d?fileName=image.png" alt=Image style="width:361px;height:689px;" width=361 height=689&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Esta Venata de error es un timeout, se procede a cambiar la libreria de c#que hace el guardado en base de datos.&amp;nbsp; &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Repetitivo-en-proceso</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -19762,7 +19790,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>519</v>
+        <v>398</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -19771,12 +19799,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ticket 477 - Wapasa - Callao - Cambiar fechas de lote CT2601 y CT2602</t>
+          <t>Ticket 415 -  Wapsa - Callao - Inspeccion - No lista los vagones observados en estado pendiente</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero - 2026</t>
+          <t>WAPSA\Sprint - Febrero - 2025</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -19784,15 +19812,19 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>[Ver. 2.21]</t>
+        </is>
+      </c>
       <c r="G160" s="7" t="n">
-        <v>46051.25902777778</v>
+        <v>45680.79166666666</v>
       </c>
       <c r="H160" s="7" t="n">
-        <v>46051.25902777778</v>
+        <v>45680.79166666666</v>
       </c>
       <c r="I160" s="7" t="n">
-        <v>46057.79166666666</v>
+        <v>45729.79166666666</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -19801,27 +19833,31 @@
       </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="n">
-        <v>477</v>
+        <v>415</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Reportado por SyC Sistemas: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Deberia mostrar en la pestaña de observados aquellos vagone pendientes por aprobar observacion &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Saludos &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Repetitivo-en-proceso</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R160" t="n">
@@ -19835,7 +19871,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>521</v>
+        <v>170</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -19844,12 +19880,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ticket 479 - Wapsa - Vagón de Inspeccion Callao no se muestra en el listado</t>
+          <t>Ticket 291 - Wapsa - Callao - Inspección -  Mail de inspección observada en Callao sin data (mail en blanco)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero - 2026</t>
+          <t>WAPSA\Sprint - Enero 2024</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -19857,33 +19893,41 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>[Ver.2.13]</t>
+        </is>
+      </c>
       <c r="G161" s="7" t="n">
-        <v>46059.29791666667</v>
+        <v>45313.79166666666</v>
       </c>
       <c r="H161" s="7" t="n">
-        <v>46059.29791666667</v>
+        <v>45316.79166666666</v>
       </c>
       <c r="I161" s="7" t="n">
-        <v>46062.79166666666</v>
+        <v>45316.79166666666</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WAPSA web</t>
         </is>
       </c>
       <c r="K161" t="n">
-        <v>168258</v>
+        <v>97296</v>
       </c>
       <c r="L161" t="n">
-        <v>479</v>
+        <v>291</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mail de inspección observada en Callao sin data (mail en blanco)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -19891,7 +19935,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
+          <t>Servidor MCP</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -19910,7 +19954,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>380</v>
+        <v>172</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -19919,12 +19963,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ticket 404- Wapsa - Mina- Despacho - Correo de Dif Peso Tara del Supervisor debe indicar la palabra Supervisor en el asunto</t>
+          <t>Ticket 290 - Wapsa - Callao - Volteo - El Wapsa permitió grabar un Numero de Guía Electrónica con la letra T en minúscula en Volteo</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero - 2025</t>
+          <t>WAPSA\Sprint - Enero 2024</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -19934,26 +19978,30 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>[Ver. 2.21]</t>
+          <t>[Ver.2.13]</t>
         </is>
       </c>
       <c r="G162" s="7" t="n">
-        <v>45652.79166666666</v>
+        <v>45314.79166666666</v>
       </c>
       <c r="H162" s="7" t="n">
-        <v>45670.79166666666</v>
+        <v>45316.79166666666</v>
       </c>
       <c r="I162" s="7" t="n">
-        <v>45729.79166666666</v>
+        <v>45319.79166666666</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>WAPSA web</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>#96873</t>
+        </is>
+      </c>
       <c r="L162" t="n">
-        <v>404</v>
+        <v>290</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -19962,7 +20010,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Carlos Zenteno: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/239e17e7-f934-47a2-b07a-30038130d4c9?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El Wapsa permitió grabar un Numero de Guía Electrónica con la letra T en minúscula en Volteo&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -19972,12 +20020,12 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R162" t="n">
@@ -19991,7 +20039,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>391</v>
+        <v>504</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -20000,12 +20048,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ticket 412 - Wapsa - Mina - Inspeccion - Cambiar orden de detalle de convoy para que se muestre por fecha de inspeccion</t>
+          <t>Ticket 468 - Wapsa - Error al cargar leyes en Callao</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero - 2025</t>
+          <t>WAPSA\Sprint - Enero - 2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -20013,19 +20061,15 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>[Ver. 2.21]</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" s="7" t="n">
-        <v>45669.79166666666</v>
+        <v>45986.79166666666</v>
       </c>
       <c r="H163" s="7" t="n">
-        <v>45669.79166666666</v>
+        <v>45988.79166666666</v>
       </c>
       <c r="I163" s="7" t="n">
-        <v>45729.79166666666</v>
+        <v>46049.79166666666</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -20034,18 +20078,14 @@
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="n">
-        <v>412</v>
+        <v>468</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Requerimiento de Jorge Garcia &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/591421cb-3eaf-47ae-843a-b788b121d79b?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -20053,7 +20093,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
+          <t>Error del usuario</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -20072,7 +20112,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>392</v>
+        <v>517</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -20081,12 +20121,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ticket 413 - Wapsa - Mina - Pesaje - Agregar columna en la vista y excel que se muestre el precinto de salida Callao (Precinto Cotecna)</t>
+          <t>Ticket 475 - Wapsa - Reporte De H2OLey de Callao no esta filtrando por la fecha correcta</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero - 2025</t>
+          <t>WAPSA\Sprint - Enero - 2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -20094,28 +20134,22 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>[Ver. 2.21]</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
       <c r="G164" s="7" t="n">
-        <v>45669.79166666666</v>
+        <v>46048.33472222222</v>
       </c>
       <c r="H164" s="7" t="n">
-        <v>45669.79166666666</v>
+        <v>46048.41805555556</v>
       </c>
       <c r="I164" s="7" t="n">
-        <v>45729.79166666666</v>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+        <v>46051.29166666666</v>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="n">
+        <v>167446</v>
+      </c>
       <c r="L164" t="n">
-        <v>412</v>
+        <v>475</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
@@ -20124,7 +20158,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Requerimiento de Jorge Garcia &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/22acfbbe-c860-40f1-b967-cb1c9276aba5?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d38e1467-c27a-4dfa-8ed2-08b6d372343c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -20134,12 +20168,12 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R164" t="n">
@@ -20153,7 +20187,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -20162,12 +20196,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ticket 414 - Wapsa - Mina - Pesaje - Despacho - Error al intentar al preasignar despacho (Bloqueo de tablas)</t>
+          <t>Ticket 406 - Wapsa - Callao - Month Evidence - Core - No calcula el total de ajuste TMS y TMH incluyendo TEE</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero - 2025</t>
+          <t>WAPSA\Sprint - Enero - 2025</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -20175,19 +20209,15 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>[Ver. 2.21]</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" s="7" t="n">
-        <v>45674.79166666666</v>
+        <v>45657.79166666666</v>
       </c>
       <c r="H165" s="7" t="n">
-        <v>45674.79166666666</v>
+        <v>45659.79166666666</v>
       </c>
       <c r="I165" s="7" t="n">
-        <v>45729.79166666666</v>
+        <v>45662.79166666666</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -20196,7 +20226,7 @@
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="n">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -20205,12 +20235,12 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>&lt;div&gt;El usaurio reporta: &lt;/div&gt;&lt;div&gt;En ocasiones al&amp;nbsp; intentar preasigna un despacho el sistema tarda mas de los comun, y al final le salta una ventana de error. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/7c904542-a451-432b-95fe-d30e75e6544d?fileName=image.png" alt=Image style="width:361px;height:689px;" width=361 height=689&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Esta Venata de error es un timeout, se procede a cambiar la libreria de c#que hace el guardado en base de datos.&amp;nbsp; &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Diego cardenas reporte diferencias entre el ajus del mes de diciembre del Month Evidence Corte y del Ajuste mensual&amp;nbsp; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Repetitivo-en-proceso</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -20234,7 +20264,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -20243,12 +20273,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ticket 415 -  Wapsa - Callao - Inspeccion - No lista los vagones observados en estado pendiente</t>
+          <t>Ticket 407 - Wapsa - Callao - Arribo -  No se listan vagones disponibles para arribo cuya salida fue en Dic-2024</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Febrero - 2025</t>
+          <t>WAPSA\Sprint - Enero - 2025</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -20256,28 +20286,26 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>[Ver. 2.21]</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
       <c r="G166" s="7" t="n">
-        <v>45680.79166666666</v>
+        <v>45659.79166666666</v>
       </c>
       <c r="H166" s="7" t="n">
-        <v>45680.79166666666</v>
+        <v>45659.79166666666</v>
       </c>
       <c r="I166" s="7" t="n">
-        <v>45729.79166666666</v>
+        <v>45683.79166666666</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="n">
+        <v>129225</v>
+      </c>
       <c r="L166" t="n">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -20286,7 +20314,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Reportado por SyC Sistemas: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Deberia mostrar en la pestaña de observados aquellos vagone pendientes por aprobar observacion &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Saludos &lt;/div&gt;</t>
+          <t>&lt;div&gt;Jorge Garcia reporte: que para realizar el arribo en callao no se estan mostyrando un conjunto de vagones que se les dio salida de mina en Dic-2024 &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -20301,7 +20329,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R166" t="n">
@@ -20315,7 +20343,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>170</v>
+        <v>386</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -20324,12 +20352,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ticket 291 - Wapsa - Callao - Inspección -  Mail de inspección observada en Callao sin data (mail en blanco)</t>
+          <t>Ticket 409 - Wapsa - Callao - Traslado entre Estab. - Lista de Despachos - Error al importar despachos</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero 2024</t>
+          <t>WAPSA\Sprint - Enero - 2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -20337,30 +20365,24 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>[Ver.2.13]</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" s="7" t="n">
-        <v>45313.79166666666</v>
+        <v>45662.79166666666</v>
       </c>
       <c r="H167" s="7" t="n">
-        <v>45316.79166666666</v>
+        <v>45663.79166666666</v>
       </c>
       <c r="I167" s="7" t="n">
-        <v>45316.79166666666</v>
+        <v>45665.79166666666</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>WAPSA web</t>
-        </is>
-      </c>
-      <c r="K167" t="n">
-        <v>97296</v>
-      </c>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="n">
-        <v>291</v>
+        <v>409</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -20369,7 +20391,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Mail de inspección observada en Callao sin data (mail en blanco)&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Diego Cardenas Reporta: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/79908219-99d1-4105-b075-609490976952?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -20379,7 +20401,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Servidor MCP</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -20398,7 +20420,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>172</v>
+        <v>387</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -20407,12 +20429,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ticket 290 - Wapsa - Callao - Volteo - El Wapsa permitió grabar un Numero de Guía Electrónica con la letra T en minúscula en Volteo</t>
+          <t>Ticket 411 - Wapsa - Callao - Stock - No muestra los vagones de limpeza en el dia que corresponde de acuerdo a la fechaHora MCP (Enviado en 407)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero 2024</t>
+          <t>WAPSA\Sprint - Enero - 2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -20420,43 +20442,31 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>[Ver.2.13]</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" s="7" t="n">
-        <v>45314.79166666666</v>
+        <v>45659.79166666666</v>
       </c>
       <c r="H168" s="7" t="n">
-        <v>45316.79166666666</v>
+        <v>45663.79166666666</v>
       </c>
       <c r="I168" s="7" t="n">
-        <v>45319.79166666666</v>
+        <v>45683.79166666666</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>WAPSA web</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>#96873</t>
-        </is>
-      </c>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="n">
-        <v>290</v>
+        <v>411</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El Wapsa permitió grabar un Numero de Guía Electrónica con la letra T en minúscula en Volteo&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -20464,7 +20474,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -20483,7 +20493,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>504</v>
+        <v>399</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -20492,12 +20502,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ticket 468 - Wapsa - Error al cargar leyes en Callao</t>
+          <t>Ticket 416 - Wapsa - Mina - Pesaje - Despacho - Error en precinto duplicado de enero 2025 sublote 440 (Enviado en 417)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero - 2026</t>
+          <t>WAPSA\Sprint - Enero - 2025</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -20507,13 +20517,13 @@
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" s="7" t="n">
-        <v>45986.79166666666</v>
+        <v>45680.79166666666</v>
       </c>
       <c r="H169" s="7" t="n">
-        <v>45988.79166666666</v>
+        <v>45680.79166666666</v>
       </c>
       <c r="I169" s="7" t="n">
-        <v>46049.79166666666</v>
+        <v>45694.79166666666</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -20522,14 +20532,18 @@
       </c>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="n">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Carloz Zenteno Reporta: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;El Wapsa esta marcando este vagon como pendiente por aprobacion por precintos. &lt;/div&gt;&lt;div&gt;Pero no es posible su aprobacion o rechazo por que da error. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -20537,12 +20551,12 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R169" t="n">
@@ -20556,7 +20570,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>517</v>
+        <v>402</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -20565,12 +20579,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ticket 475 - Wapsa - Reporte De H2OLey de Callao no esta filtrando por la fecha correcta</t>
+          <t>Ticket 417 -  Wapsa - Callao - Ajuste Mensual - Operaciones de Rumas no muestran operaciones de tipo Traslado</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero - 2026</t>
+          <t>WAPSA\Sprint - Enero - 2025</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -20580,20 +20594,24 @@
       </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" s="7" t="n">
-        <v>46048.33472222222</v>
+        <v>45682.79166666666</v>
       </c>
       <c r="H170" s="7" t="n">
-        <v>46048.41805555556</v>
+        <v>45683.79166666666</v>
       </c>
       <c r="I170" s="7" t="n">
-        <v>46051.29166666666</v>
-      </c>
-      <c r="J170" t="inlineStr"/>
+        <v>45694.79166666666</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
       <c r="K170" t="n">
-        <v>167446</v>
+        <v>129857</v>
       </c>
       <c r="L170" t="n">
-        <v>475</v>
+        <v>417</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -20602,7 +20620,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d38e1467-c27a-4dfa-8ed2-08b6d372343c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Diego CArdenas Reporta: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/2a464ff7-0863-4280-a9ed-1e801431e10c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -20631,7 +20649,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -20640,7 +20658,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ticket 406 - Wapsa - Callao - Month Evidence - Core - No calcula el total de ajuste TMS y TMH incluyendo TEE</t>
+          <t>Ticket 418 - Wapsa - Callao - C.Stock - Cambio de columna  Fecha Stock por lentitud del reporte</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20655,33 +20673,31 @@
       </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" s="7" t="n">
-        <v>45657.79166666666</v>
+        <v>45687.79166666666</v>
       </c>
       <c r="H171" s="7" t="n">
-        <v>45659.79166666666</v>
+        <v>45687.79166666666</v>
       </c>
       <c r="I171" s="7" t="n">
-        <v>45662.79166666666</v>
+        <v>45688.79166666666</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="n">
+        <v>129908</v>
+      </c>
       <c r="L171" t="n">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Diego cardenas reporte diferencias entre el ajus del mes de diciembre del Month Evidence Corte y del Ajuste mensual&amp;nbsp; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -20708,7 +20724,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>383</v>
+        <v>492</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -20717,12 +20733,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ticket 407 - Wapsa - Callao - Arribo -  No se listan vagones disponibles para arribo cuya salida fue en Dic-2024</t>
+          <t>Ticket 460 - Wapsa - Mina - Politica de reintentos/Cambio Conexion al momento de captura de peso Mina</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero - 2025</t>
+          <t>WAPSA\Sprint - Diciembre - 2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -20730,26 +20746,26 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>[Ver 2.26]</t>
+        </is>
+      </c>
       <c r="G172" s="7" t="n">
-        <v>45659.79166666666</v>
+        <v>45963.79166666666</v>
       </c>
       <c r="H172" s="7" t="n">
-        <v>45659.79166666666</v>
-      </c>
-      <c r="I172" s="7" t="n">
-        <v>45683.79166666666</v>
-      </c>
+        <v>45987.43333333333</v>
+      </c>
+      <c r="I172" s="7" t="n"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K172" t="n">
-        <v>129225</v>
-      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="n">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -20758,7 +20774,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Jorge Garcia reporte: que para realizar el arribo en callao no se estan mostyrando un conjunto de vagones que se les dio salida de mina en Dic-2024 &lt;/div&gt;</t>
+          <t>&lt;div&gt;Regirsra en el Mastyro de Parametrps de conexion el tiempo de delay: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -20773,7 +20789,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R172" t="n">
@@ -20787,7 +20803,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>386</v>
+        <v>497</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -20796,12 +20812,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ticket 409 - Wapsa - Callao - Traslado entre Estab. - Lista de Despachos - Error al importar despachos</t>
+          <t>Ticket 462 - Wapsa - Callao - Nuevas columas Reporte de H2OyLey Callao</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero - 2025</t>
+          <t>WAPSA\Sprint - Diciembre - 2025</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -20809,16 +20825,18 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>[Ver 2.26]</t>
+        </is>
+      </c>
       <c r="G173" s="7" t="n">
-        <v>45662.79166666666</v>
+        <v>45944.79166666666</v>
       </c>
       <c r="H173" s="7" t="n">
-        <v>45663.79166666666</v>
-      </c>
-      <c r="I173" s="7" t="n">
-        <v>45665.79166666666</v>
-      </c>
+        <v>45951.79166666666</v>
+      </c>
+      <c r="I173" s="7" t="n"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -20826,7 +20844,7 @@
       </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="n">
-        <v>409</v>
+        <v>462</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -20835,7 +20853,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Diego Cardenas Reporta: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/79908219-99d1-4105-b075-609490976952?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;span style="box-sizing:border-box;"&gt;- Habilitar 4 columnas de información en el reporte de H2OyLey Callao de Wapsa; grupos (G1,G2,G3,G4) para recibir la data de Cotecna&lt;/span&gt; &lt;/div&gt;&lt;div style="box-sizing:border-box;"&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -20850,7 +20868,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R173" t="n">
@@ -20864,7 +20882,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>387</v>
+        <v>498</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -20873,12 +20891,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ticket 411 - Wapsa - Callao - Stock - No muestra los vagones de limpeza en el dia que corresponde de acuerdo a la fechaHora MCP (Enviado en 407)</t>
+          <t>Ticket 463 - WapsaBI - Habilitar las 4 columnas en el dashboard (HumedadesyLeyes)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero - 2025</t>
+          <t>WAPSA\Sprint - Diciembre - 2025</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -20888,22 +20906,22 @@
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" s="7" t="n">
-        <v>45659.79166666666</v>
+        <v>45963.79166666666</v>
       </c>
       <c r="H174" s="7" t="n">
-        <v>45663.79166666666</v>
+        <v>45979.79166666666</v>
       </c>
       <c r="I174" s="7" t="n">
-        <v>45683.79166666666</v>
+        <v>46008.79166666666</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>Wapsa BI</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="n">
-        <v>411</v>
+        <v>463</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -20918,12 +20936,12 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R174" t="n">
@@ -20937,7 +20955,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -20946,12 +20964,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ticket 416 - Wapsa - Mina - Pesaje - Despacho - Error en precinto duplicado de enero 2025 sublote 440 (Enviado en 417)</t>
+          <t>Ticket 461 - Wapsa - Mina - Revision Correlativo de Sublote Pesaje</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero - 2025</t>
+          <t>WAPSA\Sprint - Diciembre - 2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -20959,16 +20977,18 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>[Ver 2.26]</t>
+        </is>
+      </c>
       <c r="G175" s="7" t="n">
-        <v>45680.79166666666</v>
+        <v>45908.79166666666</v>
       </c>
       <c r="H175" s="7" t="n">
-        <v>45680.79166666666</v>
-      </c>
-      <c r="I175" s="7" t="n">
-        <v>45694.79166666666</v>
-      </c>
+        <v>45930.79166666666</v>
+      </c>
+      <c r="I175" s="7" t="n"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -20976,18 +20996,14 @@
       </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="n">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Carloz Zenteno Reporta: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;El Wapsa esta marcando este vagon como pendiente por aprobacion por precintos. &lt;/div&gt;&lt;div&gt;Pero no es posible su aprobacion o rechazo por que da error. &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21000,7 +21016,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R175" t="n">
@@ -21014,7 +21030,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>402</v>
+        <v>500</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -21023,12 +21039,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ticket 417 -  Wapsa - Callao - Ajuste Mensual - Operaciones de Rumas no muestran operaciones de tipo Traslado</t>
+          <t>Ticket 464 - Wapsa - Gestor de Guias de Remision - Filtro Otros</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero - 2025</t>
+          <t>WAPSA\Sprint - Diciembre - 2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -21036,37 +21052,33 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>[Ver 2.26]</t>
+        </is>
+      </c>
       <c r="G176" s="7" t="n">
-        <v>45682.79166666666</v>
+        <v>45936.79166666666</v>
       </c>
       <c r="H176" s="7" t="n">
-        <v>45683.79166666666</v>
-      </c>
-      <c r="I176" s="7" t="n">
-        <v>45694.79166666666</v>
-      </c>
+        <v>45950.79166666666</v>
+      </c>
+      <c r="I176" s="7" t="n"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K176" t="n">
-        <v>129857</v>
-      </c>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="n">
-        <v>417</v>
+        <v>464</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Diego CArdenas Reporta: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/2a464ff7-0863-4280-a9ed-1e801431e10c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21079,7 +21091,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R176" t="n">
@@ -21093,7 +21105,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>403</v>
+        <v>501</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -21102,12 +21114,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ticket 418 - Wapsa - Callao - C.Stock - Cambio de columna  Fecha Stock por lentitud del reporte</t>
+          <t>Ticket 465 - Wapsa - Mina - Ajuste emision de guias por error anulación en sublotes 2530 al 2533 CT2511</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Enero - 2025</t>
+          <t>WAPSA\Sprint - Diciembre - 2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -21117,24 +21129,20 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" s="7" t="n">
-        <v>45687.79166666666</v>
+        <v>45995.79166666666</v>
       </c>
       <c r="H177" s="7" t="n">
-        <v>45687.79166666666</v>
-      </c>
-      <c r="I177" s="7" t="n">
-        <v>45688.79166666666</v>
-      </c>
+        <v>46006.29166666666</v>
+      </c>
+      <c r="I177" s="7" t="n"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K177" t="n">
-        <v>129908</v>
-      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="n">
-        <v>418</v>
+        <v>465</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -21149,12 +21157,12 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>Omisión del usuario</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R177" t="n">
@@ -21168,7 +21176,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -21177,7 +21185,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ticket 460 - Wapsa - Mina - Politica de reintentos/Cambio Conexion al momento de captura de peso Mina</t>
+          <t>Ticket 466 - Wapsa - Monitor - Ajuste en sumatoria de totales de Dashboard de Despachos</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21196,10 +21204,10 @@
         </is>
       </c>
       <c r="G178" s="7" t="n">
-        <v>45963.79166666666</v>
+        <v>45970.79166666666</v>
       </c>
       <c r="H178" s="7" t="n">
-        <v>45987.43333333333</v>
+        <v>45974.51111111111</v>
       </c>
       <c r="I178" s="7" t="n"/>
       <c r="J178" t="inlineStr">
@@ -21209,18 +21217,14 @@
       </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Regirsra en el Mastyro de Parametrps de conexion el tiempo de delay: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21233,7 +21237,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R178" t="n">
@@ -21247,7 +21251,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -21256,7 +21260,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ticket 462 - Wapsa - Callao - Nuevas columas Reporte de H2OyLey Callao</t>
+          <t>Ticket 467 - Wapsa - Habilitar las 4 columnas en el dashboard (HumedadesyLeyes)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21275,10 +21279,10 @@
         </is>
       </c>
       <c r="G179" s="7" t="n">
-        <v>45944.79166666666</v>
+        <v>45981.79166666666</v>
       </c>
       <c r="H179" s="7" t="n">
-        <v>45951.79166666666</v>
+        <v>46006.43541666667</v>
       </c>
       <c r="I179" s="7" t="n"/>
       <c r="J179" t="inlineStr">
@@ -21288,18 +21292,14 @@
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;span style="box-sizing:border-box;"&gt;- Habilitar 4 columnas de información en el reporte de H2OyLey Callao de Wapsa; grupos (G1,G2,G3,G4) para recibir la data de Cotecna&lt;/span&gt; &lt;/div&gt;&lt;div style="box-sizing:border-box;"&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21326,7 +21326,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>498</v>
+        <v>368</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ticket 463 - WapsaBI - Habilitar las 4 columnas en el dashboard (HumedadesyLeyes)</t>
+          <t>Ticket 399 - Wapsa - Mina - Pesaje - Modificar frecuencia notificacion de despachos pendientes por aprobar por supervisor</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2025</t>
+          <t>WAPSA\Sprint - Diciembre - 2024</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -21350,29 +21350,35 @@
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" s="7" t="n">
-        <v>45963.79166666666</v>
+        <v>45628.79166666666</v>
       </c>
       <c r="H180" s="7" t="n">
-        <v>45979.79166666666</v>
+        <v>45628.79166666666</v>
       </c>
       <c r="I180" s="7" t="n">
-        <v>46008.79166666666</v>
+        <v>45652.79166666666</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Wapsa BI</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>126521</v>
+      </c>
       <c r="L180" t="n">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Carlos Zentenos Solicita: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;-Cambiar la frecuencia con la cual le llega el mail de recordatorio de aprobar un despacho pendiente por parte del supervisor cuando existe diferencias de taras, actualmente se enva cada 4 horas ´si hay alguno pendiente, solicita que se reprograme para llegar a las 10 am solo una vez al dia &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Nombre del JOB:&amp;nbsp;Envio_Notificaciones_Pesaje_Pendiente_Supervisor &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O180" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21380,12 +21386,12 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R180" t="n">
@@ -21399,7 +21405,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>499</v>
+        <v>373</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -21408,12 +21414,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ticket 461 - Wapsa - Mina - Revision Correlativo de Sublote Pesaje</t>
+          <t>Ticket 401 - Wapsa - Callao - Ajuste Mensual - El listado de Facturas/Notas no debe sumar NC/ND que pertenezcan a ventas documentarias</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2025</t>
+          <t>WAPSA\Sprint - Diciembre - 2024</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -21421,33 +21427,37 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>[Ver 2.26]</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" s="7" t="n">
-        <v>45908.79166666666</v>
+        <v>45642.79166666666</v>
       </c>
       <c r="H181" s="7" t="n">
-        <v>45930.79166666666</v>
-      </c>
-      <c r="I181" s="7" t="n"/>
+        <v>45652.79166666666</v>
+      </c>
+      <c r="I181" s="7" t="n">
+        <v>45651.79166666666</v>
+      </c>
       <c r="J181" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="n">
+        <v>126514</v>
+      </c>
       <c r="L181" t="n">
-        <v>461</v>
+        <v>401</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;El usuario Diego Cardenas Reporta: &lt;/div&gt;&lt;div&gt;Que los comprobantes a contnuacion no debeerian aparecer con montos sumando o restando debido a que son NC de Ventas documentarias &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/4bfdcd75-3aef-46e2-8c51-73cc6f19884c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21455,12 +21465,12 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R181" t="n">
@@ -21474,7 +21484,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>500</v>
+        <v>381</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -21483,12 +21493,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ticket 464 - Wapsa - Gestor de Guias de Remision - Filtro Otros</t>
+          <t>Ticket 405 - Wapsa - Callao - Ajuste Mensual - No totaliza correctamente el TMS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2025</t>
+          <t>WAPSA\Sprint - Diciembre - 2024</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -21498,16 +21508,18 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>[Ver 2.26]</t>
+          <t>[Ver. 2.19]</t>
         </is>
       </c>
       <c r="G182" s="7" t="n">
-        <v>45936.79166666666</v>
+        <v>45652.79166666666</v>
       </c>
       <c r="H182" s="7" t="n">
-        <v>45950.79166666666</v>
-      </c>
-      <c r="I182" s="7" t="n"/>
+        <v>45652.79166666666</v>
+      </c>
+      <c r="I182" s="7" t="n">
+        <v>45655.79166666666</v>
+      </c>
       <c r="J182" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21515,14 +21527,18 @@
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="n">
-        <v>464</v>
+        <v>405</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Diego cardenas reporta que el Wapsa presenta un error cuando totaliza la columna TMS de ajuste mensual en al seccion final: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/a0b16eb3-2b0c-4ecc-bc9a-99301ad577a6?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21530,12 +21546,12 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R182" t="n">
@@ -21549,7 +21565,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>501</v>
+        <v>445</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -21558,12 +21574,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Ticket 465 - Wapsa - Mina - Ajuste emision de guias por error anulación en sublotes 2530 al 2533 CT2511</t>
+          <t>Ticket 440- Wapsa - Mina - UBICACIÓN DE VAGONES - Corrección Listado de Vagones</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2025</t>
+          <t>WAPSA\Sprint - Agosto - 2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -21571,12 +21587,16 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>[Ver 2.24]</t>
+        </is>
+      </c>
       <c r="G183" s="7" t="n">
-        <v>45995.79166666666</v>
+        <v>45820.79166666666</v>
       </c>
       <c r="H183" s="7" t="n">
-        <v>46006.29166666666</v>
+        <v>45823.79166666666</v>
       </c>
       <c r="I183" s="7" t="n"/>
       <c r="J183" t="inlineStr">
@@ -21586,14 +21606,18 @@
       </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="n">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;El listado de vagones no muestra información más alla de un rango de tres meses &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21601,7 +21625,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Omisión del usuario</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -21620,7 +21644,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>502</v>
+        <v>282</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -21629,12 +21653,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Ticket 466 - Wapsa - Monitor - Ajuste en sumatoria de totales de Dashboard de Despachos</t>
+          <t>Ticket 364 - Wapsa - Callao - Lista Despacho - El filtro por IE's en estado abierto no muestra las que tiene peso = 0</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2025</t>
+          <t>WAPSA\Sprint - Agosto - 2024</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -21644,16 +21668,18 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>[Ver 2.26]</t>
+          <t>[Ver. 2.17]</t>
         </is>
       </c>
       <c r="G184" s="7" t="n">
-        <v>45970.79166666666</v>
+        <v>45481.79166666666</v>
       </c>
       <c r="H184" s="7" t="n">
-        <v>45974.51111111111</v>
-      </c>
-      <c r="I184" s="7" t="n"/>
+        <v>45481.79166666666</v>
+      </c>
+      <c r="I184" s="7" t="n">
+        <v>45481.79166666666</v>
+      </c>
       <c r="J184" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -21661,14 +21687,18 @@
       </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="n">
-        <v>466</v>
+        <v>364</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Wally Reporta &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/616c5f86-3724-46e2-9b51-448e347b952e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;09/07 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Corregido. Se agrega archivo script a la espera de enviar correcion a TICA &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21676,7 +21706,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -21695,7 +21725,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>503</v>
+        <v>291</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -21704,12 +21734,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ticket 467 - Wapsa - Habilitar las 4 columnas en el dashboard (HumedadesyLeyes)</t>
+          <t>Ticket 368 - Wapsa - General - Copia de Base de datos de WAPSA y TRADER de Testing y Desarrollo</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2025</t>
+          <t>WAPSA\Sprint - Agosto - 2024</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -21717,33 +21747,37 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>[Ver 2.26]</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" s="7" t="n">
-        <v>45981.79166666666</v>
+        <v>45490.79166666666</v>
       </c>
       <c r="H185" s="7" t="n">
-        <v>46006.43541666667</v>
-      </c>
-      <c r="I185" s="7" t="n"/>
+        <v>45490.79166666666</v>
+      </c>
+      <c r="I185" s="7" t="n">
+        <v>45508.79166666666</v>
+      </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="n">
+        <v>112853</v>
+      </c>
       <c r="L185" t="n">
-        <v>467</v>
+        <v>368</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Nicolas Solicita: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/83d4dfa7-68b5-42c5-91e2-b9b948bcc469?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -21751,7 +21785,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Servidor MCP</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -21770,7 +21804,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>368</v>
+        <v>296</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -21779,12 +21813,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ticket 399 - Wapsa - Mina - Pesaje - Modificar frecuencia notificacion de despachos pendientes por aprobar por supervisor</t>
+          <t>Ticket 370 - Wapsa - Mina - Pesaje - Despachos - Texto incorrecto en el campo Tipo de Pesaje Manual Tara</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2024</t>
+          <t>WAPSA\Sprint - Agosto - 2024</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -21794,13 +21828,13 @@
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" s="7" t="n">
-        <v>45628.79166666666</v>
+        <v>45505.79166666666</v>
       </c>
       <c r="H186" s="7" t="n">
-        <v>45628.79166666666</v>
+        <v>45505.79166666666</v>
       </c>
       <c r="I186" s="7" t="n">
-        <v>45652.79166666666</v>
+        <v>45525.79166666666</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -21808,10 +21842,10 @@
         </is>
       </c>
       <c r="K186" t="n">
-        <v>126521</v>
+        <v>115970</v>
       </c>
       <c r="L186" t="n">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -21820,7 +21854,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Carlos Zentenos Solicita: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;-Cambiar la frecuencia con la cual le llega el mail de recordatorio de aprobar un despacho pendiente por parte del supervisor cuando existe diferencias de taras, actualmente se enva cada 4 horas ´si hay alguno pendiente, solicita que se reprograme para llegar a las 10 am solo una vez al dia &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Nombre del JOB:&amp;nbsp;Envio_Notificaciones_Pesaje_Pendiente_Supervisor &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Luis Casas Reporta &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/b2479b90-17f9-4c69-bcb0-35b6c498b045?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Preparar Formatos Tickets &lt;/div&gt;&lt;div&gt;08/08 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Enviado a TICA &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -21835,7 +21869,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R186" t="n">
@@ -21849,7 +21883,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>373</v>
+        <v>300</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -21858,12 +21892,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ticket 401 - Wapsa - Callao - Ajuste Mensual - El listado de Facturas/Notas no debe sumar NC/ND que pertenezcan a ventas documentarias</t>
+          <t>Ticket 372 - Wapsa Movil - General - Actualización de Apk en los equipos de Callao(Cotecna)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2024</t>
+          <t>WAPSA\Sprint - Agosto - 2024</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -21873,24 +21907,22 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" s="7" t="n">
-        <v>45642.79166666666</v>
+        <v>45526.79166666666</v>
       </c>
       <c r="H187" s="7" t="n">
-        <v>45652.79166666666</v>
+        <v>45529.79166666666</v>
       </c>
       <c r="I187" s="7" t="n">
-        <v>45651.79166666666</v>
+        <v>45529.79166666666</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K187" t="n">
-        <v>126514</v>
-      </c>
+          <t>Wapsa Movil</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="n">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
@@ -21899,7 +21931,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>&lt;div&gt;El usuario Diego Cardenas Reporta: &lt;/div&gt;&lt;div&gt;Que los comprobantes a contnuacion no debeerian aparecer con montos sumando o restando debido a que son NC de Ventas documentarias &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/4bfdcd75-3aef-46e2-8c51-73cc6f19884c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Se inslara el dia Lunes 26/08 &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -21909,12 +21941,12 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R187" t="n">
@@ -21928,7 +21960,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>381</v>
+        <v>305</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -21937,12 +21969,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Ticket 405 - Wapsa - Callao - Ajuste Mensual - No totaliza correctamente el TMS</t>
+          <t>Ticket 373 - Wapsa - Callao - Asignacion - Ruma no visualizada en el listado para Muestreo</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Diciembre - 2024</t>
+          <t>WAPSA\Sprint - Agosto - 2024</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -21950,19 +21982,15 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>[Ver. 2.19]</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" s="7" t="n">
-        <v>45652.79166666666</v>
+        <v>45528.79166666666</v>
       </c>
       <c r="H188" s="7" t="n">
-        <v>45652.79166666666</v>
+        <v>45528.79166666666</v>
       </c>
       <c r="I188" s="7" t="n">
-        <v>45655.79166666666</v>
+        <v>45528.79166666666</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -21971,16 +21999,16 @@
       </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="n">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Diego cardenas reporta que el Wapsa presenta un error cuando totaliza la columna TMS de ajuste mensual en al seccion final: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/a0b16eb3-2b0c-4ecc-bc9a-99301ad577a6?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Luis casas reporta &lt;/div&gt;&lt;div&gt;Que una ruma nose visualiza en: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/5b2218a2-9772-4327-b767-0a4325cb7645?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;25/08 &lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;Solucionado. Configuración de tipo muestro para el almacen modulo &amp;quot;Configuración - Conf. Tipo Muestreo&amp;quot; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -21990,12 +22018,12 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>Omisión del usuario</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R188" t="n">
@@ -22009,7 +22037,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>445</v>
+        <v>222</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -22018,12 +22046,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ticket 440- Wapsa - Mina - UBICACIÓN DE VAGONES - Corrección Listado de Vagones</t>
+          <t>Ticket 332 - Wapsa - Callao - Lista Despacho - Error en plantilla correo de JOB Factor Pesos</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Agosto - 2025</t>
+          <t>WAPSA\Sprint - Abril -2024</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -22031,26 +22059,26 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>[Ver 2.24]</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" s="7" t="n">
-        <v>45820.79166666666</v>
+        <v>45388.79166666666</v>
       </c>
       <c r="H189" s="7" t="n">
-        <v>45823.79166666666</v>
-      </c>
-      <c r="I189" s="7" t="n"/>
+        <v>45388.79166666666</v>
+      </c>
+      <c r="I189" s="7" t="n">
+        <v>45397.79166666666</v>
+      </c>
       <c r="J189" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="n">
+        <v>103860</v>
+      </c>
       <c r="L189" t="n">
-        <v>440</v>
+        <v>332</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -22059,7 +22087,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>&lt;div&gt;El listado de vagones no muestra información más alla de un rango de tres meses &lt;/div&gt;</t>
+          <t>&lt;div&gt;EL JOB en produccion envia el mail periodicamente pero con error al mostrar la plantilla&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/dad51db9-b8bd-4219-a98e-6f5ae5ceb9f1?fileName=image.png" alt=Image style="width:444px;height:370px;" width=444 height=370&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;08/04: &lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;Corrige script para enviarlo como Ticket &lt;/div&gt;&lt;div&gt;08/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se envia a Alejandro para firma &lt;/div&gt;&lt;div&gt;09/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Enviado a TICA &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -22069,12 +22097,12 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R189" t="n">
@@ -22088,7 +22116,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -22097,12 +22125,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ticket 364 - Wapsa - Callao - Lista Despacho - El filtro por IE's en estado abierto no muestra las que tiene peso = 0</t>
+          <t>Ticket 334 - Wapsa - Mina - Pesaje - Error en el listado de vagones observados en Mina</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Agosto - 2024</t>
+          <t>WAPSA\Sprint - Abril -2024</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -22110,28 +22138,26 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>[Ver. 2.17]</t>
-        </is>
-      </c>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" s="7" t="n">
-        <v>45481.79166666666</v>
+        <v>45392.79166666666</v>
       </c>
       <c r="H190" s="7" t="n">
-        <v>45481.79166666666</v>
+        <v>45399.79166666666</v>
       </c>
       <c r="I190" s="7" t="n">
-        <v>45481.79166666666</v>
+        <v>45404.79166666666</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="n">
+        <v>104784</v>
+      </c>
       <c r="L190" t="n">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -22140,22 +22166,22 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Wally Reporta &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/616c5f86-3724-46e2-9b51-448e347b952e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;09/07 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Corregido. Se agrega archivo script a la espera de enviar correcion a TICA &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;No se muestran los datos iguales en la misma pantalla de vagones normales y observados &lt;/div&gt;&lt;div&gt;Observados: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d5db6e3f-95e1-4b04-9440-47f2781682c0?fileName=image.png" alt=Image style="width:226px;height:230px;" width=226 height=230&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Normales: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/00e8a42b-a9c8-47ef-9c49-e66926e44bc2?fileName=image.png" alt=Image style="width:231px;height:180px;" width=231 height=180&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;11/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se envia Formato para la firma &lt;/div&gt;&lt;div&gt;15/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se recibe firma por parte de AM, se envia a TICA&amp;nbsp; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Repetitivo-en-proceso</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R190" t="n">
@@ -22169,7 +22195,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>291</v>
+        <v>227</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -22178,12 +22204,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Ticket 368 - Wapsa - General - Copia de Base de datos de WAPSA y TRADER de Testing y Desarrollo</t>
+          <t>Ticket 337 - Wapsa - Callao - Lista Despacho - Alerta despachos pesos 0 no manda todas las IE's de los dos ultimos meses</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Agosto - 2024</t>
+          <t>WAPSA\Sprint - Abril -2024</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -22193,24 +22219,24 @@
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" s="7" t="n">
-        <v>45490.79166666666</v>
+        <v>45397.79166666666</v>
       </c>
       <c r="H191" s="7" t="n">
-        <v>45490.79166666666</v>
+        <v>45397.79166666666</v>
       </c>
       <c r="I191" s="7" t="n">
-        <v>45508.79166666666</v>
+        <v>45404.79166666666</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WAPSA Web</t>
         </is>
       </c>
       <c r="K191" t="n">
-        <v>112853</v>
+        <v>104786</v>
       </c>
       <c r="L191" t="n">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -22219,22 +22245,22 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Nicolas Solicita: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/83d4dfa7-68b5-42c5-91e2-b9b948bcc469?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El usuario notifico que no se estan enviando todas las IE's con peso 0 de los utimos dos meses &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se valido en el script que se estaban usando valores en duro para consultar los lotes, se procedio a hacerlos dinamicos y que coja los dos ultimos lotes &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Repetitivo-en-proceso</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Servidor MCP</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R191" t="n">
@@ -22248,7 +22274,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>296</v>
+        <v>232</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -22257,12 +22283,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ticket 370 - Wapsa - Mina - Pesaje - Despachos - Texto incorrecto en el campo Tipo de Pesaje Manual Tara</t>
+          <t>Ticket 342 - Wapsa - Callao - Ajuste Mensual - Error en datos de la IE 280/24 Ruma R24-004</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Agosto - 2024</t>
+          <t>WAPSA\Sprint - Abril -2024</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -22272,24 +22298,22 @@
       </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" s="7" t="n">
-        <v>45505.79166666666</v>
+        <v>45407.79166666666</v>
       </c>
       <c r="H192" s="7" t="n">
-        <v>45505.79166666666</v>
+        <v>45407.79166666666</v>
       </c>
       <c r="I192" s="7" t="n">
-        <v>45525.79166666666</v>
+        <v>45413.79166666666</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K192" t="n">
-        <v>115970</v>
-      </c>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="n">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -22298,22 +22322,22 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Luis Casas Reporta &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/b2479b90-17f9-4c69-bcb0-35b6c498b045?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Preparar Formatos Tickets &lt;/div&gt;&lt;div&gt;08/08 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Enviado a TICA &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/127ab7ed-9b0d-4ebb-b753-311b6ea49cd3?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;26-04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se revisa con &lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp; y el error se debe a que han importado con datos incorrectos los datos de los pesos para la IE&amp;nbsp;280/24 &lt;/div&gt;&lt;div&gt;\ &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Repetitivo-en-proceso</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R192" t="n">
@@ -22327,7 +22351,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -22336,12 +22360,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ticket 372 - Wapsa Movil - General - Actualización de Apk en los equipos de Callao(Cotecna)</t>
+          <t>Ticket 343 - Wapsa - Callao - Lista de Despachos - Error en el listado de detalle de pesos de la IE 0052/24</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Agosto - 2024</t>
+          <t>WAPSA\Sprint - Abril -2024</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -22351,22 +22375,24 @@
       </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" s="7" t="n">
-        <v>45526.79166666666</v>
+        <v>45407.79166666666</v>
       </c>
       <c r="H193" s="7" t="n">
-        <v>45529.79166666666</v>
+        <v>45413.79166666666</v>
       </c>
       <c r="I193" s="7" t="n">
-        <v>45529.79166666666</v>
+        <v>45413.79166666666</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Wapsa Movil</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>105866</v>
+      </c>
       <c r="L193" t="n">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -22375,22 +22401,22 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Se inslara el dia Lunes 26/08 &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/39d13485-8e1d-4bbd-b8dd-f77172463a30?fileName=image.png" alt=Image style="width:446px;height:315px;" width=446 height=315&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;26-04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se intenta listar la IE 280/24 si sale la lista vacia se crea validacion para que liste correctamente &lt;/div&gt;&lt;div&gt;26-04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se soluciona el Ticket y se envia formato a AM para firma &lt;/div&gt;&lt;div&gt;29-04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se envia PDF firmado por AM a TICA &lt;/div&gt;&lt;div&gt;02/05 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Alexander envia para firmas internas &lt;/div&gt;&lt;div&gt;02/05 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Resuelto &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Repetitivo-en-proceso</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R193" t="n">
@@ -22404,7 +22430,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>305</v>
+        <v>340</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -22413,29 +22439,25 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ticket 373 - Wapsa - Callao - Asignacion - Ruma no visualizada en el listado para Muestreo</t>
+          <t>Ticket 384 - Wapsa - General - Configuracion -  Crear Modulo para guardar las plantilla de importacion de datos</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Agosto - 2024</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" s="7" t="n">
-        <v>45528.79166666666</v>
-      </c>
-      <c r="H194" s="7" t="n">
-        <v>45528.79166666666</v>
-      </c>
-      <c r="I194" s="7" t="n">
-        <v>45528.79166666666</v>
-      </c>
+        <v>45951.79166666666</v>
+      </c>
+      <c r="H194" s="7" t="n"/>
+      <c r="I194" s="7" t="n"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -22443,18 +22465,14 @@
       </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="n">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Luis casas reporta &lt;/div&gt;&lt;div&gt;Que una ruma nose visualiza en: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/5b2218a2-9772-4327-b767-0a4325cb7645?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;25/08 &lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;Solucionado. Configuración de tipo muestro para el almacen modulo &amp;quot;Configuración - Conf. Tipo Muestreo&amp;quot; &lt;/div&gt;</t>
-        </is>
-      </c>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -22462,7 +22480,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Omisión del usuario</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -22481,7 +22499,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>222</v>
+        <v>377</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -22490,39 +22508,35 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ticket 332 - Wapsa - Callao - Lista Despacho - Error en plantilla correo de JOB Factor Pesos</t>
+          <t>Ticket 402 - Wapsa - Callao - E. Shipments - Cuando ocurre un bloqueo al obtener data del Trader Wapsa no muestra el error</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Abril -2024</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" s="7" t="n">
-        <v>45388.79166666666</v>
+        <v>45642.79166666666</v>
       </c>
       <c r="H195" s="7" t="n">
-        <v>45388.79166666666</v>
-      </c>
-      <c r="I195" s="7" t="n">
-        <v>45397.79166666666</v>
-      </c>
+        <v>45642.79166666666</v>
+      </c>
+      <c r="I195" s="7" t="n"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K195" t="n">
-        <v>103860</v>
-      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="n">
-        <v>332</v>
+        <v>402</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -22531,7 +22545,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>&lt;div&gt;EL JOB en produccion envia el mail periodicamente pero con error al mostrar la plantilla&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/dad51db9-b8bd-4219-a98e-6f5ae5ceb9f1?fileName=image.png" alt=Image style="width:444px;height:370px;" width=444 height=370&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;08/04: &lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;Corrige script para enviarlo como Ticket &lt;/div&gt;&lt;div&gt;08/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se envia a Alejandro para firma &lt;/div&gt;&lt;div&gt;09/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Enviado a TICA &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Cuando se obtienen datos desde el Trader y se genrea algun tipo de error de bloqueo o comunicacion entra ambas Bd's no se muestra: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/c3f5d344-76e8-4365-9a52-10b27bb70854?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -22541,12 +22555,12 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R195" t="n">
@@ -22560,7 +22574,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>224</v>
+        <v>450</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -22569,12 +22583,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ticket 334 - Wapsa - Mina - Pesaje - Error en el listado de vagones observados en Mina</t>
+          <t>Ticket 442 - Wapsa - Stock Callao - Error en calculo de TMH en listado detalle por día</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Abril -2024</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -22582,40 +22596,44 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>[Ver 2.24]</t>
+        </is>
+      </c>
       <c r="G196" s="7" t="n">
-        <v>45392.79166666666</v>
+        <v>45845.25347222222</v>
       </c>
       <c r="H196" s="7" t="n">
-        <v>45399.79166666666</v>
-      </c>
-      <c r="I196" s="7" t="n">
-        <v>45404.79166666666</v>
-      </c>
+        <v>45845.79166666666</v>
+      </c>
+      <c r="I196" s="7" t="n"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K196" t="n">
-        <v>104784</v>
-      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="n">
-        <v>334</v>
+        <v>442</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>&lt;div&gt;No se muestran los datos iguales en la misma pantalla de vagones normales y observados &lt;/div&gt;&lt;div&gt;Observados: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d5db6e3f-95e1-4b04-9440-47f2781682c0?fileName=image.png" alt=Image style="width:226px;height:230px;" width=226 height=230&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Normales: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/00e8a42b-a9c8-47ef-9c49-e66926e44bc2?fileName=image.png" alt=Image style="width:231px;height:180px;" width=231 height=180&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;11/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se envia Formato para la firma &lt;/div&gt;&lt;div&gt;15/04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se recibe firma por parte de AM, se envia a TICA&amp;nbsp; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;p style="margin:0cm;font-size:11pt;font-family:Calibri, sans-serif;"&gt;Este ticket tiene como objetivo atender el requerimiento de
+Diego Cárdenas el cual ha detecto que se debe cambiar la fecha que utiliza el
+Wapsa para obtener el listado de stock por día, ahora debe utilizar la fecha de
+proceso según calendario; para que los valores de TMH cuadren correctamente con
+la de otros reportes. &lt;/p&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>Repetitivo-en-proceso</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -22625,7 +22643,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R196" t="n">
@@ -22639,7 +22657,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>227</v>
+        <v>518</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -22648,63 +22666,59 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ticket 337 - Wapsa - Callao - Lista Despacho - Alerta despachos pesos 0 no manda todas las IE's de los dos ultimos meses</t>
+          <t>Ticket 476 - Wapsa -Varios - Mejora Listado para elegir vagones en Arribo, Entrega y Salida</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Abril -2024</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr"/>
+          <t>Resuelto</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>[Ver. 2.29]</t>
+        </is>
+      </c>
       <c r="G197" s="7" t="n">
-        <v>45397.79166666666</v>
+        <v>46047.79166666666</v>
       </c>
       <c r="H197" s="7" t="n">
-        <v>45397.79166666666</v>
-      </c>
-      <c r="I197" s="7" t="n">
-        <v>45404.79166666666</v>
-      </c>
+        <v>46104.26111111111</v>
+      </c>
+      <c r="I197" s="7" t="n"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>WAPSA Web</t>
-        </is>
-      </c>
-      <c r="K197" t="n">
-        <v>104786</v>
-      </c>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="n">
-        <v>337</v>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;El usuario notifico que no se estan enviando todas las IE's con peso 0 de los utimos dos meses &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;Se valido en el script que se estaban usando valores en duro para consultar los lotes, se procedio a hacerlos dinamicos y que coja los dos ultimos lotes &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/8562dbaa-6874-4c02-b55e-12a8ad13591f?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>Repetitivo-en-proceso</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R197" t="n">
@@ -22718,7 +22732,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>232</v>
+        <v>520</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -22727,29 +22741,31 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Ticket 342 - Wapsa - Callao - Ajuste Mensual - Error en datos de la IE 280/24 Ruma R24-004</t>
+          <t>Ticket 486 - Wapsa - Configuracion - Restringir que no se puede crear un hora cierre de lote diferente a las 06:59</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Abril -2024</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr"/>
+          <t>Resuelto</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>[Ver. 2.29]</t>
+        </is>
+      </c>
       <c r="G198" s="7" t="n">
-        <v>45407.79166666666</v>
+        <v>46050.79166666666</v>
       </c>
       <c r="H198" s="7" t="n">
-        <v>45407.79166666666</v>
-      </c>
-      <c r="I198" s="7" t="n">
-        <v>45413.79166666666</v>
-      </c>
+        <v>46062.46458333333</v>
+      </c>
+      <c r="I198" s="7" t="n"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -22757,31 +22773,27 @@
       </c>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="n">
-        <v>342</v>
+        <v>486</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/127ab7ed-9b0d-4ebb-b753-311b6ea49cd3?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;26-04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se revisa con &lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp; y el error se debe a que han importado con datos incorrectos los datos de los pesos para la IE&amp;nbsp;280/24 &lt;/div&gt;&lt;div&gt;\ &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr">
         <is>
-          <t>Repetitivo-en-proceso</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R198" t="n">
@@ -22795,7 +22807,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>233</v>
+        <v>522</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -22804,39 +22816,43 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ticket 343 - Wapsa - Callao - Lista de Despachos - Error en el listado de detalle de pesos de la IE 0052/24</t>
+          <t>Ticket 482 - Wapsa - Lista de Despacho - No muestra la informacion del campo Almacen vacíos al ver la IE</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Abril -2024</t>
+          <t>WAPSA\Sprint - Abril - 2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr"/>
+          <t>Resuelto</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>[Ver. 2.29]; SLA</t>
+        </is>
+      </c>
       <c r="G199" s="7" t="n">
-        <v>45407.79166666666</v>
+        <v>46090.20833333334</v>
       </c>
       <c r="H199" s="7" t="n">
-        <v>45413.79166666666</v>
-      </c>
-      <c r="I199" s="7" t="n">
-        <v>45413.79166666666</v>
-      </c>
+        <v>46090.33333333334</v>
+      </c>
+      <c r="I199" s="7" t="n"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K199" t="n">
-        <v>105866</v>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>SLA</t>
+        </is>
       </c>
       <c r="L199" t="n">
-        <v>343</v>
+        <v>482</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -22845,12 +22861,12 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/39d13485-8e1d-4bbd-b8dd-f77172463a30?fileName=image.png" alt=Image style="width:446px;height:315px;" width=446 height=315&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;26-04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se intenta listar la IE 280/24 si sale la lista vacia se crea validacion para que liste correctamente &lt;/div&gt;&lt;div&gt;26-04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se soluciona el Ticket y se envia formato a AM para firma &lt;/div&gt;&lt;div&gt;29-04 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se envia PDF firmado por AM a TICA &lt;/div&gt;&lt;div&gt;02/05 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Alexander envia para firmas internas &lt;/div&gt;&lt;div&gt;02/05 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Resuelto &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/0caa4914-6dfb-43dc-acba-dc8d7e950b43?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Corregido siguiente pase &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Repetitivo-en-proceso</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22860,7 +22876,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>Estabilización de req. de Mantenimiento</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R199" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -7505,7 +7505,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
+          <t>WAPSA\Sprint - Junio - 2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
+          <t>WAPSA\Sprint - Junio - 2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
+          <t>WAPSA\Sprint - Junio - 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
+          <t>WAPSA\Sprint - Junio - 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10644,7 +10644,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -10653,23 +10653,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ticket 452 - Guia Remisión Electronica nuevos casos</t>
+          <t>Ticket 453 - Wapsa - Envio datos WAPSA-SAP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
+          <t>WAPSA\Sprint - Marzo - 2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="7" t="n"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>[Ver. 2.25]</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>45930.79166666666</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>45937.45138888889</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>45937.57986111111</v>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10677,12 +10687,16 @@
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>452</v>
-      </c>
-      <c r="M44" t="inlineStr"/>
+        <v>453</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/225fb9c5-e533-4606-9111-042ef763c56c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Mina:&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/63d719b2-06d8-4c83-884f-50e2ce343ba6?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/392f0895-d410-422e-9107-e47dbd4df527?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d71da09a-4188-4259-a9d4-7cafa283440e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Callao :&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/20d9850d-70fe-49d7-b2f3-9e2b8b1ba05c?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/f1c8ff88-3eec-49b6-9adc-8d745baf35d4?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Ejecución Manual Envió a SAP:&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/26feb9be-d0fd-4d53-9fc2-39f8c872e02e?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -10711,7 +10725,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -10720,23 +10734,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ticket 454 - Guia Remisión Electronica nuevos casos</t>
+          <t>Ticket 471 - Wapsa - SAP Envio de datos</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
+          <t>WAPSA\Sprint - Marzo - 2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>[Ver. 2.27]; [Ver. 2.28]</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>45991.79166666666</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>46106.79166666666</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>46106.79166666666</v>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10744,12 +10768,16 @@
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>454</v>
-      </c>
-      <c r="M45" t="inlineStr"/>
+        <v>471</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/27469beb-ea0f-4125-8ece-8774b4e8b960?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/6fd9a9f1-f4d3-41d8-a8b0-630480829703?fileName=image.png" alt=Image style="box-sizing:border-box;max-width:100%;align-self:center;"&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -10778,7 +10806,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -10787,33 +10815,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ticket 453 - Wapsa - Envio datos WAPSA-SAP</t>
+          <t>Ticket 452 - Guia Remisión Electronica nuevos casos</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Junio - 2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>[Ver. 2.25]</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>45930.79166666666</v>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>45937.45138888889</v>
-      </c>
-      <c r="I46" s="7" t="n">
-        <v>45937.57986111111</v>
-      </c>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10821,16 +10839,12 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>453</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Mina:&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/63d719b2-06d8-4c83-884f-50e2ce343ba6?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/392f0895-d410-422e-9107-e47dbd4df527?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/d71da09a-4188-4259-a9d4-7cafa283440e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Callao :&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/20d9850d-70fe-49d7-b2f3-9e2b8b1ba05c?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/f1c8ff88-3eec-49b6-9adc-8d745baf35d4?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Modulo Ejecución Manual Envió a SAP:&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/26feb9be-d0fd-4d53-9fc2-39f8c872e02e?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/225fb9c5-e533-4606-9111-042ef763c56c?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -10859,7 +10873,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -10868,33 +10882,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ticket 471 - Wapsa - SAP Envio de datos</t>
+          <t>Ticket 454 - Guia Remisión Electronica nuevos casos</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Junio - 2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>[Ver. 2.27]; [Ver. 2.28]</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>45991.79166666666</v>
-      </c>
-      <c r="H47" s="7" t="n">
-        <v>46106.79166666666</v>
-      </c>
-      <c r="I47" s="7" t="n">
-        <v>46106.79166666666</v>
-      </c>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -10902,16 +10906,12 @@
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>471</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/6fd9a9f1-f4d3-41d8-a8b0-630480829703?fileName=image.png" alt=Image style="box-sizing:border-box;max-width:100%;align-self:center;"&gt;&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/27469beb-ea0f-4125-8ece-8774b4e8b960?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -18781,7 +18781,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>377</v>
+        <v>529</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ticket 402 - Wapsa - Callao - E. Shipments - Cuando ocurre un bloqueo al obtener data del Trader Wapsa no muestra el error</t>
+          <t>Ticket 480 - Wapsa - Volteo - Mejora Importacion de pesos</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -18800,15 +18800,19 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>[Ver. 2.29]</t>
+        </is>
+      </c>
       <c r="G147" s="7" t="n">
-        <v>45642.79166666666</v>
+        <v>46105.79166666666</v>
       </c>
       <c r="H147" s="7" t="n">
-        <v>45642.79166666666</v>
+        <v>46113.49097222222</v>
       </c>
       <c r="I147" s="7" t="n"/>
       <c r="J147" t="inlineStr">
@@ -18818,18 +18822,14 @@
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
-        <v>402</v>
+        <v>480</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Cuando se obtienen datos desde el Trader y se genrea algun tipo de error de bloqueo o comunicacion entra ambas Bd's no se muestra: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/c3f5d344-76e8-4365-9a52-10b27bb70854?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -18856,7 +18856,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>450</v>
+        <v>535</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ticket 442 - Wapsa - Stock Callao - Error en calculo de TMH en listado detalle por día</t>
+          <t>Ticket 490 - SAP TMS Implementación</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18875,36 +18875,727 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>[Ver. 2.24]</t>
+          <t>[Ver. 2.29]</t>
         </is>
       </c>
       <c r="G148" s="7" t="n">
-        <v>45845.25347222222</v>
+        <v>46113.46527777778</v>
       </c>
       <c r="H148" s="7" t="n">
-        <v>45845.79166666666</v>
+        <v>46134.79166666666</v>
       </c>
       <c r="I148" s="7" t="n"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WAPSA</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="n">
+        <v>490</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Requerimiento Nuevo-Area Comercial</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>No implica estabilización</t>
+        </is>
+      </c>
+      <c r="R148" t="n">
+        <v>538</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>536</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ticket 491- Wapsa - Callao - Mejoras Importacion de Leyes</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Mayo - 2026</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>[Ver. 2.29]</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="n">
+        <v>46120.52361111111</v>
+      </c>
+      <c r="H149" s="7" t="n">
+        <v>46128.79166666666</v>
+      </c>
+      <c r="I149" s="7" t="n"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="n">
+        <v>491</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Repetitivo-por-resolver</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>A&amp;S</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Estabilización de req. de Mantenimiento</t>
+        </is>
+      </c>
+      <c r="R149" t="n">
+        <v>538</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>214</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ticket 327 - Wapsa - Callao - Ajuste Mensual - Error en Month Evidence historico de Ruma R24-002</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Marzo 2024</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" s="7" t="n">
+        <v>45368.79166666666</v>
+      </c>
+      <c r="H150" s="7" t="n">
+        <v>45369.79166666666</v>
+      </c>
+      <c r="I150" s="7" t="n">
+        <v>45376.79166666666</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>102692</v>
+      </c>
+      <c r="L150" t="n">
+        <v>315</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/6493e66f-26e8-4eb8-a1be-dc375450192d?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;La ruma 45 es parte del historico de la ruma 002 &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;19/03 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; se envia&amp;nbsp;para firmas de Alejandro &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Repetitivo-en-proceso</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>A&amp;S</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Estabilización de req. de Mantenimiento</t>
+        </is>
+      </c>
+      <c r="R150" t="n">
+        <v>538</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>516</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ticket 474 - Wapsa - Agregar Ajuste D en Reporte de Ajuste Mensual En Linea</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Marzo - 2026</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>[Ver. 2.28]</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="n">
+        <v>46054.79166666666</v>
+      </c>
+      <c r="H151" s="7" t="n">
+        <v>46062.43472222222</v>
+      </c>
+      <c r="I151" s="7" t="n">
+        <v>46106.79166666666</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>474</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Requerimiento Nuevo-Area Comercial</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>No implica estabilización</t>
+        </is>
+      </c>
+      <c r="R151" t="n">
+        <v>538</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>527</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ticket 486 - Wapsa - Ajuste Mensual - Muestra erroneamente los ingresos de la ruma R26-001</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Marzo - 2026</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" s="7" t="n">
+        <v>46097.56319444445</v>
+      </c>
+      <c r="H152" s="7" t="n">
+        <v>46097.56319444445</v>
+      </c>
+      <c r="I152" s="7" t="n">
+        <v>46097.56319444445</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="n">
+        <v>486</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/a6f748b8-2d6a-423d-b875-20010a0b164e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Solución: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;El usuario no recordo que no esta contemplado en el lógica moviemientos internos por lo que lo cambio a junta y todo funciono como lo esperado &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Error del usuario</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>No implica estabilización</t>
+        </is>
+      </c>
+      <c r="R152" t="n">
+        <v>538</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>362</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ticket 397 - Wapsa - Callao - Evidence Of Shipments - Evidence of Shipment nuevo caso NC</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Marzo - 2025</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" s="7" t="n">
+        <v>45725.79166666666</v>
+      </c>
+      <c r="H153" s="7" t="n">
+        <v>45725.79166666666</v>
+      </c>
+      <c r="I153" s="7" t="n">
+        <v>45725.79166666666</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="n">
+        <v>397</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Se requiere considerar nuevo caso que viene de la vista del Trader para ser consumido por el modulo del wapsa Evidence of shipment.&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Nicolas se hará cargo de la modificación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Luego tenemos que importar y ver esta operación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>A&amp;S</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Estabilización de req. de Mantenimiento</t>
+        </is>
+      </c>
+      <c r="R153" t="n">
+        <v>538</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>234</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ticket 344 - Wapsa - Callao - Lista Despacho - Alerta despachos pesos 0 no manda datos sobre las IE's</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Junio 2024</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" s="7" t="n">
+        <v>45410.79166666666</v>
+      </c>
+      <c r="H154" s="7" t="n">
+        <v>45454.79166666666</v>
+      </c>
+      <c r="I154" s="7" t="n">
+        <v>45460.79166666666</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>109586</v>
+      </c>
+      <c r="L154" t="n">
+        <v>344</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/83c9d948-689e-4ab1-88be-3336f3a5a233?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;la IE en cuestion no ha cumplido los 7 dias de registrada hasta la fecha y pos eso no sale en el listado &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/12b0b23a-f9f8-4862-ba1c-6120f6c4bdf5?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;04/06&amp;nbsp;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se corrige listado para que filtre correctamnete utilizando los lotes actual y el anterior. &lt;/div&gt;&lt;div&gt;Se enviara como tikcet. Se envia un formato para firma de AM &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;AM Envia docuemento firmado. Se adjunta &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Wally solicita en reunion del 11/06, que el listado incluya un lote mas hacia atras del tiempo. Se haran los cambios. S emueve Ticket a estado en Desarrollo &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se agrega cambio al script y se envia a TICA 12/06/2023 13:24 pm &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Repetitivo-en-proceso</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>A&amp;S</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Estabilización de req. de Mantenimiento</t>
+        </is>
+      </c>
+      <c r="R154" t="n">
+        <v>538</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>268</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ticket 361 - Wapsa - Callao - Ajuste Mensual - Problema en  ajuste en línea R24-013 - JUNIO</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Junio 2024</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" s="7" t="n">
+        <v>45466.79166666666</v>
+      </c>
+      <c r="H155" s="7" t="n">
+        <v>45466.79166666666</v>
+      </c>
+      <c r="I155" s="7" t="n">
+        <v>45466.79166666666</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="n">
+        <v>361</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Diego Cardenas reporta&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/b7318f47-b451-4aa8-b5d8-729247a0d339?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;24/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se detecta un repeso total duplicado: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/0b3e7192-c054-4a41-a921-7f64bd67bee5?fileName=WhatsApp%20Image%202024-06-24%20at%2016.49.35.jpeg" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;&amp;nbsp;Responde via mail &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/51ef8424-2061-4f19-9ade-d42b9a5351cf?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Error del usuario</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>No implica estabilización</t>
+        </is>
+      </c>
+      <c r="R155" t="n">
+        <v>538</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>377</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ticket 402 - Wapsa - Callao - E. Shipments - Cuando ocurre un bloqueo al obtener data del Trader Wapsa no muestra el error</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Junio - 2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" s="7" t="n">
+        <v>45642.79166666666</v>
+      </c>
+      <c r="H156" s="7" t="n">
+        <v>45642.79166666666</v>
+      </c>
+      <c r="I156" s="7" t="n"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="n">
+        <v>402</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Cuando se obtienen datos desde el Trader y se genrea algun tipo de error de bloqueo o comunicacion entra ambas Bd's no se muestra: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/c3f5d344-76e8-4365-9a52-10b27bb70854?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>A&amp;S</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Estabilización de req. de Mantenimiento</t>
+        </is>
+      </c>
+      <c r="R156" t="n">
+        <v>538</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>450</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ticket 442 - Wapsa - Stock Callao - Error en calculo de TMH en listado detalle por día</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>WAPSA\Sprint - Junio - 2026</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>[Ver. 2.24]</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="n">
+        <v>45845.25347222222</v>
+      </c>
+      <c r="H157" s="7" t="n">
+        <v>45845.79166666666</v>
+      </c>
+      <c r="I157" s="7" t="n"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Wapsa Web</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="n">
         <v>442</v>
       </c>
-      <c r="M148" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr">
+      <c r="N157" t="inlineStr">
         <is>
           <t>&lt;div&gt;&lt;p style="margin:0cm;font-size:11pt;font-family:Calibri, sans-serif;"&gt;Este ticket tiene como objetivo atender el requerimiento de
 Diego Cárdenas el cual ha detecto que se debe cambiar la fecha que utiliza el
@@ -18913,681 +19604,14 @@
 la de otros reportes. &lt;/p&gt;&lt;br&gt; &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Nuevo</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
         <is>
           <t>S&amp;C Sistemas</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>Estabilización de req. de Mantenimiento</t>
-        </is>
-      </c>
-      <c r="R148" t="n">
-        <v>538</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>Callao</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>529</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Ticket 480 - Wapsa - Volteo - Mejora Importacion de pesos</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Resuelto</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>[Ver. 2.29]</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="n">
-        <v>46105.79166666666</v>
-      </c>
-      <c r="H149" s="7" t="n">
-        <v>46113.49097222222</v>
-      </c>
-      <c r="I149" s="7" t="n"/>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="n">
-        <v>480</v>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>A&amp;S</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>Estabilización de req. de Mantenimiento</t>
-        </is>
-      </c>
-      <c r="R149" t="n">
-        <v>538</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>Callao</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>535</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Ticket 490 - SAP TMS Implementación</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Resuelto</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>[Ver. 2.29]</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="n">
-        <v>46113.46527777778</v>
-      </c>
-      <c r="H150" s="7" t="n">
-        <v>46134.79166666666</v>
-      </c>
-      <c r="I150" s="7" t="n"/>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>WAPSA</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="n">
-        <v>490</v>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>No implica estabilización</t>
-        </is>
-      </c>
-      <c r="R150" t="n">
-        <v>538</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>Callao</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>536</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Ticket 491- Wapsa - Callao - Mejoras Importacion de Leyes</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Resuelto</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>[Ver. 2.29]</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="n">
-        <v>46120.52361111111</v>
-      </c>
-      <c r="H151" s="7" t="n">
-        <v>46128.79166666666</v>
-      </c>
-      <c r="I151" s="7" t="n"/>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="n">
-        <v>491</v>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Repetitivo-por-resolver</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>A&amp;S</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>Estabilización de req. de Mantenimiento</t>
-        </is>
-      </c>
-      <c r="R151" t="n">
-        <v>538</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>Callao</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>542</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Ticket 493 - Wapsa - Callao - Utilizar Fechamcp para las operaciones de ingresos</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" s="7" t="n"/>
-      <c r="H152" s="7" t="n"/>
-      <c r="I152" s="7" t="n"/>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="n">
-        <v>538</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>Callao</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>214</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Ticket 327 - Wapsa - Callao - Ajuste Mensual - Error en Month Evidence historico de Ruma R24-002</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Marzo 2024</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" s="7" t="n">
-        <v>45368.79166666666</v>
-      </c>
-      <c r="H153" s="7" t="n">
-        <v>45369.79166666666</v>
-      </c>
-      <c r="I153" s="7" t="n">
-        <v>45376.79166666666</v>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K153" t="n">
-        <v>102692</v>
-      </c>
-      <c r="L153" t="n">
-        <v>315</v>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/6493e66f-26e8-4eb8-a1be-dc375450192d?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;La ruma 45 es parte del historico de la ruma 002 &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;19/03 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; se envia&amp;nbsp;para firmas de Alejandro &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Repetitivo-en-proceso</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>A&amp;S</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>Estabilización de req. de Mantenimiento</t>
-        </is>
-      </c>
-      <c r="R153" t="n">
-        <v>538</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>Callao</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>516</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Ticket 474 - Wapsa - Agregar Ajuste D en Reporte de Ajuste Mensual En Linea</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>[Ver. 2.28]</t>
-        </is>
-      </c>
-      <c r="G154" s="7" t="n">
-        <v>46054.79166666666</v>
-      </c>
-      <c r="H154" s="7" t="n">
-        <v>46062.43472222222</v>
-      </c>
-      <c r="I154" s="7" t="n">
-        <v>46106.79166666666</v>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="n">
-        <v>474</v>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>No implica estabilización</t>
-        </is>
-      </c>
-      <c r="R154" t="n">
-        <v>538</v>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>Callao</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>527</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Ticket 486 - Wapsa - Ajuste Mensual - Muestra erroneamente los ingresos de la ruma R26-001</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" s="7" t="n">
-        <v>46097.56319444445</v>
-      </c>
-      <c r="H155" s="7" t="n">
-        <v>46097.56319444445</v>
-      </c>
-      <c r="I155" s="7" t="n">
-        <v>46097.56319444445</v>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="n">
-        <v>486</v>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/a6f748b8-2d6a-423d-b875-20010a0b164e?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Solución: &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;El usuario no recordo que no esta contemplado en el lógica moviemientos internos por lo que lo cambio a junta y todo funciono como lo esperado &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>Error del usuario</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>No implica estabilización</t>
-        </is>
-      </c>
-      <c r="R155" t="n">
-        <v>538</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>Callao</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>362</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Ticket 397 - Wapsa - Callao - Evidence Of Shipments - Evidence of Shipment nuevo caso NC</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Marzo - 2025</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" s="7" t="n">
-        <v>45725.79166666666</v>
-      </c>
-      <c r="H156" s="7" t="n">
-        <v>45725.79166666666</v>
-      </c>
-      <c r="I156" s="7" t="n">
-        <v>45725.79166666666</v>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="n">
-        <v>397</v>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Se requiere considerar nuevo caso que viene de la vista del Trader para ser consumido por el modulo del wapsa Evidence of shipment.&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Nicolas se hará cargo de la modificación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Luego tenemos que importar y ver esta operación &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>A&amp;S</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>Estabilización de req. de Mantenimiento</t>
-        </is>
-      </c>
-      <c r="R156" t="n">
-        <v>538</v>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>Callao</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>234</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Ticket 344 - Wapsa - Callao - Lista Despacho - Alerta despachos pesos 0 no manda datos sobre las IE's</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>WAPSA\Sprint - Junio 2024</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" s="7" t="n">
-        <v>45410.79166666666</v>
-      </c>
-      <c r="H157" s="7" t="n">
-        <v>45454.79166666666</v>
-      </c>
-      <c r="I157" s="7" t="n">
-        <v>45460.79166666666</v>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>Wapsa Web</t>
-        </is>
-      </c>
-      <c r="K157" t="n">
-        <v>109586</v>
-      </c>
-      <c r="L157" t="n">
-        <v>344</v>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/83c9d948-689e-4ab1-88be-3336f3a5a233?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;la IE en cuestion no ha cumplido los 7 dias de registrada hasta la fecha y pos eso no sale en el listado &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/12b0b23a-f9f8-4862-ba1c-6120f6c4bdf5?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;04/06&amp;nbsp;&lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se corrige listado para que filtre correctamnete utilizando los lotes actual y el anterior. &lt;/div&gt;&lt;div&gt;Se enviara como tikcet. Se envia un formato para firma de AM &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;AM Envia docuemento firmado. Se adjunta &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Wally solicita en reunion del 11/06, que el listado incluya un lote mas hacia atras del tiempo. Se haran los cambios. S emueve Ticket a estado en Desarrollo &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se agrega cambio al script y se envia a TICA 12/06/2023 13:24 pm &lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>Repetitivo-en-proceso</t>
-        </is>
-      </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -19606,7 +19630,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>268</v>
+        <v>542</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -19615,29 +19639,25 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ticket 361 - Wapsa - Callao - Ajuste Mensual - Problema en  ajuste en línea R24-013 - JUNIO</t>
+          <t>Ticket 493 - Wapsa - Callao - Utilizar Fechamcp para las operaciones de ingresos</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio 2024</t>
+          <t>WAPSA\Sprint - Junio - 2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>En Testing</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" s="7" t="n">
-        <v>45466.79166666666</v>
-      </c>
-      <c r="H158" s="7" t="n">
-        <v>45466.79166666666</v>
-      </c>
-      <c r="I158" s="7" t="n">
-        <v>45466.79166666666</v>
-      </c>
+        <v>46155.79166666666</v>
+      </c>
+      <c r="H158" s="7" t="n"/>
+      <c r="I158" s="7" t="n"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -19645,18 +19665,14 @@
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="n">
-        <v>361</v>
+        <v>493</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Diego Cardenas reporta&amp;nbsp; &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/b7318f47-b451-4aa8-b5d8-729247a0d339?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;24/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Se detecta un repeso total duplicado: &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/0b3e7192-c054-4a41-a921-7f64bd67bee5?fileName=WhatsApp%20Image%202024-06-24%20at%2016.49.35.jpeg" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;a href="#" data-vss-mention="version:2.0,758aadd7-85a1-6893-9bad-8face9b229c8"&gt;@Frank Macavilca&lt;/a&gt;&amp;nbsp;&amp;nbsp;Responde via mail &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/51ef8424-2061-4f19-9ade-d42b9a5351cf?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -19664,12 +19680,12 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Error del usuario</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización de req. de Mantenimiento</t>
         </is>
       </c>
       <c r="R158" t="n">
@@ -23360,7 +23376,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>340</v>
+        <v>518</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -23369,7 +23385,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Ticket 384 - Wapsa - General - Configuracion -  Crear Modulo para guardar las plantilla de importacion de datos</t>
+          <t>Ticket 476 - Wapsa -Varios - Mejora Listado para elegir vagones en Arribo, Entrega y Salida</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -23379,14 +23395,20 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Nuevo</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>[Ver. 2.29]</t>
+        </is>
+      </c>
       <c r="G206" s="7" t="n">
-        <v>45951.79166666666</v>
-      </c>
-      <c r="H206" s="7" t="n"/>
+        <v>46047.79166666666</v>
+      </c>
+      <c r="H206" s="7" t="n">
+        <v>46104.26111111111</v>
+      </c>
       <c r="I206" s="7" t="n"/>
       <c r="J206" t="inlineStr">
         <is>
@@ -23395,14 +23417,14 @@
       </c>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="n">
-        <v>384</v>
-      </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr"/>
+        <v>476</v>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/8562dbaa-6874-4c02-b55e-12a8ad13591f?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O206" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -23429,7 +23451,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -23438,7 +23460,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ticket 476 - Wapsa -Varios - Mejora Listado para elegir vagones en Arribo, Entrega y Salida</t>
+          <t>Ticket 486 - Wapsa - Lotes - Validar que la hora de cierre del lote sea únicamente 06:59</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -23448,7 +23470,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Resuelto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -23457,10 +23479,10 @@
         </is>
       </c>
       <c r="G207" s="7" t="n">
-        <v>46047.79166666666</v>
+        <v>46050.79166666666</v>
       </c>
       <c r="H207" s="7" t="n">
-        <v>46104.26111111111</v>
+        <v>46062.46458333333</v>
       </c>
       <c r="I207" s="7" t="n"/>
       <c r="J207" t="inlineStr">
@@ -23470,14 +23492,14 @@
       </c>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="n">
-        <v>476</v>
-      </c>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/8562dbaa-6874-4c02-b55e-12a8ad13591f?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -23504,7 +23526,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -23513,7 +23535,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Ticket 486 - Wapsa - Lotes - Validar que la hora de cierre del lote sea únicamente 06:59</t>
+          <t>Ticket 482 - Wapsa - Lista de Despacho - No muestra la informacion del campo Almacen vacíos al ver la IE</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -23523,19 +23545,19 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Resuelto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>[Ver. 2.29]</t>
+          <t>[Ver. 2.29]; SLA</t>
         </is>
       </c>
       <c r="G208" s="7" t="n">
-        <v>46050.79166666666</v>
+        <v>46090.20833333334</v>
       </c>
       <c r="H208" s="7" t="n">
-        <v>46062.46458333333</v>
+        <v>46090.33333333334</v>
       </c>
       <c r="I208" s="7" t="n"/>
       <c r="J208" t="inlineStr">
@@ -23543,16 +23565,24 @@
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>SLA</t>
+        </is>
+      </c>
       <c r="L208" t="n">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/0caa4914-6dfb-43dc-acba-dc8d7e950b43?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Corregido siguiente pase &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O208" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -23560,7 +23590,7 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>A&amp;S</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
@@ -23579,7 +23609,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -23588,7 +23618,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ticket 482 - Wapsa - Lista de Despacho - No muestra la informacion del campo Almacen vacíos al ver la IE</t>
+          <t>Ticket 492-  Wapsa - Incrementar tiempo de sesion del usuario MCP</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23598,19 +23628,19 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Resuelto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>[Ver. 2.29]; SLA</t>
+          <t>[Ver. 2.29]</t>
         </is>
       </c>
       <c r="G209" s="7" t="n">
-        <v>46090.20833333334</v>
+        <v>46128.79166666666</v>
       </c>
       <c r="H209" s="7" t="n">
-        <v>46090.33333333334</v>
+        <v>46129.80625</v>
       </c>
       <c r="I209" s="7" t="n"/>
       <c r="J209" t="inlineStr">
@@ -23618,24 +23648,16 @@
           <t>Wapsa Web</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>SLA</t>
-        </is>
-      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="n">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/0caa4914-6dfb-43dc-acba-dc8d7e950b43?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;Corregido siguiente pase &lt;/div&gt;&lt;div&gt; &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -23643,7 +23665,7 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>A&amp;S</t>
+          <t>Requerimiento Nuevo-Area Comercial</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -23662,7 +23684,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -23671,31 +23693,33 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Ticket 492-  Wapsa - Incrementar tiempo de sesion del usuario MCP</t>
+          <t>Ticket 483 - Wapsa - Lista de Despacho - Error de formato de fechas al exportar detalle de despachos de pesos de una IE</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Mayo - 2026</t>
+          <t>WAPSA\Sprint - Marzo - 2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Resuelto</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>[Ver. 2.29]</t>
+          <t>[Ver. 2.28]; SLA</t>
         </is>
       </c>
       <c r="G210" s="7" t="n">
-        <v>46128.79166666666</v>
+        <v>46089.79166666666</v>
       </c>
       <c r="H210" s="7" t="n">
-        <v>46129.80625</v>
-      </c>
-      <c r="I210" s="7" t="n"/>
+        <v>46089.79166666666</v>
+      </c>
+      <c r="I210" s="7" t="n">
+        <v>46089.79166666666</v>
+      </c>
       <c r="J210" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -23703,14 +23727,14 @@
       </c>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="n">
-        <v>492</v>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr"/>
+        <v>483</v>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;Al importar información como Guías/Pesos a una IE de la Lista de Despacho el formato de fecha esta errado, WAPSA interpreta erróneamente la info y graba la fecha con un formato distinto al del Excel de importación, favor corregir ya que no esta quedando grabada correctamente la información en WAPSA.&lt;br&gt; &lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="O210" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -23718,7 +23742,7 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Requerimiento Nuevo-Area Comercial</t>
+          <t>Omisión del usuario</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
@@ -23737,7 +23761,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -23746,7 +23770,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ticket 483 - Wapsa - Lista de Despacho - Error de formato de fechas al exportar detalle de despachos de pesos de una IE</t>
+          <t>Ticket 485 - WAPSA - Ajuste Final no deja registrar debido a validacion</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -23761,31 +23785,33 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>[Ver. 2.28]; SLA</t>
+          <t>[Ver. 2.28]</t>
         </is>
       </c>
       <c r="G211" s="7" t="n">
-        <v>46089.79166666666</v>
+        <v>46096.71458333333</v>
       </c>
       <c r="H211" s="7" t="n">
-        <v>46089.79166666666</v>
-      </c>
-      <c r="I211" s="7" t="n">
-        <v>46089.79166666666</v>
-      </c>
+        <v>46096.71458333333</v>
+      </c>
+      <c r="I211" s="7" t="n"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Wapsa Web</t>
+          <t>WAPSA</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="n">
-        <v>483</v>
-      </c>
-      <c r="M211" t="inlineStr"/>
+        <v>485</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+        </is>
+      </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>&lt;div&gt;Al importar información como Guías/Pesos a una IE de la Lista de Despacho el formato de fecha esta errado, WAPSA interpreta erróneamente la info y graba la fecha con un formato distinto al del Excel de importación, favor corregir ya que no esta quedando grabada correctamente la información en WAPSA.&lt;br&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;He registrado el ultimo movimiento de esa ruma a las 23:00 hrs del 14/03, el ajuste lo estoy poniendo como 14/03 23:59, por que si le pongo 15/03 que fue en realidad la operación me sale otro error que dice que la fecha no puede ser posterior a la fecha de resumen&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/9970cbf3-cd07-41b8-8c16-d3ff09d6b2f6?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -23795,12 +23821,12 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Omisión del usuario</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>No implica estabilización</t>
+          <t>Estabilización por proyecto</t>
         </is>
       </c>
       <c r="R211" t="n">
@@ -23814,7 +23840,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>526</v>
+        <v>255</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -23823,12 +23849,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Ticket 485 - WAPSA - Ajuste Final no deja registrar debido a validacion</t>
+          <t>Ticket 358 - Wapsa - General - Informacion sobre propuesta de mejoras para los Pases a produccion, tickets y ambientes de pruebas</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Marzo - 2026</t>
+          <t>WAPSA\Sprint - Junio 2024</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -23836,35 +23862,33 @@
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>[Ver. 2.28]</t>
-        </is>
-      </c>
+      <c r="F212" t="inlineStr"/>
       <c r="G212" s="7" t="n">
-        <v>46096.71458333333</v>
+        <v>45453.79166666666</v>
       </c>
       <c r="H212" s="7" t="n">
-        <v>46096.71458333333</v>
-      </c>
-      <c r="I212" s="7" t="n"/>
+        <v>45454.79166666666</v>
+      </c>
+      <c r="I212" s="7" t="n">
+        <v>45454.79166666666</v>
+      </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>WAPSA</t>
+          <t>Wapsa Web</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="n">
-        <v>485</v>
+        <v>358</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Frank Macavilca &lt;dmacavilca@syc-sistemas.com&gt;</t>
+          <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>&lt;div&gt;&lt;b&gt;Descripción:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;He registrado el ultimo movimiento de esa ruma a las 23:00 hrs del 14/03, el ajuste lo estoy poniendo como 14/03 23:59, por que si le pongo 15/03 que fue en realidad la operación me sale otro error que dice que la fecha no puede ser posterior a la fecha de resumen&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/9970cbf3-cd07-41b8-8c16-d3ff09d6b2f6?fileName=image.png" alt=Image&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;Solución:&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;&lt;div&gt;&lt;b&gt;&lt;br&gt;&lt;/b&gt; &lt;/div&gt;</t>
+          <t>&lt;div&gt;Nicolas solicitar completar infromacion resulotante de uan reunion con Chnalco sobre propuestas de mejoras acerca de los Pases a produccion, tickets y ambientes de pruebas &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/5ee0bb74-9fda-4771-adab-e78824534323?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Reunion con NV y DM para revisar propuestas de mejoras. &lt;/div&gt;&lt;div&gt;12/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se envian propuestas a evaluacion de NV &lt;/div&gt;</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -23874,12 +23898,12 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>S&amp;C Sistemas</t>
+          <t>Externos</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>Estabilización por proyecto</t>
+          <t>No implica estabilización</t>
         </is>
       </c>
       <c r="R212" t="n">
@@ -23893,7 +23917,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>255</v>
+        <v>340</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -23902,29 +23926,25 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Ticket 358 - Wapsa - General - Informacion sobre propuesta de mejoras para los Pases a produccion, tickets y ambientes de pruebas</t>
+          <t>Ticket 384 - Wapsa - General - Configuracion -  Crear Modulo para guardar las plantilla de importacion de datos</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>WAPSA\Sprint - Junio 2024</t>
+          <t>WAPSA\Sprint - Junio - 2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" s="7" t="n">
-        <v>45453.79166666666</v>
-      </c>
-      <c r="H213" s="7" t="n">
-        <v>45454.79166666666</v>
-      </c>
-      <c r="I213" s="7" t="n">
-        <v>45454.79166666666</v>
-      </c>
+        <v>45951.79166666666</v>
+      </c>
+      <c r="H213" s="7" t="n"/>
+      <c r="I213" s="7" t="n"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>Wapsa Web</t>
@@ -23932,18 +23952,14 @@
       </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="n">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Cristian Pastor Artigas &lt;cartigas@syc-sistemas.com&gt;</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;Nicolas solicitar completar infromacion resulotante de uan reunion con Chnalco sobre propuestas de mejoras acerca de los Pases a produccion, tickets y ambientes de pruebas &lt;/div&gt;&lt;div&gt;&lt;img src="https://dev.azure.com/SycSistemas/833274e7-44d5-4093-8f90-9bab7903e605/_apis/wit/attachments/5ee0bb74-9fda-4771-adab-e78824534323?fileName=image.png" alt=Image&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;&lt;br&gt; &lt;/div&gt;&lt;div&gt;11/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp;Reunion con NV y DM para revisar propuestas de mejoras. &lt;/div&gt;&lt;div&gt;12/06 &lt;a href="#" data-vss-mention="version:2.0,d542a3a1-6dfe-6329-8f4f-0c05b9f92ebc"&gt;@Cristian Pastor Artigas&lt;/a&gt;&amp;nbsp; Se envian propuestas a evaluacion de NV &lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -23951,7 +23967,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Externos</t>
+          <t>S&amp;C Sistemas</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
